--- a/Data/ModelResponse/1A/evaluation/1A_evaluation_summary.xlsx
+++ b/Data/ModelResponse/1A/evaluation/1A_evaluation_summary.xlsx
@@ -546,52 +546,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4935416666666667</v>
+        <v>0.49515625</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4935416666666667</v>
+        <v>0.49515625</v>
       </c>
       <c r="H2" t="n">
         <v>9554</v>
       </c>
       <c r="I2" t="n">
-        <v>14174</v>
+        <v>12305</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4940031042754339</v>
+        <v>0.4943518894758228</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7328867490056521</v>
+        <v>0.6366966715511827</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5901888064733648</v>
+        <v>0.5565670890708632</v>
       </c>
       <c r="M2" t="n">
         <v>9646</v>
       </c>
       <c r="N2" t="n">
-        <v>5026</v>
+        <v>6895</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4922403501790689</v>
+        <v>0.4965917331399565</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2564793696869169</v>
+        <v>0.3549657889280531</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3372410032715376</v>
+        <v>0.4140015718517623</v>
       </c>
       <c r="R2" t="n">
-        <v>7002</v>
+        <v>6083</v>
       </c>
       <c r="S2" t="n">
-        <v>2552</v>
+        <v>3471</v>
       </c>
       <c r="T2" t="n">
-        <v>7172</v>
+        <v>6222</v>
       </c>
       <c r="U2" t="n">
-        <v>2474</v>
+        <v>3424</v>
       </c>
     </row>
   </sheetData>
@@ -734,52 +734,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.48875</v>
+        <v>0.46875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.48875</v>
+        <v>0.46875</v>
       </c>
       <c r="H2" t="n">
         <v>387</v>
       </c>
       <c r="I2" t="n">
-        <v>630</v>
+        <v>492</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4825396825396825</v>
+        <v>0.4613821138211382</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7855297157622739</v>
+        <v>0.58656330749354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5978367748279253</v>
+        <v>0.5164960182025029</v>
       </c>
       <c r="M2" t="n">
         <v>413</v>
       </c>
       <c r="N2" t="n">
-        <v>170</v>
+        <v>308</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5117647058823529</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2106537530266344</v>
+        <v>0.3583535108958838</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2984562607204117</v>
+        <v>0.4105409153952844</v>
       </c>
       <c r="R2" t="n">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="S2" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="T2" t="n">
-        <v>326</v>
+        <v>265</v>
       </c>
       <c r="U2" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -801,52 +801,52 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.51625</v>
+        <v>0.49375</v>
       </c>
       <c r="G3" t="n">
-        <v>0.51625</v>
+        <v>0.49375</v>
       </c>
       <c r="H3" t="n">
         <v>404</v>
       </c>
       <c r="I3" t="n">
-        <v>663</v>
+        <v>521</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5128205128205128</v>
+        <v>0.4990403071017274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.6435643564356436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6373008434864105</v>
+        <v>0.5621621621621622</v>
       </c>
       <c r="M3" t="n">
         <v>396</v>
       </c>
       <c r="N3" t="n">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5328467153284672</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1843434343434343</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2739212007504691</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="S3" t="n">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="T3" t="n">
-        <v>323</v>
+        <v>261</v>
       </c>
       <c r="U3" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -868,52 +868,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4925</v>
+        <v>0.50125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4925</v>
+        <v>0.50125</v>
       </c>
       <c r="H4" t="n">
         <v>821</v>
       </c>
       <c r="I4" t="n">
-        <v>903</v>
+        <v>1017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5049833887043189</v>
+        <v>0.511307767944936</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5554202192448234</v>
+        <v>0.633373934226553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5290023201856148</v>
+        <v>0.5658324265505985</v>
       </c>
       <c r="M4" t="n">
         <v>779</v>
       </c>
       <c r="N4" t="n">
-        <v>697</v>
+        <v>583</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4763271162123386</v>
+        <v>0.483704974271012</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4261874197689345</v>
+        <v>0.362002567394095</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4498644986449865</v>
+        <v>0.4140969162995595</v>
       </c>
       <c r="R4" t="n">
-        <v>456</v>
+        <v>520</v>
       </c>
       <c r="S4" t="n">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="T4" t="n">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="U4" t="n">
-        <v>332</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -935,52 +935,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.489375</v>
+        <v>0.50625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.489375</v>
+        <v>0.50625</v>
       </c>
       <c r="H5" t="n">
         <v>805</v>
       </c>
       <c r="I5" t="n">
-        <v>1246</v>
+        <v>961</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4951845906902086</v>
+        <v>0.5078043704474505</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7664596273291926</v>
+        <v>0.6062111801242236</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6016577279375914</v>
+        <v>0.552661381653454</v>
       </c>
       <c r="M5" t="n">
         <v>795</v>
       </c>
       <c r="N5" t="n">
-        <v>354</v>
+        <v>639</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4689265536723164</v>
+        <v>0.5039123630672926</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2088050314465409</v>
+        <v>0.4050314465408805</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2889469103568321</v>
+        <v>0.4490934449093445</v>
       </c>
       <c r="R5" t="n">
-        <v>617</v>
+        <v>488</v>
       </c>
       <c r="S5" t="n">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="T5" t="n">
-        <v>629</v>
+        <v>473</v>
       </c>
       <c r="U5" t="n">
-        <v>166</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
@@ -1002,52 +1002,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.503125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.503125</v>
       </c>
       <c r="H6" t="n">
         <v>821</v>
       </c>
       <c r="I6" t="n">
-        <v>1309</v>
+        <v>1156</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5095492742551566</v>
+        <v>0.5112456747404844</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8124238733252132</v>
+        <v>0.7198538367844093</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6262910798122066</v>
+        <v>0.5978755690440061</v>
       </c>
       <c r="M6" t="n">
         <v>779</v>
       </c>
       <c r="N6" t="n">
-        <v>291</v>
+        <v>444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4707903780068728</v>
+        <v>0.481981981981982</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1758664955070603</v>
+        <v>0.2747111681643132</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2560747663551401</v>
+        <v>0.3499591169255928</v>
       </c>
       <c r="R6" t="n">
-        <v>667</v>
+        <v>591</v>
       </c>
       <c r="S6" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="T6" t="n">
-        <v>642</v>
+        <v>565</v>
       </c>
       <c r="U6" t="n">
-        <v>137</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
@@ -1069,52 +1069,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.46375</v>
+        <v>0.4675</v>
       </c>
       <c r="G7" t="n">
-        <v>0.46375</v>
+        <v>0.4675</v>
       </c>
       <c r="H7" t="n">
         <v>740</v>
       </c>
       <c r="I7" t="n">
-        <v>1570</v>
+        <v>1512</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4624203821656051</v>
+        <v>0.462962962962963</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9810810810810811</v>
+        <v>0.9459459459459459</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.6216696269982238</v>
       </c>
       <c r="M7" t="n">
         <v>860</v>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0186046511627907</v>
+        <v>0.05581395348837209</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03595505617977528</v>
+        <v>0.1012658227848101</v>
       </c>
       <c r="R7" t="n">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="S7" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="T7" t="n">
-        <v>844</v>
+        <v>812</v>
       </c>
       <c r="U7" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -1136,52 +1136,52 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.485</v>
+        <v>0.4825</v>
       </c>
       <c r="G8" t="n">
-        <v>0.485</v>
+        <v>0.4825</v>
       </c>
       <c r="H8" t="n">
         <v>769</v>
       </c>
       <c r="I8" t="n">
-        <v>1397</v>
+        <v>1235</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4803149606299212</v>
+        <v>0.4761133603238866</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8725617685305592</v>
+        <v>0.764629388816645</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6195752539242844</v>
+        <v>0.5868263473053893</v>
       </c>
       <c r="M8" t="n">
         <v>831</v>
       </c>
       <c r="N8" t="n">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5172413793103449</v>
+        <v>0.5041095890410959</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1263537906137184</v>
+        <v>0.2214199759326113</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2030947775628626</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="R8" t="n">
-        <v>671</v>
+        <v>588</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="T8" t="n">
-        <v>726</v>
+        <v>647</v>
       </c>
       <c r="U8" t="n">
-        <v>105</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
@@ -1203,52 +1203,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.51</v>
+        <v>0.486875</v>
       </c>
       <c r="G9" t="n">
-        <v>0.51</v>
+        <v>0.486875</v>
       </c>
       <c r="H9" t="n">
         <v>822</v>
       </c>
       <c r="I9" t="n">
-        <v>1294</v>
+        <v>1019</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5146831530139103</v>
+        <v>0.5004906771344455</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8102189781021898</v>
+        <v>0.6204379562043796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6294896030245747</v>
+        <v>0.5540467137425312</v>
       </c>
       <c r="M9" t="n">
         <v>778</v>
       </c>
       <c r="N9" t="n">
-        <v>306</v>
+        <v>581</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.4629948364888124</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1928020565552699</v>
+        <v>0.345758354755784</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2767527675276753</v>
+        <v>0.3958793230316409</v>
       </c>
       <c r="R9" t="n">
-        <v>666</v>
+        <v>510</v>
       </c>
       <c r="S9" t="n">
-        <v>156</v>
+        <v>312</v>
       </c>
       <c r="T9" t="n">
-        <v>628</v>
+        <v>509</v>
       </c>
       <c r="U9" t="n">
-        <v>150</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -1270,52 +1270,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.501875</v>
+        <v>0.505625</v>
       </c>
       <c r="G10" t="n">
-        <v>0.501875</v>
+        <v>0.505625</v>
       </c>
       <c r="H10" t="n">
         <v>804</v>
       </c>
       <c r="I10" t="n">
-        <v>1493</v>
+        <v>1447</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5023442732752846</v>
+        <v>0.5044920525224602</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9328358208955224</v>
+        <v>0.9079601990049752</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6530256856769699</v>
+        <v>0.6486006219458018</v>
       </c>
       <c r="M10" t="n">
         <v>796</v>
       </c>
       <c r="N10" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4953271028037383</v>
+        <v>0.5163398692810458</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06658291457286432</v>
+        <v>0.09924623115577889</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1173864894795127</v>
+        <v>0.166491043203372</v>
       </c>
       <c r="R10" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="S10" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="T10" t="n">
-        <v>743</v>
+        <v>717</v>
       </c>
       <c r="U10" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -1337,52 +1337,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.490625</v>
+        <v>0.491875</v>
       </c>
       <c r="G11" t="n">
-        <v>0.490625</v>
+        <v>0.491875</v>
       </c>
       <c r="H11" t="n">
         <v>812</v>
       </c>
       <c r="I11" t="n">
-        <v>857</v>
+        <v>533</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4982497082847141</v>
+        <v>0.49906191369606</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5258620689655172</v>
+        <v>0.3275862068965517</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5116836428999401</v>
+        <v>0.3955390334572491</v>
       </c>
       <c r="M11" t="n">
         <v>788</v>
       </c>
       <c r="N11" t="n">
-        <v>743</v>
+        <v>1067</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4818304172274562</v>
+        <v>0.4882849109653233</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4543147208121827</v>
+        <v>0.6611675126903553</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4676681907250163</v>
+        <v>0.5617250673854447</v>
       </c>
       <c r="R11" t="n">
-        <v>427</v>
+        <v>266</v>
       </c>
       <c r="S11" t="n">
-        <v>385</v>
+        <v>546</v>
       </c>
       <c r="T11" t="n">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="U11" t="n">
-        <v>358</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12">
@@ -1404,52 +1404,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.508125</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.508125</v>
       </c>
       <c r="H12" t="n">
         <v>788</v>
       </c>
       <c r="I12" t="n">
-        <v>1004</v>
+        <v>731</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4960159362549801</v>
+        <v>0.5006839945280438</v>
       </c>
       <c r="K12" t="n">
-        <v>0.631979695431472</v>
+        <v>0.4644670050761421</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5558035714285714</v>
+        <v>0.4818959842001317</v>
       </c>
       <c r="M12" t="n">
         <v>812</v>
       </c>
       <c r="N12" t="n">
-        <v>596</v>
+        <v>869</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5134228187919463</v>
+        <v>0.5143843498273878</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3768472906403941</v>
+        <v>0.5504926108374384</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4346590909090909</v>
+        <v>0.5318262938726948</v>
       </c>
       <c r="R12" t="n">
-        <v>498</v>
+        <v>366</v>
       </c>
       <c r="S12" t="n">
-        <v>290</v>
+        <v>422</v>
       </c>
       <c r="T12" t="n">
-        <v>506</v>
+        <v>365</v>
       </c>
       <c r="U12" t="n">
-        <v>306</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13">
@@ -1471,52 +1471,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.496875</v>
+        <v>0.51125</v>
       </c>
       <c r="G13" t="n">
-        <v>0.496875</v>
+        <v>0.51125</v>
       </c>
       <c r="H13" t="n">
         <v>813</v>
       </c>
       <c r="I13" t="n">
-        <v>1066</v>
+        <v>921</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5037523452157598</v>
+        <v>0.5168295331161781</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6605166051660517</v>
+        <v>0.5854858548585485</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5715806279936136</v>
+        <v>0.5490196078431373</v>
       </c>
       <c r="M13" t="n">
         <v>787</v>
       </c>
       <c r="N13" t="n">
-        <v>534</v>
+        <v>679</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4831460674157304</v>
+        <v>0.5036818851251841</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3278271918678526</v>
+        <v>0.434561626429479</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3906131718395154</v>
+        <v>0.4665757162346521</v>
       </c>
       <c r="R13" t="n">
-        <v>537</v>
+        <v>476</v>
       </c>
       <c r="S13" t="n">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="T13" t="n">
-        <v>529</v>
+        <v>445</v>
       </c>
       <c r="U13" t="n">
-        <v>258</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
@@ -1538,46 +1538,46 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.485</v>
+        <v>0.49625</v>
       </c>
       <c r="G14" t="n">
-        <v>0.485</v>
+        <v>0.49625</v>
       </c>
       <c r="H14" t="n">
         <v>768</v>
       </c>
       <c r="I14" t="n">
-        <v>742</v>
+        <v>760</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4622641509433962</v>
+        <v>0.475</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4466145833333333</v>
+        <v>0.4700520833333333</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4543046357615895</v>
+        <v>0.4725130890052356</v>
       </c>
       <c r="M14" t="n">
         <v>832</v>
       </c>
       <c r="N14" t="n">
-        <v>858</v>
+        <v>840</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5046620046620046</v>
+        <v>0.5154761904761904</v>
       </c>
       <c r="P14" t="n">
         <v>0.5204326923076923</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5124260355029586</v>
+        <v>0.5179425837320574</v>
       </c>
       <c r="R14" t="n">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="S14" t="n">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="T14" t="n">
         <v>399</v>
@@ -1726,52 +1726,52 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="H2" t="n">
         <v>89</v>
       </c>
       <c r="I2" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4421768707482993</v>
+        <v>0.4603174603174603</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7303370786516854</v>
+        <v>0.651685393258427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5508474576271186</v>
+        <v>0.5395348837209303</v>
       </c>
       <c r="M2" t="n">
         <v>103</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2038834951456311</v>
+        <v>0.3398058252427185</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2837837837837838</v>
+        <v>0.4142011834319526</v>
       </c>
       <c r="R2" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="S2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="T2" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="U2" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -1793,52 +1793,52 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="H3" t="n">
         <v>93</v>
       </c>
       <c r="I3" t="n">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4744525547445255</v>
+        <v>0.4587155963302753</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6989247311827957</v>
+        <v>0.5376344086021505</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.495049504950495</v>
       </c>
       <c r="M3" t="n">
         <v>99</v>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4909090909090909</v>
+        <v>0.4819277108433735</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.404040404040404</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3506493506493506</v>
+        <v>0.4395604395604396</v>
       </c>
       <c r="R3" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="S3" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="T3" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="U3" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -1860,52 +1860,52 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H4" t="n">
         <v>110</v>
       </c>
       <c r="I4" t="n">
-        <v>149</v>
+        <v>120</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5503355704697986</v>
+        <v>0.55</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7454545454545455</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6332046332046332</v>
+        <v>0.5739130434782609</v>
       </c>
       <c r="M4" t="n">
         <v>82</v>
       </c>
       <c r="N4" t="n">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3488372093023256</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1829268292682927</v>
+        <v>0.3414634146341464</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.24</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="R4" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="S4" t="n">
+        <v>44</v>
+      </c>
+      <c r="T4" t="n">
+        <v>54</v>
+      </c>
+      <c r="U4" t="n">
         <v>28</v>
-      </c>
-      <c r="T4" t="n">
-        <v>67</v>
-      </c>
-      <c r="U4" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -1927,52 +1927,52 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.46875</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G5" t="n">
-        <v>0.46875</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H5" t="n">
         <v>97</v>
       </c>
       <c r="I5" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="J5" t="n">
-        <v>0.481203007518797</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6597938144329897</v>
+        <v>0.6804123711340206</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5565217391304348</v>
+        <v>0.584070796460177</v>
       </c>
       <c r="M5" t="n">
         <v>95</v>
       </c>
       <c r="N5" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4406779661016949</v>
+        <v>0.5079365079365079</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2736842105263158</v>
+        <v>0.3368421052631579</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.4050632911392405</v>
       </c>
       <c r="R5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="T5" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="U5" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -1994,52 +1994,52 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>103</v>
       </c>
       <c r="I6" t="n">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5170068027210885</v>
+        <v>0.5275590551181102</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.6504854368932039</v>
       </c>
       <c r="L6" t="n">
-        <v>0.608</v>
+        <v>0.5826086956521738</v>
       </c>
       <c r="M6" t="n">
         <v>89</v>
       </c>
       <c r="N6" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4</v>
+        <v>0.4461538461538462</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2022471910112359</v>
+        <v>0.3258426966292135</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2686567164179105</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="R6" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="T6" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="U6" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -2061,52 +2061,52 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H7" t="n">
         <v>94</v>
       </c>
       <c r="I7" t="n">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5106382978723404</v>
+        <v>0.4710743801652892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.6063829787234043</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6127659574468084</v>
+        <v>0.5302325581395348</v>
       </c>
       <c r="M7" t="n">
         <v>98</v>
       </c>
       <c r="N7" t="n">
-        <v>51</v>
+        <v>71</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5686274509803921</v>
+        <v>0.4788732394366197</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2959183673469388</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3892617449664429</v>
+        <v>0.4023668639053254</v>
       </c>
       <c r="R7" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T7" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="U7" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -2128,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4375</v>
       </c>
       <c r="H8" t="n">
         <v>92</v>
@@ -2140,13 +2140,13 @@
         <v>140</v>
       </c>
       <c r="J8" t="n">
-        <v>0.45</v>
+        <v>0.4428571428571428</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6847826086956522</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5431034482758621</v>
+        <v>0.5344827586206895</v>
       </c>
       <c r="M8" t="n">
         <v>100</v>
@@ -2155,25 +2155,25 @@
         <v>52</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4423076923076923</v>
+        <v>0.4230769230769231</v>
       </c>
       <c r="P8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3026315789473685</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="R8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -2195,52 +2195,52 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H9" t="n">
         <v>104</v>
       </c>
       <c r="I9" t="n">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5447761194029851</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7019230769230769</v>
+        <v>0.625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6134453781512604</v>
+        <v>0.5701754385964912</v>
       </c>
       <c r="M9" t="n">
         <v>88</v>
       </c>
       <c r="N9" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4655172413793103</v>
+        <v>0.4264705882352941</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3068181818181818</v>
+        <v>0.3295454545454545</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.3717948717948718</v>
       </c>
       <c r="R9" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="T9" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -2262,52 +2262,52 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.515625</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.515625</v>
+        <v>0.5</v>
       </c>
       <c r="H10" t="n">
         <v>106</v>
       </c>
       <c r="I10" t="n">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="J10" t="n">
-        <v>0.543046357615894</v>
+        <v>0.5431034482758621</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6381322957198443</v>
+        <v>0.5675675675675675</v>
       </c>
       <c r="M10" t="n">
         <v>86</v>
       </c>
       <c r="N10" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.4342105263157895</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1976744186046512</v>
+        <v>0.3837209302325582</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2677165354330709</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="R10" t="n">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="S10" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="T10" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="U10" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -2329,52 +2329,52 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H11" t="n">
         <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5228758169934641</v>
+        <v>0.5037593984962406</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="L11" t="n">
-        <v>0.642570281124498</v>
+        <v>0.5851528384279476</v>
       </c>
       <c r="M11" t="n">
         <v>96</v>
       </c>
       <c r="N11" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5897435897435898</v>
+        <v>0.5084745762711864</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2395833333333333</v>
+        <v>0.3125</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3407407407407407</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="R11" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="S11" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="T11" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -2396,52 +2396,52 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H12" t="n">
         <v>96</v>
       </c>
       <c r="I12" t="n">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4333333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.4814814814814815</v>
       </c>
       <c r="M12" t="n">
         <v>96</v>
       </c>
       <c r="N12" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="P12" t="n">
-        <v>0.25</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="R12" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="S12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="T12" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2463,52 +2463,52 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.453125</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.453125</v>
       </c>
       <c r="H13" t="n">
         <v>96</v>
       </c>
       <c r="I13" t="n">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4647887323943662</v>
+        <v>0.464</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6875</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5546218487394957</v>
+        <v>0.5248868778280542</v>
       </c>
       <c r="M13" t="n">
         <v>96</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4</v>
+        <v>0.4328358208955224</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2083333333333333</v>
+        <v>0.3020833333333333</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.273972602739726</v>
+        <v>0.3558282208588957</v>
       </c>
       <c r="R13" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="T13" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -2539,43 +2539,43 @@
         <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5354330708661418</v>
+        <v>0.5371900826446281</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6238532110091743</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="L14" t="n">
-        <v>0.576271186440678</v>
+        <v>0.5652173913043478</v>
       </c>
       <c r="M14" t="n">
         <v>83</v>
       </c>
       <c r="N14" t="n">
+        <v>71</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.3802816901408451</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.3253012048192771</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3506493506493507</v>
+      </c>
+      <c r="R14" t="n">
         <v>65</v>
       </c>
-      <c r="O14" t="n">
-        <v>0.3692307692307693</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.2891566265060241</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.3243243243243243</v>
-      </c>
-      <c r="R14" t="n">
-        <v>68</v>
-      </c>
       <c r="S14" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="T14" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2597,52 +2597,52 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H15" t="n">
         <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="J15" t="n">
-        <v>0.496551724137931</v>
+        <v>0.4745762711864407</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7659574468085106</v>
+        <v>0.5957446808510638</v>
       </c>
       <c r="L15" t="n">
-        <v>0.602510460251046</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="M15" t="n">
         <v>98</v>
       </c>
       <c r="N15" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.4864864864864865</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2551020408163265</v>
+        <v>0.3673469387755102</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.4186046511627907</v>
       </c>
       <c r="R15" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="S15" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="T15" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="U15" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2664,52 +2664,52 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H16" t="n">
         <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="J16" t="n">
-        <v>0.49375</v>
+        <v>0.481203007518797</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8777777777777778</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6320000000000001</v>
+        <v>0.5739910313901345</v>
       </c>
       <c r="M16" t="n">
         <v>102</v>
       </c>
       <c r="N16" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="O16" t="n">
-        <v>0.65625</v>
+        <v>0.559322033898305</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2058823529411765</v>
+        <v>0.3235294117647059</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3134328358208955</v>
+        <v>0.4099378881987578</v>
       </c>
       <c r="R16" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="S16" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="T16" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="U16" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17">
@@ -2731,52 +2731,52 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H17" t="n">
         <v>81</v>
       </c>
       <c r="I17" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4330708661417323</v>
+        <v>0.4311926605504587</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6790123456790124</v>
+        <v>0.5802469135802469</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5288461538461539</v>
+        <v>0.4947368421052632</v>
       </c>
       <c r="M17" t="n">
         <v>111</v>
       </c>
       <c r="N17" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>0.5903614457831325</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3513513513513514</v>
+        <v>0.4414414414414414</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4431818181818182</v>
+        <v>0.5051546391752577</v>
       </c>
       <c r="R17" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="S17" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T17" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="U17" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -2798,52 +2798,52 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
         <v>105</v>
       </c>
       <c r="I18" t="n">
-        <v>130</v>
+        <v>93</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5153846153846153</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="K18" t="n">
-        <v>0.638095238095238</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5702127659574467</v>
+        <v>0.5151515151515151</v>
       </c>
       <c r="M18" t="n">
         <v>87</v>
       </c>
       <c r="N18" t="n">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3870967741935484</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2758620689655172</v>
+        <v>0.5172413793103449</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3221476510067114</v>
+        <v>0.4838709677419355</v>
       </c>
       <c r="R18" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="S18" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="T18" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -2865,52 +2865,52 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H19" t="n">
         <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>141</v>
+        <v>112</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4964539007092199</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7216494845360825</v>
+        <v>0.5567010309278351</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5167464114832535</v>
       </c>
       <c r="M19" t="n">
         <v>95</v>
       </c>
       <c r="N19" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4625</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2526315789473684</v>
+        <v>0.3894736842105263</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3287671232876713</v>
+        <v>0.4228571428571429</v>
       </c>
       <c r="R19" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="S19" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="T19" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="U19" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -2932,52 +2932,52 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>83</v>
       </c>
       <c r="I20" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4525547445255474</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7951807228915663</v>
+        <v>0.7469879518072289</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5814977973568282</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="M20" t="n">
         <v>109</v>
       </c>
       <c r="N20" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6458333333333334</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2844036697247707</v>
+        <v>0.3119266055045872</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.3949044585987262</v>
+        <v>0.4146341463414634</v>
       </c>
       <c r="R20" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="S20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="T20" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21">
@@ -2999,52 +2999,52 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H21" t="n">
         <v>99</v>
       </c>
       <c r="I21" t="n">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5061728395061729</v>
+        <v>0.5147058823529411</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8282828282828283</v>
+        <v>0.7070707070707071</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6283524904214559</v>
+        <v>0.5957446808510637</v>
       </c>
       <c r="M21" t="n">
         <v>93</v>
       </c>
       <c r="N21" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1397849462365591</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2113821138211382</v>
+        <v>0.3624161073825504</v>
       </c>
       <c r="R21" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="S21" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="U21" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -3066,52 +3066,52 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.484375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>0.484375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H22" t="n">
         <v>81</v>
       </c>
       <c r="I22" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4383561643835616</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7901234567901234</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5638766519823789</v>
+        <v>0.5700934579439252</v>
       </c>
       <c r="M22" t="n">
         <v>111</v>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6304347826086957</v>
+        <v>0.6610169491525424</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2612612612612613</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3694267515923567</v>
+        <v>0.4588235294117647</v>
       </c>
       <c r="R22" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="S22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T22" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="U22" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -3142,43 +3142,43 @@
         <v>84</v>
       </c>
       <c r="I23" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4822695035460993</v>
+        <v>0.4778761061946903</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6044444444444445</v>
+        <v>0.5482233502538072</v>
       </c>
       <c r="M23" t="n">
         <v>108</v>
       </c>
       <c r="N23" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="O23" t="n">
-        <v>0.6862745098039216</v>
+        <v>0.620253164556962</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3240740740740741</v>
+        <v>0.4537037037037037</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.440251572327044</v>
+        <v>0.5240641711229946</v>
       </c>
       <c r="R23" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="T23" t="n">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="U23" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -3200,46 +3200,46 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.453125</v>
+        <v>0.484375</v>
       </c>
       <c r="G24" t="n">
-        <v>0.453125</v>
+        <v>0.484375</v>
       </c>
       <c r="H24" t="n">
         <v>88</v>
       </c>
       <c r="I24" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4330708661417323</v>
+        <v>0.4586466165413534</v>
       </c>
       <c r="K24" t="n">
-        <v>0.625</v>
+        <v>0.6931818181818182</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5116279069767442</v>
+        <v>0.5520361990950227</v>
       </c>
       <c r="M24" t="n">
         <v>104</v>
       </c>
       <c r="N24" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="O24" t="n">
-        <v>0.4923076923076923</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="P24" t="n">
         <v>0.3076923076923077</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3786982248520711</v>
+        <v>0.392638036809816</v>
       </c>
       <c r="R24" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="S24" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="T24" t="n">
         <v>72</v>
@@ -3267,52 +3267,52 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H25" t="n">
         <v>99</v>
       </c>
       <c r="I25" t="n">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5342465753424658</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="L25" t="n">
-        <v>0.636734693877551</v>
+        <v>0.5779816513761468</v>
       </c>
       <c r="M25" t="n">
         <v>93</v>
       </c>
       <c r="N25" t="n">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5434782608695652</v>
+        <v>0.5068493150684932</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2688172043010753</v>
+        <v>0.3978494623655914</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.3597122302158273</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="R25" t="n">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="S25" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="T25" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="U25" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
@@ -3334,52 +3334,52 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="H26" t="n">
         <v>87</v>
       </c>
       <c r="I26" t="n">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4539473684210527</v>
+        <v>0.4098360655737705</v>
       </c>
       <c r="K26" t="n">
-        <v>0.7931034482758621</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5774058577405857</v>
+        <v>0.4784688995215311</v>
       </c>
       <c r="M26" t="n">
         <v>105</v>
       </c>
       <c r="N26" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="O26" t="n">
-        <v>0.55</v>
+        <v>0.4714285714285714</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2095238095238095</v>
+        <v>0.3142857142857143</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.303448275862069</v>
+        <v>0.3771428571428572</v>
       </c>
       <c r="R26" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="S26" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="T26" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="U26" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -3401,52 +3401,52 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.546875</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.546875</v>
       </c>
       <c r="H27" t="n">
         <v>101</v>
       </c>
       <c r="I27" t="n">
-        <v>137</v>
+        <v>110</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5328467153284672</v>
+        <v>0.5636363636363636</v>
       </c>
       <c r="K27" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.6138613861386139</v>
       </c>
       <c r="L27" t="n">
-        <v>0.6134453781512605</v>
+        <v>0.5876777251184834</v>
       </c>
       <c r="M27" t="n">
         <v>91</v>
       </c>
       <c r="N27" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4909090909090909</v>
+        <v>0.524390243902439</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2967032967032967</v>
+        <v>0.4725274725274725</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.3698630136986301</v>
+        <v>0.4971098265895953</v>
       </c>
       <c r="R27" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="S27" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="T27" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="U27" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28">
@@ -3468,52 +3468,52 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="H28" t="n">
         <v>95</v>
       </c>
       <c r="I28" t="n">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="J28" t="n">
-        <v>0.503448275862069</v>
+        <v>0.5190839694656488</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7684210526315789</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6083333333333333</v>
+        <v>0.6017699115044248</v>
       </c>
       <c r="M28" t="n">
         <v>97</v>
       </c>
       <c r="N28" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.5573770491803278</v>
       </c>
       <c r="P28" t="n">
-        <v>0.2577319587628866</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3472222222222222</v>
+        <v>0.430379746835443</v>
       </c>
       <c r="R28" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="S28" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="T28" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="U28" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -3535,52 +3535,52 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.46875</v>
+        <v>0.484375</v>
       </c>
       <c r="G29" t="n">
-        <v>0.46875</v>
+        <v>0.484375</v>
       </c>
       <c r="H29" t="n">
         <v>90</v>
       </c>
       <c r="I29" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.4645669291338583</v>
       </c>
       <c r="K29" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5565217391304348</v>
+        <v>0.5437788018433179</v>
       </c>
       <c r="M29" t="n">
         <v>102</v>
       </c>
       <c r="N29" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5</v>
+        <v>0.5230769230769231</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2549019607843137</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3376623376623377</v>
+        <v>0.4071856287425149</v>
       </c>
       <c r="R29" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="S29" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="T29" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="U29" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
@@ -3602,52 +3602,52 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H30" t="n">
         <v>99</v>
       </c>
       <c r="I30" t="n">
-        <v>156</v>
+        <v>114</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4935897435897436</v>
+        <v>0.5350877192982456</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6161616161616161</v>
       </c>
       <c r="L30" t="n">
-        <v>0.6039215686274511</v>
+        <v>0.5727699530516432</v>
       </c>
       <c r="M30" t="n">
         <v>93</v>
       </c>
       <c r="N30" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="O30" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="P30" t="n">
-        <v>0.1505376344086022</v>
+        <v>0.4301075268817204</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.2170542635658914</v>
+        <v>0.4678362573099414</v>
       </c>
       <c r="R30" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="S30" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="T30" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="U30" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31">
@@ -3669,52 +3669,52 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.46875</v>
       </c>
       <c r="H31" t="n">
         <v>92</v>
       </c>
       <c r="I31" t="n">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4632352941176471</v>
       </c>
       <c r="K31" t="n">
-        <v>0.75</v>
+        <v>0.6847826086956522</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5847457627118644</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="M31" t="n">
         <v>100</v>
       </c>
       <c r="N31" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="P31" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="R31" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="S31" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="U31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -3736,52 +3736,52 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H32" t="n">
         <v>89</v>
       </c>
       <c r="I32" t="n">
-        <v>144</v>
+        <v>117</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4305555555555556</v>
+        <v>0.452991452991453</v>
       </c>
       <c r="K32" t="n">
-        <v>0.6966292134831461</v>
+        <v>0.5955056179775281</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5321888412017167</v>
+        <v>0.5145631067961165</v>
       </c>
       <c r="M32" t="n">
         <v>103</v>
       </c>
       <c r="N32" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="O32" t="n">
-        <v>0.4375</v>
+        <v>0.52</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2038834951456311</v>
+        <v>0.3786407766990291</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.2781456953642384</v>
+        <v>0.4382022471910112</v>
       </c>
       <c r="R32" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="S32" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="T32" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="U32" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -3803,52 +3803,52 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H33" t="n">
         <v>94</v>
       </c>
       <c r="I33" t="n">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4938271604938271</v>
+        <v>0.5285714285714286</v>
       </c>
       <c r="K33" t="n">
-        <v>0.851063829787234</v>
+        <v>0.7872340425531915</v>
       </c>
       <c r="L33" t="n">
-        <v>0.625</v>
+        <v>0.6324786324786325</v>
       </c>
       <c r="M33" t="n">
         <v>98</v>
       </c>
       <c r="N33" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="O33" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="P33" t="n">
-        <v>0.163265306122449</v>
+        <v>0.3265306122448979</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.25</v>
+        <v>0.4266666666666666</v>
       </c>
       <c r="R33" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T33" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="U33" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34">
@@ -3870,40 +3870,40 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="H34" t="n">
         <v>93</v>
       </c>
       <c r="I34" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4931506849315068</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="K34" t="n">
         <v>0.7741935483870968</v>
       </c>
       <c r="L34" t="n">
-        <v>0.602510460251046</v>
+        <v>0.6343612334801763</v>
       </c>
       <c r="M34" t="n">
         <v>99</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5434782608695652</v>
+        <v>0.6379310344827587</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2525252525252525</v>
+        <v>0.3737373737373738</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.3448275862068966</v>
+        <v>0.4713375796178345</v>
       </c>
       <c r="R34" t="n">
         <v>72</v>
@@ -3912,10 +3912,10 @@
         <v>21</v>
       </c>
       <c r="T34" t="n">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="U34" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
@@ -3937,52 +3937,52 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.546875</v>
       </c>
       <c r="G35" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.546875</v>
       </c>
       <c r="H35" t="n">
         <v>92</v>
       </c>
       <c r="I35" t="n">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4834437086092715</v>
+        <v>0.5210084033613446</v>
       </c>
       <c r="K35" t="n">
-        <v>0.7934782608695652</v>
+        <v>0.6739130434782609</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6008230452674898</v>
+        <v>0.5876777251184835</v>
       </c>
       <c r="M35" t="n">
         <v>100</v>
       </c>
       <c r="N35" t="n">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="O35" t="n">
-        <v>0.5365853658536586</v>
+        <v>0.589041095890411</v>
       </c>
       <c r="P35" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3120567375886525</v>
+        <v>0.4971098265895953</v>
       </c>
       <c r="R35" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="S35" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="U35" t="n">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
@@ -4004,52 +4004,52 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="H36" t="n">
         <v>84</v>
       </c>
       <c r="I36" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4477611940298508</v>
+        <v>0.4695652173913044</v>
       </c>
       <c r="K36" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L36" t="n">
-        <v>0.5504587155963303</v>
+        <v>0.542713567839196</v>
       </c>
       <c r="M36" t="n">
         <v>108</v>
       </c>
       <c r="N36" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="O36" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.6103896103896104</v>
       </c>
       <c r="P36" t="n">
-        <v>0.3148148148148148</v>
+        <v>0.4351851851851852</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4096385542168675</v>
+        <v>0.508108108108108</v>
       </c>
       <c r="R36" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="S36" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="T36" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="U36" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -4071,52 +4071,52 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H37" t="n">
         <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="K37" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5901639344262295</v>
+        <v>0.5702127659574469</v>
       </c>
       <c r="M37" t="n">
         <v>92</v>
       </c>
       <c r="N37" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3221476510067114</v>
       </c>
       <c r="R37" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="S37" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="T37" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -4138,52 +4138,52 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.46875</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G38" t="n">
-        <v>0.46875</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H38" t="n">
         <v>98</v>
       </c>
       <c r="I38" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4861111111111111</v>
+        <v>0.4761904761904762</v>
       </c>
       <c r="K38" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.5102040816326531</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5785123966942148</v>
+        <v>0.4926108374384236</v>
       </c>
       <c r="M38" t="n">
         <v>94</v>
       </c>
       <c r="N38" t="n">
+        <v>87</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.4148936170212766</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.430939226519337</v>
+      </c>
+      <c r="R38" t="n">
+        <v>50</v>
+      </c>
+      <c r="S38" t="n">
         <v>48</v>
       </c>
-      <c r="O38" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0.2127659574468085</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0.2816901408450704</v>
-      </c>
-      <c r="R38" t="n">
-        <v>70</v>
-      </c>
-      <c r="S38" t="n">
-        <v>28</v>
-      </c>
       <c r="T38" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="U38" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39">
@@ -4205,52 +4205,52 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="H39" t="n">
         <v>84</v>
       </c>
       <c r="I39" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4461538461538462</v>
+        <v>0.4621848739495799</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6904761904761905</v>
+        <v>0.6547619047619048</v>
       </c>
       <c r="L39" t="n">
-        <v>0.5420560747663552</v>
+        <v>0.541871921182266</v>
       </c>
       <c r="M39" t="n">
         <v>108</v>
       </c>
       <c r="N39" t="n">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="O39" t="n">
-        <v>0.5806451612903226</v>
+        <v>0.6027397260273972</v>
       </c>
       <c r="P39" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4235294117647058</v>
+        <v>0.4861878453038674</v>
       </c>
       <c r="R39" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="S39" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="T39" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="U39" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="40">
@@ -4272,52 +4272,52 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.484375</v>
+        <v>0.453125</v>
       </c>
       <c r="G40" t="n">
-        <v>0.484375</v>
+        <v>0.453125</v>
       </c>
       <c r="H40" t="n">
         <v>98</v>
       </c>
       <c r="I40" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4964539007092199</v>
+        <v>0.4724409448818898</v>
       </c>
       <c r="K40" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5857740585774059</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="M40" t="n">
         <v>94</v>
       </c>
       <c r="N40" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4509803921568628</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2446808510638298</v>
+        <v>0.2872340425531915</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3172413793103449</v>
+        <v>0.3396226415094341</v>
       </c>
       <c r="R40" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="S40" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T40" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -4339,52 +4339,52 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H41" t="n">
         <v>105</v>
       </c>
       <c r="I41" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5337837837837838</v>
+        <v>0.5251798561151079</v>
       </c>
       <c r="K41" t="n">
-        <v>0.7523809523809524</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6245059288537549</v>
+        <v>0.5983606557377048</v>
       </c>
       <c r="M41" t="n">
         <v>87</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="O41" t="n">
-        <v>0.4090909090909091</v>
+        <v>0.3962264150943396</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.2748091603053435</v>
+        <v>0.3</v>
       </c>
       <c r="R41" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="S41" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T41" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="U41" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
@@ -4415,43 +4415,43 @@
         <v>89</v>
       </c>
       <c r="I42" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4297520661157025</v>
+        <v>0.4247787610619469</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5842696629213483</v>
+        <v>0.5393258426966292</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4952380952380952</v>
+        <v>0.4752475247524752</v>
       </c>
       <c r="M42" t="n">
         <v>103</v>
       </c>
       <c r="N42" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O42" t="n">
-        <v>0.4788732394366197</v>
+        <v>0.4810126582278481</v>
       </c>
       <c r="P42" t="n">
-        <v>0.3300970873786408</v>
+        <v>0.3689320388349515</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.3908045977011494</v>
+        <v>0.4175824175824176</v>
       </c>
       <c r="R42" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="S42" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="T42" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="U42" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43">
@@ -4473,52 +4473,52 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4270833333333333</v>
       </c>
       <c r="H43" t="n">
         <v>98</v>
       </c>
       <c r="I43" t="n">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4491525423728814</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5408163265306123</v>
       </c>
       <c r="L43" t="n">
-        <v>0.5550660792951543</v>
+        <v>0.4907407407407408</v>
       </c>
       <c r="M43" t="n">
         <v>94</v>
       </c>
       <c r="N43" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="O43" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.3918918918918919</v>
       </c>
       <c r="P43" t="n">
-        <v>0.2978723404255319</v>
+        <v>0.3085106382978723</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.356687898089172</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="R43" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="S43" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="T43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U43" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
@@ -4540,52 +4540,52 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="H44" t="n">
         <v>111</v>
       </c>
       <c r="I44" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5704225352112676</v>
+        <v>0.6178861788617886</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.6846846846846847</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6403162055335968</v>
+        <v>0.6495726495726496</v>
       </c>
       <c r="M44" t="n">
         <v>81</v>
       </c>
       <c r="N44" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4</v>
+        <v>0.4927536231884058</v>
       </c>
       <c r="P44" t="n">
-        <v>0.2469135802469136</v>
+        <v>0.4197530864197531</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.3053435114503816</v>
+        <v>0.4533333333333333</v>
       </c>
       <c r="R44" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S44" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="T44" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="U44" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
@@ -4607,52 +4607,52 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.484375</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>0.484375</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H45" t="n">
         <v>95</v>
       </c>
       <c r="I45" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4859154929577465</v>
+        <v>0.5</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7263157894736842</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5822784810126583</v>
+        <v>0.5887445887445888</v>
       </c>
       <c r="M45" t="n">
         <v>97</v>
       </c>
       <c r="N45" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O45" t="n">
-        <v>0.48</v>
+        <v>0.5178571428571429</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2474226804123711</v>
+        <v>0.2989690721649484</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.3265306122448979</v>
+        <v>0.3790849673202615</v>
       </c>
       <c r="R45" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S45" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T45" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="U45" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46">
@@ -4674,52 +4674,52 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H46" t="n">
         <v>102</v>
       </c>
       <c r="I46" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="J46" t="n">
-        <v>0.50625</v>
+        <v>0.5153846153846153</v>
       </c>
       <c r="K46" t="n">
-        <v>0.7941176470588235</v>
+        <v>0.6568627450980392</v>
       </c>
       <c r="L46" t="n">
-        <v>0.6183206106870228</v>
+        <v>0.5775862068965517</v>
       </c>
       <c r="M46" t="n">
         <v>90</v>
       </c>
       <c r="N46" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="O46" t="n">
-        <v>0.34375</v>
+        <v>0.4354838709677419</v>
       </c>
       <c r="P46" t="n">
-        <v>0.1222222222222222</v>
+        <v>0.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.180327868852459</v>
+        <v>0.3552631578947368</v>
       </c>
       <c r="R46" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="S46" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="T46" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="U46" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -4741,52 +4741,52 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G47" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H47" t="n">
         <v>99</v>
       </c>
       <c r="I47" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5337837837837838</v>
+        <v>0.4915254237288136</v>
       </c>
       <c r="K47" t="n">
-        <v>0.797979797979798</v>
+        <v>0.5858585858585859</v>
       </c>
       <c r="L47" t="n">
-        <v>0.6396761133603239</v>
+        <v>0.5345622119815668</v>
       </c>
       <c r="M47" t="n">
         <v>93</v>
       </c>
       <c r="N47" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4459459459459459</v>
       </c>
       <c r="P47" t="n">
-        <v>0.2580645161290323</v>
+        <v>0.3548387096774194</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.3503649635036496</v>
+        <v>0.3952095808383234</v>
       </c>
       <c r="R47" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="T47" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="U47" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -4808,52 +4808,52 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.515625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G48" t="n">
-        <v>0.515625</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H48" t="n">
         <v>93</v>
       </c>
       <c r="I48" t="n">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5</v>
+        <v>0.4963503649635037</v>
       </c>
       <c r="K48" t="n">
-        <v>0.8602150537634409</v>
+        <v>0.7311827956989247</v>
       </c>
       <c r="L48" t="n">
-        <v>0.6324110671936758</v>
+        <v>0.5913043478260869</v>
       </c>
       <c r="M48" t="n">
         <v>99</v>
       </c>
       <c r="N48" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="O48" t="n">
-        <v>0.59375</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P48" t="n">
-        <v>0.1919191919191919</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.2900763358778626</v>
+        <v>0.3896103896103897</v>
       </c>
       <c r="R48" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="S48" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T48" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="U48" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49">
@@ -4875,52 +4875,52 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.484375</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.484375</v>
       </c>
       <c r="H49" t="n">
         <v>87</v>
       </c>
       <c r="I49" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4710144927536232</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7471264367816092</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5777777777777777</v>
+        <v>0.5352112676056338</v>
       </c>
       <c r="M49" t="n">
         <v>105</v>
       </c>
       <c r="N49" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="O49" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3047619047619048</v>
+        <v>0.3428571428571429</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4025157232704403</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="R49" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="S49" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="T49" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="U49" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
@@ -4942,52 +4942,52 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H50" t="n">
         <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4436619718309859</v>
+        <v>0.4553571428571428</v>
       </c>
       <c r="K50" t="n">
-        <v>0.7159090909090909</v>
+        <v>0.5795454545454546</v>
       </c>
       <c r="L50" t="n">
-        <v>0.5478260869565218</v>
+        <v>0.51</v>
       </c>
       <c r="M50" t="n">
         <v>104</v>
       </c>
       <c r="N50" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5</v>
+        <v>0.5375</v>
       </c>
       <c r="P50" t="n">
-        <v>0.2403846153846154</v>
+        <v>0.4134615384615384</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.4673913043478261</v>
       </c>
       <c r="R50" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="T50" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="U50" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
@@ -5018,43 +5018,43 @@
         <v>88</v>
       </c>
       <c r="I51" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4932432432432433</v>
+        <v>0.4925373134328358</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8295454545454546</v>
+        <v>0.75</v>
       </c>
       <c r="L51" t="n">
-        <v>0.6186440677966103</v>
+        <v>0.5945945945945946</v>
       </c>
       <c r="M51" t="n">
         <v>104</v>
       </c>
       <c r="N51" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="O51" t="n">
-        <v>0.6590909090909091</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="P51" t="n">
-        <v>0.2788461538461539</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.3918918918918919</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="R51" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="T51" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="U51" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="52">
@@ -5076,52 +5076,52 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H52" t="n">
         <v>93</v>
       </c>
       <c r="I52" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="J52" t="n">
-        <v>0.4671052631578947</v>
+        <v>0.5035971223021583</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7634408602150538</v>
+        <v>0.7526881720430108</v>
       </c>
       <c r="L52" t="n">
-        <v>0.5795918367346939</v>
+        <v>0.603448275862069</v>
       </c>
       <c r="M52" t="n">
         <v>99</v>
       </c>
       <c r="N52" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O52" t="n">
-        <v>0.45</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="P52" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.2589928057553957</v>
+        <v>0.3947368421052631</v>
       </c>
       <c r="R52" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S52" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T52" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="U52" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53">
@@ -5143,52 +5143,52 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H53" t="n">
         <v>95</v>
       </c>
       <c r="I53" t="n">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="J53" t="n">
-        <v>0.4965034965034965</v>
+        <v>0.46875</v>
       </c>
       <c r="K53" t="n">
-        <v>0.7473684210526316</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5966386554621849</v>
+        <v>0.5381165919282511</v>
       </c>
       <c r="M53" t="n">
         <v>97</v>
       </c>
       <c r="N53" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="O53" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.453125</v>
       </c>
       <c r="P53" t="n">
-        <v>0.2577319587628866</v>
+        <v>0.2989690721649484</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3424657534246575</v>
+        <v>0.3602484472049689</v>
       </c>
       <c r="R53" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S53" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="T53" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="U53" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54">
@@ -5210,52 +5210,52 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.46875</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.46875</v>
       </c>
       <c r="H54" t="n">
         <v>99</v>
       </c>
       <c r="I54" t="n">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5244755244755245</v>
+        <v>0.488</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.6161616161616161</v>
       </c>
       <c r="L54" t="n">
-        <v>0.6198347107438017</v>
+        <v>0.5446428571428571</v>
       </c>
       <c r="M54" t="n">
         <v>93</v>
       </c>
       <c r="N54" t="n">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="O54" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.4328358208955224</v>
       </c>
       <c r="P54" t="n">
-        <v>0.2688172043010753</v>
+        <v>0.3118279569892473</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.352112676056338</v>
+        <v>0.3625</v>
       </c>
       <c r="R54" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="S54" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="T54" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="U54" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="55">
@@ -5277,52 +5277,52 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G55" t="n">
-        <v>0.453125</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="H55" t="n">
         <v>90</v>
       </c>
       <c r="I55" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.4596774193548387</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7222222222222222</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.5327102803738317</v>
       </c>
       <c r="M55" t="n">
         <v>102</v>
       </c>
       <c r="N55" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="O55" t="n">
-        <v>0.4680851063829787</v>
+        <v>0.5147058823529411</v>
       </c>
       <c r="P55" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.2953020134228188</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="R55" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="U55" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
@@ -5344,52 +5344,52 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.484375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G56" t="n">
-        <v>0.484375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H56" t="n">
         <v>94</v>
       </c>
       <c r="I56" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4836601307189543</v>
+        <v>0.5075757575757576</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.7127659574468085</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5991902834008098</v>
+        <v>0.5929203539823009</v>
       </c>
       <c r="M56" t="n">
         <v>98</v>
       </c>
       <c r="N56" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="O56" t="n">
-        <v>0.4871794871794872</v>
+        <v>0.55</v>
       </c>
       <c r="P56" t="n">
-        <v>0.1938775510204082</v>
+        <v>0.336734693877551</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.2773722627737226</v>
+        <v>0.4177215189873417</v>
       </c>
       <c r="R56" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="T56" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="U56" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="57">
@@ -5411,52 +5411,52 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H57" t="n">
         <v>95</v>
       </c>
       <c r="I57" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="K57" t="n">
-        <v>0.7263157894736842</v>
+        <v>0.5894736842105263</v>
       </c>
       <c r="L57" t="n">
-        <v>0.592274678111588</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="M57" t="n">
         <v>97</v>
       </c>
       <c r="N57" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="O57" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="P57" t="n">
-        <v>0.288659793814433</v>
+        <v>0.3402061855670103</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.3708609271523178</v>
+        <v>0.3905325443786982</v>
       </c>
       <c r="R57" t="n">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="S57" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="T57" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="U57" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58">
@@ -5478,40 +5478,40 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4427083333333333</v>
+        <v>0.5</v>
       </c>
       <c r="H58" t="n">
         <v>91</v>
       </c>
       <c r="I58" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="J58" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.481203007518797</v>
       </c>
       <c r="K58" t="n">
         <v>0.7032967032967034</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5446808510638298</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M58" t="n">
         <v>101</v>
       </c>
       <c r="N58" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="O58" t="n">
-        <v>0.4375</v>
+        <v>0.5423728813559322</v>
       </c>
       <c r="P58" t="n">
-        <v>0.2079207920792079</v>
+        <v>0.3168316831683168</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.2818791946308725</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="R58" t="n">
         <v>64</v>
@@ -5520,10 +5520,10 @@
         <v>27</v>
       </c>
       <c r="T58" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="U58" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59">
@@ -5545,52 +5545,52 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="H59" t="n">
         <v>88</v>
       </c>
       <c r="I59" t="n">
-        <v>148</v>
+        <v>119</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4459459459459459</v>
+        <v>0.453781512605042</v>
       </c>
       <c r="K59" t="n">
-        <v>0.75</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="L59" t="n">
-        <v>0.559322033898305</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="M59" t="n">
         <v>104</v>
       </c>
       <c r="N59" t="n">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="O59" t="n">
-        <v>0.5</v>
+        <v>0.5342465753424658</v>
       </c>
       <c r="P59" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.375</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.2972972972972973</v>
+        <v>0.440677966101695</v>
       </c>
       <c r="R59" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="S59" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="T59" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="U59" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="60">
@@ -5612,52 +5612,52 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.546875</v>
+        <v>0.5</v>
       </c>
       <c r="G60" t="n">
-        <v>0.546875</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="n">
         <v>111</v>
       </c>
       <c r="I60" t="n">
-        <v>150</v>
+        <v>123</v>
       </c>
       <c r="J60" t="n">
-        <v>0.58</v>
+        <v>0.5609756097560976</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="L60" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5897435897435899</v>
       </c>
       <c r="M60" t="n">
         <v>81</v>
       </c>
       <c r="N60" t="n">
+        <v>69</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="R60" t="n">
+        <v>69</v>
+      </c>
+      <c r="S60" t="n">
         <v>42</v>
       </c>
-      <c r="O60" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="P60" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.2926829268292683</v>
-      </c>
-      <c r="R60" t="n">
-        <v>87</v>
-      </c>
-      <c r="S60" t="n">
-        <v>24</v>
-      </c>
       <c r="T60" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="U60" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
@@ -5679,52 +5679,52 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H61" t="n">
         <v>98</v>
       </c>
       <c r="I61" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5378787878787878</v>
+        <v>0.5254237288135594</v>
       </c>
       <c r="K61" t="n">
-        <v>0.7244897959183674</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="L61" t="n">
-        <v>0.6173913043478261</v>
+        <v>0.5740740740740742</v>
       </c>
       <c r="M61" t="n">
         <v>94</v>
       </c>
       <c r="N61" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="O61" t="n">
-        <v>0.55</v>
+        <v>0.5135135135135135</v>
       </c>
       <c r="P61" t="n">
-        <v>0.351063829787234</v>
+        <v>0.4042553191489361</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4523809523809524</v>
       </c>
       <c r="R61" t="n">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="S61" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="T61" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="U61" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -5746,52 +5746,52 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.515625</v>
+        <v>0.453125</v>
       </c>
       <c r="G62" t="n">
-        <v>0.515625</v>
+        <v>0.453125</v>
       </c>
       <c r="H62" t="n">
         <v>106</v>
       </c>
       <c r="I62" t="n">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="J62" t="n">
-        <v>0.543046357615894</v>
+        <v>0.5041322314049587</v>
       </c>
       <c r="K62" t="n">
-        <v>0.7735849056603774</v>
+        <v>0.5754716981132075</v>
       </c>
       <c r="L62" t="n">
-        <v>0.6381322957198443</v>
+        <v>0.5374449339207049</v>
       </c>
       <c r="M62" t="n">
         <v>86</v>
       </c>
       <c r="N62" t="n">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="O62" t="n">
-        <v>0.4146341463414634</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="P62" t="n">
-        <v>0.1976744186046512</v>
+        <v>0.3023255813953488</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.2677165354330709</v>
+        <v>0.3312101910828025</v>
       </c>
       <c r="R62" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="S62" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="T62" t="n">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="U62" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
@@ -5813,52 +5813,52 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H63" t="n">
         <v>88</v>
       </c>
       <c r="I63" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4222222222222222</v>
+        <v>0.4344262295081967</v>
       </c>
       <c r="K63" t="n">
-        <v>0.6477272727272727</v>
+        <v>0.6022727272727273</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5112107623318386</v>
+        <v>0.5047619047619047</v>
       </c>
       <c r="M63" t="n">
         <v>104</v>
       </c>
       <c r="N63" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="O63" t="n">
-        <v>0.456140350877193</v>
+        <v>0.5</v>
       </c>
       <c r="P63" t="n">
-        <v>0.25</v>
+        <v>0.3365384615384616</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.3229813664596273</v>
+        <v>0.4022988505747127</v>
       </c>
       <c r="R63" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S63" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T63" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="U63" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="64">
@@ -5880,52 +5880,52 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H64" t="n">
         <v>91</v>
       </c>
       <c r="I64" t="n">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4758620689655172</v>
+        <v>0.4848484848484849</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7582417582417582</v>
+        <v>0.7032967032967034</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5847457627118644</v>
+        <v>0.5739910313901345</v>
       </c>
       <c r="M64" t="n">
         <v>101</v>
       </c>
       <c r="N64" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="O64" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.55</v>
       </c>
       <c r="P64" t="n">
-        <v>0.2475247524752475</v>
+        <v>0.3267326732673267</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.3378378378378378</v>
+        <v>0.4099378881987578</v>
       </c>
       <c r="R64" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="S64" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="T64" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="U64" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="65">
@@ -5947,52 +5947,52 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H65" t="n">
         <v>95</v>
       </c>
       <c r="I65" t="n">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4927536231884058</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="K65" t="n">
-        <v>0.7157894736842105</v>
+        <v>0.6210526315789474</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5836909871244635</v>
+        <v>0.5339366515837105</v>
       </c>
       <c r="M65" t="n">
         <v>97</v>
       </c>
       <c r="N65" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="O65" t="n">
-        <v>0.5</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="P65" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.3092783505154639</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.3576158940397351</v>
+        <v>0.3680981595092024</v>
       </c>
       <c r="R65" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="S65" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="T65" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="U65" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -6014,52 +6014,52 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.453125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G66" t="n">
-        <v>0.453125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H66" t="n">
         <v>83</v>
       </c>
       <c r="I66" t="n">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="J66" t="n">
-        <v>0.417910447761194</v>
+        <v>0.423728813559322</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6746987951807228</v>
+        <v>0.6024096385542169</v>
       </c>
       <c r="L66" t="n">
-        <v>0.5161290322580645</v>
+        <v>0.4975124378109452</v>
       </c>
       <c r="M66" t="n">
         <v>109</v>
       </c>
       <c r="N66" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="O66" t="n">
-        <v>0.5344827586206896</v>
+        <v>0.5540540540540541</v>
       </c>
       <c r="P66" t="n">
-        <v>0.2844036697247707</v>
+        <v>0.3761467889908257</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.3712574850299401</v>
+        <v>0.4480874316939891</v>
       </c>
       <c r="R66" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="S66" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="T66" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="U66" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -6081,52 +6081,52 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H67" t="n">
         <v>92</v>
       </c>
       <c r="I67" t="n">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4697986577181208</v>
+        <v>0.4552845528455284</v>
       </c>
       <c r="K67" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5809128630705395</v>
+        <v>0.5209302325581395</v>
       </c>
       <c r="M67" t="n">
         <v>100</v>
       </c>
       <c r="N67" t="n">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="O67" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="P67" t="n">
-        <v>0.21</v>
+        <v>0.33</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.2937062937062937</v>
+        <v>0.3905325443786983</v>
       </c>
       <c r="R67" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="S67" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="T67" t="n">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="U67" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
     </row>
     <row r="68">
@@ -6148,52 +6148,52 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="G68" t="n">
-        <v>0.46875</v>
+        <v>0.5</v>
       </c>
       <c r="H68" t="n">
         <v>98</v>
       </c>
       <c r="I68" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4866666666666667</v>
+        <v>0.5078125</v>
       </c>
       <c r="K68" t="n">
-        <v>0.7448979591836735</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="L68" t="n">
-        <v>0.588709677419355</v>
+        <v>0.5752212389380531</v>
       </c>
       <c r="M68" t="n">
         <v>94</v>
       </c>
       <c r="N68" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="O68" t="n">
-        <v>0.4047619047619048</v>
+        <v>0.484375</v>
       </c>
       <c r="P68" t="n">
-        <v>0.1808510638297872</v>
+        <v>0.3297872340425532</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.25</v>
+        <v>0.3924050632911392</v>
       </c>
       <c r="R68" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="T68" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="U68" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="69">
@@ -6215,52 +6215,52 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="H69" t="n">
         <v>94</v>
       </c>
       <c r="I69" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4758064516129032</v>
+        <v>0.4818181818181818</v>
       </c>
       <c r="K69" t="n">
-        <v>0.6276595744680851</v>
+        <v>0.5638297872340425</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5412844036697247</v>
+        <v>0.5196078431372548</v>
       </c>
       <c r="M69" t="n">
         <v>98</v>
       </c>
       <c r="N69" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="O69" t="n">
-        <v>0.4852941176470588</v>
+        <v>0.5</v>
       </c>
       <c r="P69" t="n">
-        <v>0.336734693877551</v>
+        <v>0.4183673469387755</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.3975903614457831</v>
+        <v>0.4555555555555555</v>
       </c>
       <c r="R69" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="S69" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="T69" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="U69" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
@@ -6282,52 +6282,52 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G70" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="H70" t="n">
         <v>83</v>
       </c>
       <c r="I70" t="n">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4609375</v>
       </c>
       <c r="K70" t="n">
-        <v>0.7831325301204819</v>
+        <v>0.7108433734939759</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5579399141630902</v>
+        <v>0.5592417061611374</v>
       </c>
       <c r="M70" t="n">
         <v>109</v>
       </c>
       <c r="N70" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="O70" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="P70" t="n">
-        <v>0.2201834862385321</v>
+        <v>0.3669724770642202</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.3178807947019867</v>
+        <v>0.4624277456647399</v>
       </c>
       <c r="R70" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="S70" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T70" t="n">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="U70" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -6349,52 +6349,52 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="H71" t="n">
         <v>93</v>
       </c>
       <c r="I71" t="n">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4842767295597484</v>
+        <v>0.4769230769230769</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8279569892473119</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L71" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.5560538116591929</v>
       </c>
       <c r="M71" t="n">
         <v>99</v>
       </c>
       <c r="N71" t="n">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="O71" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.5</v>
       </c>
       <c r="P71" t="n">
-        <v>0.1717171717171717</v>
+        <v>0.3131313131313131</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.2575757575757576</v>
+        <v>0.3850931677018634</v>
       </c>
       <c r="R71" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="S71" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="T71" t="n">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="U71" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="72">
@@ -6416,52 +6416,52 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G72" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H72" t="n">
         <v>101</v>
       </c>
       <c r="I72" t="n">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5277777777777778</v>
+        <v>0.5378151260504201</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7524752475247525</v>
+        <v>0.6336633663366337</v>
       </c>
       <c r="L72" t="n">
-        <v>0.620408163265306</v>
+        <v>0.5818181818181819</v>
       </c>
       <c r="M72" t="n">
         <v>91</v>
       </c>
       <c r="N72" t="n">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="O72" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4931506849315068</v>
       </c>
       <c r="P72" t="n">
-        <v>0.2527472527472527</v>
+        <v>0.3956043956043956</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.3309352517985611</v>
+        <v>0.4390243902439024</v>
       </c>
       <c r="R72" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="T72" t="n">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="U72" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="73">
@@ -6492,43 +6492,43 @@
         <v>105</v>
       </c>
       <c r="I73" t="n">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="J73" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.5185185185185185</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5877551020408163</v>
+        <v>0.5258215962441314</v>
       </c>
       <c r="M73" t="n">
         <v>87</v>
       </c>
       <c r="N73" t="n">
+        <v>84</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.4022988505747127</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.4093567251461988</v>
+      </c>
+      <c r="R73" t="n">
+        <v>56</v>
+      </c>
+      <c r="S73" t="n">
+        <v>49</v>
+      </c>
+      <c r="T73" t="n">
         <v>52</v>
       </c>
-      <c r="O73" t="n">
-        <v>0.3653846153846154</v>
-      </c>
-      <c r="P73" t="n">
-        <v>0.2183908045977012</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>0.2733812949640288</v>
-      </c>
-      <c r="R73" t="n">
-        <v>72</v>
-      </c>
-      <c r="S73" t="n">
-        <v>33</v>
-      </c>
-      <c r="T73" t="n">
-        <v>68</v>
-      </c>
       <c r="U73" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="74">
@@ -6550,52 +6550,52 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="H74" t="n">
         <v>84</v>
       </c>
       <c r="I74" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="J74" t="n">
-        <v>0.4370370370370371</v>
+        <v>0.4193548387096774</v>
       </c>
       <c r="K74" t="n">
-        <v>0.7023809523809523</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5388127853881278</v>
+        <v>0.5</v>
       </c>
       <c r="M74" t="n">
         <v>108</v>
       </c>
       <c r="N74" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5614035087719298</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="P74" t="n">
-        <v>0.2962962962962963</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.3878787878787879</v>
+        <v>0.409090909090909</v>
       </c>
       <c r="R74" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="T74" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="U74" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="75">
@@ -6617,52 +6617,52 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.453125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G75" t="n">
-        <v>0.453125</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H75" t="n">
         <v>99</v>
       </c>
       <c r="I75" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6767676767676768</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="L75" t="n">
-        <v>0.5606694560669456</v>
+        <v>0.4975124378109453</v>
       </c>
       <c r="M75" t="n">
         <v>93</v>
       </c>
       <c r="N75" t="n">
+        <v>90</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.4555555555555555</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.4408602150537634</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.4480874316939891</v>
+      </c>
+      <c r="R75" t="n">
+        <v>50</v>
+      </c>
+      <c r="S75" t="n">
+        <v>49</v>
+      </c>
+      <c r="T75" t="n">
         <v>52</v>
       </c>
-      <c r="O75" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0.2150537634408602</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>0.2758620689655172</v>
-      </c>
-      <c r="R75" t="n">
-        <v>67</v>
-      </c>
-      <c r="S75" t="n">
-        <v>32</v>
-      </c>
-      <c r="T75" t="n">
-        <v>73</v>
-      </c>
       <c r="U75" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76">
@@ -6684,52 +6684,52 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.546875</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G76" t="n">
-        <v>0.546875</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H76" t="n">
         <v>99</v>
       </c>
       <c r="I76" t="n">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="L76" t="n">
-        <v>0.6419753086419753</v>
+        <v>0.6276150627615062</v>
       </c>
       <c r="M76" t="n">
         <v>93</v>
       </c>
       <c r="N76" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5625</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="P76" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.3010752688172043</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.3829787234042554</v>
+        <v>0.3862068965517241</v>
       </c>
       <c r="R76" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="S76" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="T76" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U76" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
@@ -6751,52 +6751,52 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H77" t="n">
         <v>97</v>
       </c>
       <c r="I77" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="J77" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.5</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7628865979381443</v>
+        <v>0.6185567010309279</v>
       </c>
       <c r="L77" t="n">
-        <v>0.6244725738396625</v>
+        <v>0.5529953917050692</v>
       </c>
       <c r="M77" t="n">
         <v>95</v>
       </c>
       <c r="N77" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="O77" t="n">
-        <v>0.5576923076923077</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="P77" t="n">
-        <v>0.3052631578947368</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.3945578231292517</v>
+        <v>0.4191616766467066</v>
       </c>
       <c r="R77" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="S77" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="T77" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="U77" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78">
@@ -6818,52 +6818,52 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.609375</v>
       </c>
       <c r="G78" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.609375</v>
       </c>
       <c r="H78" t="n">
         <v>111</v>
       </c>
       <c r="I78" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.640625</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8108108108108109</v>
+        <v>0.7387387387387387</v>
       </c>
       <c r="L78" t="n">
-        <v>0.7031250000000001</v>
+        <v>0.6861924686192469</v>
       </c>
       <c r="M78" t="n">
         <v>81</v>
       </c>
       <c r="N78" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="O78" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.546875</v>
       </c>
       <c r="P78" t="n">
-        <v>0.3209876543209876</v>
+        <v>0.4320987654320987</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.40625</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="R78" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="S78" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="T78" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="U78" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79">
@@ -6885,40 +6885,40 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="H79" t="n">
         <v>94</v>
       </c>
       <c r="I79" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J79" t="n">
-        <v>0.5234375</v>
+        <v>0.5153846153846153</v>
       </c>
       <c r="K79" t="n">
         <v>0.7127659574468085</v>
       </c>
       <c r="L79" t="n">
-        <v>0.6036036036036035</v>
+        <v>0.5982142857142856</v>
       </c>
       <c r="M79" t="n">
         <v>98</v>
       </c>
       <c r="N79" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O79" t="n">
-        <v>0.578125</v>
+        <v>0.5645161290322581</v>
       </c>
       <c r="P79" t="n">
-        <v>0.3775510204081632</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4567901234567902</v>
+        <v>0.4375000000000001</v>
       </c>
       <c r="R79" t="n">
         <v>67</v>
@@ -6927,10 +6927,10 @@
         <v>27</v>
       </c>
       <c r="T79" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U79" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="80">
@@ -6952,52 +6952,52 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.53125</v>
       </c>
       <c r="G80" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.53125</v>
       </c>
       <c r="H80" t="n">
         <v>87</v>
       </c>
       <c r="I80" t="n">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="J80" t="n">
-        <v>0.4405594405594406</v>
+        <v>0.4867256637168141</v>
       </c>
       <c r="K80" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.632183908045977</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5478260869565218</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="M80" t="n">
         <v>105</v>
       </c>
       <c r="N80" t="n">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="O80" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.5949367088607594</v>
       </c>
       <c r="P80" t="n">
-        <v>0.2380952380952381</v>
+        <v>0.4476190476190476</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.3246753246753247</v>
+        <v>0.5108695652173914</v>
       </c>
       <c r="R80" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="S80" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="T80" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="U80" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
@@ -7019,52 +7019,52 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G81" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="H81" t="n">
         <v>92</v>
       </c>
       <c r="I81" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="J81" t="n">
-        <v>0.4827586206896552</v>
+        <v>0.4921875</v>
       </c>
       <c r="K81" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.6847826086956522</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5907172995780591</v>
+        <v>0.5727272727272728</v>
       </c>
       <c r="M81" t="n">
         <v>100</v>
       </c>
       <c r="N81" t="n">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="O81" t="n">
-        <v>0.5319148936170213</v>
+        <v>0.546875</v>
       </c>
       <c r="P81" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.3401360544217687</v>
+        <v>0.4268292682926829</v>
       </c>
       <c r="R81" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="S81" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="T81" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U81" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82">
@@ -7086,52 +7086,52 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.390625</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G82" t="n">
-        <v>0.390625</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H82" t="n">
         <v>84</v>
       </c>
       <c r="I82" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="J82" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.415929203539823</v>
       </c>
       <c r="K82" t="n">
-        <v>0.6071428571428571</v>
+        <v>0.5595238095238095</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4657534246575342</v>
+        <v>0.4771573604060914</v>
       </c>
       <c r="M82" t="n">
         <v>108</v>
       </c>
       <c r="N82" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="O82" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.5316455696202531</v>
       </c>
       <c r="P82" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.2909090909090909</v>
+        <v>0.4491978609625669</v>
       </c>
       <c r="R82" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="S82" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T82" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="U82" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
@@ -7153,52 +7153,52 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.484375</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G83" t="n">
-        <v>0.484375</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H83" t="n">
         <v>94</v>
       </c>
       <c r="I83" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4796747967479675</v>
+        <v>0.4594594594594595</v>
       </c>
       <c r="K83" t="n">
-        <v>0.6276595744680851</v>
+        <v>0.5425531914893617</v>
       </c>
       <c r="L83" t="n">
-        <v>0.5437788018433179</v>
+        <v>0.4975609756097561</v>
       </c>
       <c r="M83" t="n">
         <v>98</v>
       </c>
       <c r="N83" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O83" t="n">
-        <v>0.4927536231884058</v>
+        <v>0.4691358024691358</v>
       </c>
       <c r="P83" t="n">
-        <v>0.3469387755102041</v>
+        <v>0.3877551020408163</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.407185628742515</v>
+        <v>0.4245810055865922</v>
       </c>
       <c r="R83" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="S83" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="T83" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="U83" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84">
@@ -7220,52 +7220,52 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5885416666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5885416666666666</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="H84" t="n">
         <v>103</v>
       </c>
       <c r="I84" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="J84" t="n">
-        <v>0.5869565217391305</v>
+        <v>0.5590551181102362</v>
       </c>
       <c r="K84" t="n">
-        <v>0.7864077669902912</v>
+        <v>0.6893203883495146</v>
       </c>
       <c r="L84" t="n">
-        <v>0.6721991701244814</v>
+        <v>0.6173913043478261</v>
       </c>
       <c r="M84" t="n">
         <v>89</v>
       </c>
       <c r="N84" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.5076923076923077</v>
       </c>
       <c r="P84" t="n">
-        <v>0.3595505617977528</v>
+        <v>0.3707865168539326</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4475524475524476</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="R84" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="S84" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="T84" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="U84" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="85">
@@ -7296,43 +7296,43 @@
         <v>107</v>
       </c>
       <c r="I85" t="n">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="J85" t="n">
-        <v>0.528169014084507</v>
+        <v>0.5294117647058824</v>
       </c>
       <c r="K85" t="n">
-        <v>0.7009345794392523</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="L85" t="n">
-        <v>0.6024096385542168</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="M85" t="n">
         <v>85</v>
       </c>
       <c r="N85" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="O85" t="n">
-        <v>0.36</v>
+        <v>0.375</v>
       </c>
       <c r="P85" t="n">
-        <v>0.2117647058823529</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2978723404255319</v>
       </c>
       <c r="R85" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S85" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="T85" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="U85" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
@@ -7354,52 +7354,52 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.484375</v>
+        <v>0.453125</v>
       </c>
       <c r="G86" t="n">
-        <v>0.484375</v>
+        <v>0.453125</v>
       </c>
       <c r="H86" t="n">
         <v>101</v>
       </c>
       <c r="I86" t="n">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="J86" t="n">
-        <v>0.5069444444444444</v>
+        <v>0.4846153846153846</v>
       </c>
       <c r="K86" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.6237623762376238</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5959183673469387</v>
+        <v>0.5454545454545455</v>
       </c>
       <c r="M86" t="n">
         <v>91</v>
       </c>
       <c r="N86" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="O86" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="P86" t="n">
-        <v>0.2197802197802198</v>
+        <v>0.2637362637362637</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="R86" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="S86" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="T86" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="U86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
@@ -7421,46 +7421,46 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G87" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H87" t="n">
         <v>97</v>
       </c>
       <c r="I87" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5433070866141733</v>
+        <v>0.4821428571428572</v>
       </c>
       <c r="K87" t="n">
-        <v>0.711340206185567</v>
+        <v>0.5567010309278351</v>
       </c>
       <c r="L87" t="n">
-        <v>0.6160714285714286</v>
+        <v>0.5167464114832535</v>
       </c>
       <c r="M87" t="n">
         <v>95</v>
       </c>
       <c r="N87" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="O87" t="n">
-        <v>0.5692307692307692</v>
+        <v>0.4625</v>
       </c>
       <c r="P87" t="n">
         <v>0.3894736842105263</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.4625</v>
+        <v>0.4228571428571429</v>
       </c>
       <c r="R87" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="S87" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="T87" t="n">
         <v>58</v>
@@ -7488,52 +7488,52 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="G88" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.53125</v>
       </c>
       <c r="H88" t="n">
         <v>101</v>
       </c>
       <c r="I88" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5503875968992248</v>
+        <v>0.5504587155963303</v>
       </c>
       <c r="K88" t="n">
-        <v>0.7029702970297029</v>
+        <v>0.594059405940594</v>
       </c>
       <c r="L88" t="n">
-        <v>0.6173913043478262</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="M88" t="n">
         <v>91</v>
       </c>
       <c r="N88" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="O88" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.5060240963855421</v>
       </c>
       <c r="P88" t="n">
-        <v>0.3626373626373626</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.4827586206896552</v>
       </c>
       <c r="R88" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S88" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="T88" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="U88" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="89">
@@ -7564,43 +7564,43 @@
         <v>103</v>
       </c>
       <c r="I89" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J89" t="n">
-        <v>0.5508474576271186</v>
+        <v>0.55</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6310679611650486</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5882352941176471</v>
+        <v>0.5919282511210763</v>
       </c>
       <c r="M89" t="n">
         <v>89</v>
       </c>
       <c r="N89" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="O89" t="n">
-        <v>0.4864864864864865</v>
+        <v>0.4861111111111111</v>
       </c>
       <c r="P89" t="n">
-        <v>0.4044943820224719</v>
+        <v>0.3932584269662922</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4417177914110429</v>
+        <v>0.4347826086956522</v>
       </c>
       <c r="R89" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S89" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="T89" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="U89" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
@@ -7622,52 +7622,52 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H90" t="n">
         <v>100</v>
       </c>
       <c r="I90" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4881889763779528</v>
       </c>
       <c r="K90" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5583333333333333</v>
+        <v>0.5462555066079294</v>
       </c>
       <c r="M90" t="n">
         <v>92</v>
       </c>
       <c r="N90" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="O90" t="n">
-        <v>0.3653846153846154</v>
+        <v>0.4153846153846154</v>
       </c>
       <c r="P90" t="n">
-        <v>0.2065217391304348</v>
+        <v>0.2934782608695652</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.2638888888888889</v>
+        <v>0.3439490445859873</v>
       </c>
       <c r="R90" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="S90" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="T90" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="U90" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
@@ -7689,46 +7689,46 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5520833333333334</v>
       </c>
       <c r="H91" t="n">
         <v>105</v>
       </c>
       <c r="I91" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="J91" t="n">
-        <v>0.5968992248062015</v>
+        <v>0.5772357723577236</v>
       </c>
       <c r="K91" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.6761904761904762</v>
       </c>
       <c r="L91" t="n">
-        <v>0.6581196581196581</v>
+        <v>0.6228070175438597</v>
       </c>
       <c r="M91" t="n">
         <v>87</v>
       </c>
       <c r="N91" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="O91" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.5072463768115942</v>
       </c>
       <c r="P91" t="n">
         <v>0.4022988505747127</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.4487179487179487</v>
       </c>
       <c r="R91" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="S91" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="T91" t="n">
         <v>52</v>
@@ -7756,52 +7756,52 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H92" t="n">
         <v>106</v>
       </c>
       <c r="I92" t="n">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="J92" t="n">
-        <v>0.564935064935065</v>
+        <v>0.5625</v>
       </c>
       <c r="K92" t="n">
-        <v>0.8207547169811321</v>
+        <v>0.5943396226415094</v>
       </c>
       <c r="L92" t="n">
-        <v>0.6692307692307693</v>
+        <v>0.5779816513761468</v>
       </c>
       <c r="M92" t="n">
         <v>86</v>
       </c>
       <c r="N92" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="O92" t="n">
-        <v>0.5</v>
+        <v>0.4625</v>
       </c>
       <c r="P92" t="n">
-        <v>0.2209302325581395</v>
+        <v>0.4302325581395349</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.3064516129032258</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="R92" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="S92" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="T92" t="n">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="U92" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="93">
@@ -7823,52 +7823,52 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="H93" t="n">
         <v>103</v>
       </c>
       <c r="I93" t="n">
-        <v>159</v>
+        <v>124</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="K93" t="n">
-        <v>0.7864077669902912</v>
+        <v>0.6310679611650486</v>
       </c>
       <c r="L93" t="n">
-        <v>0.6183206106870229</v>
+        <v>0.5726872246696035</v>
       </c>
       <c r="M93" t="n">
         <v>89</v>
       </c>
       <c r="N93" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="O93" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4411764705882353</v>
       </c>
       <c r="P93" t="n">
-        <v>0.1235955056179775</v>
+        <v>0.3370786516853932</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.180327868852459</v>
+        <v>0.3821656050955414</v>
       </c>
       <c r="R93" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="S93" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="T93" t="n">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="U93" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="94">
@@ -7890,52 +7890,52 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H94" t="n">
         <v>104</v>
       </c>
       <c r="I94" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J94" t="n">
-        <v>0.5590551181102362</v>
+        <v>0.536</v>
       </c>
       <c r="K94" t="n">
-        <v>0.6826923076923077</v>
+        <v>0.6442307692307693</v>
       </c>
       <c r="L94" t="n">
-        <v>0.6147186147186147</v>
+        <v>0.5851528384279477</v>
       </c>
       <c r="M94" t="n">
         <v>88</v>
       </c>
       <c r="N94" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="O94" t="n">
-        <v>0.4923076923076923</v>
+        <v>0.4477611940298508</v>
       </c>
       <c r="P94" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.4183006535947713</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="R94" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="S94" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="T94" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U94" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
@@ -7957,52 +7957,52 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H95" t="n">
         <v>96</v>
       </c>
       <c r="I95" t="n">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4962962962962963</v>
+        <v>0.4786324786324787</v>
       </c>
       <c r="K95" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="L95" t="n">
-        <v>0.5800865800865801</v>
+        <v>0.5258215962441315</v>
       </c>
       <c r="M95" t="n">
         <v>96</v>
       </c>
       <c r="N95" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="O95" t="n">
-        <v>0.4912280701754386</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="P95" t="n">
-        <v>0.2916666666666667</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.3660130718954248</v>
+        <v>0.4093567251461988</v>
       </c>
       <c r="R95" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="S95" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="T95" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="U95" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96">
@@ -8024,52 +8024,52 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H96" t="n">
         <v>94</v>
       </c>
       <c r="I96" t="n">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4802631578947368</v>
+        <v>0.4748201438848921</v>
       </c>
       <c r="K96" t="n">
-        <v>0.776595744680851</v>
+        <v>0.7021276595744681</v>
       </c>
       <c r="L96" t="n">
-        <v>0.5934959349593495</v>
+        <v>0.5665236051502146</v>
       </c>
       <c r="M96" t="n">
         <v>98</v>
       </c>
       <c r="N96" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="O96" t="n">
-        <v>0.475</v>
+        <v>0.4716981132075472</v>
       </c>
       <c r="P96" t="n">
-        <v>0.1938775510204082</v>
+        <v>0.2551020408163265</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.2753623188405797</v>
+        <v>0.3311258278145695</v>
       </c>
       <c r="R96" t="n">
+        <v>66</v>
+      </c>
+      <c r="S96" t="n">
+        <v>28</v>
+      </c>
+      <c r="T96" t="n">
         <v>73</v>
       </c>
-      <c r="S96" t="n">
-        <v>21</v>
-      </c>
-      <c r="T96" t="n">
-        <v>79</v>
-      </c>
       <c r="U96" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="97">
@@ -8091,52 +8091,52 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="H97" t="n">
         <v>94</v>
       </c>
       <c r="I97" t="n">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="J97" t="n">
-        <v>0.512396694214876</v>
+        <v>0.5252525252525253</v>
       </c>
       <c r="K97" t="n">
-        <v>0.6595744680851063</v>
+        <v>0.5531914893617021</v>
       </c>
       <c r="L97" t="n">
-        <v>0.5767441860465115</v>
+        <v>0.5388601036269431</v>
       </c>
       <c r="M97" t="n">
         <v>98</v>
       </c>
       <c r="N97" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="O97" t="n">
-        <v>0.5492957746478874</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="P97" t="n">
-        <v>0.3979591836734694</v>
+        <v>0.5204081632653061</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5340314136125655</v>
       </c>
       <c r="R97" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="S97" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="T97" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="U97" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -8158,52 +8158,52 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G98" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="H98" t="n">
         <v>90</v>
       </c>
       <c r="I98" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="J98" t="n">
-        <v>0.460431654676259</v>
+        <v>0.4793388429752066</v>
       </c>
       <c r="K98" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="L98" t="n">
-        <v>0.5589519650655023</v>
+        <v>0.5497630331753555</v>
       </c>
       <c r="M98" t="n">
         <v>102</v>
       </c>
       <c r="N98" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="O98" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.5492957746478874</v>
       </c>
       <c r="P98" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.3483870967741935</v>
+        <v>0.4508670520231214</v>
       </c>
       <c r="R98" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="S98" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="T98" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="U98" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="99">
@@ -8225,52 +8225,52 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="H99" t="n">
         <v>101</v>
       </c>
       <c r="I99" t="n">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="J99" t="n">
-        <v>0.503448275862069</v>
+        <v>0.4918032786885246</v>
       </c>
       <c r="K99" t="n">
-        <v>0.7227722772277227</v>
+        <v>0.594059405940594</v>
       </c>
       <c r="L99" t="n">
-        <v>0.5934959349593495</v>
+        <v>0.5381165919282511</v>
       </c>
       <c r="M99" t="n">
         <v>91</v>
       </c>
       <c r="N99" t="n">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="O99" t="n">
-        <v>0.4042553191489361</v>
+        <v>0.4142857142857143</v>
       </c>
       <c r="P99" t="n">
-        <v>0.2087912087912088</v>
+        <v>0.3186813186813187</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.2753623188405797</v>
+        <v>0.3602484472049689</v>
       </c>
       <c r="R99" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="S99" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="T99" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="U99" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="100">
@@ -8292,52 +8292,52 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.421875</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G100" t="n">
-        <v>0.421875</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="H100" t="n">
         <v>90</v>
       </c>
       <c r="I100" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4244604316546763</v>
+        <v>0.4552845528455284</v>
       </c>
       <c r="K100" t="n">
-        <v>0.6555555555555556</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="L100" t="n">
-        <v>0.5152838427947599</v>
+        <v>0.5258215962441314</v>
       </c>
       <c r="M100" t="n">
         <v>102</v>
       </c>
       <c r="N100" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="O100" t="n">
-        <v>0.4150943396226415</v>
+        <v>0.5072463768115942</v>
       </c>
       <c r="P100" t="n">
-        <v>0.2156862745098039</v>
+        <v>0.3431372549019608</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.2838709677419355</v>
+        <v>0.4093567251461988</v>
       </c>
       <c r="R100" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="S100" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="T100" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="U100" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
@@ -8359,52 +8359,52 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G101" t="n">
-        <v>0.515625</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="H101" t="n">
         <v>98</v>
       </c>
       <c r="I101" t="n">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5177304964539007</v>
+        <v>0.525</v>
       </c>
       <c r="K101" t="n">
-        <v>0.7448979591836735</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="L101" t="n">
-        <v>0.610878661087866</v>
+        <v>0.5779816513761468</v>
       </c>
       <c r="M101" t="n">
         <v>94</v>
       </c>
       <c r="N101" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="O101" t="n">
-        <v>0.5098039215686274</v>
+        <v>0.5138888888888888</v>
       </c>
       <c r="P101" t="n">
-        <v>0.2765957446808511</v>
+        <v>0.3936170212765958</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.3586206896551724</v>
+        <v>0.4457831325301205</v>
       </c>
       <c r="R101" t="n">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="T101" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="U101" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7002</v>
+        <v>6083</v>
       </c>
       <c r="C2" t="n">
-        <v>2552</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="3">
@@ -8453,10 +8453,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7172</v>
+        <v>6222</v>
       </c>
       <c r="C3" t="n">
-        <v>2474</v>
+        <v>3424</v>
       </c>
     </row>
   </sheetData>
@@ -8507,16 +8507,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>304</v>
+        <v>227</v>
       </c>
       <c r="C2" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="D2" t="n">
-        <v>326</v>
+        <v>265</v>
       </c>
       <c r="E2" t="n">
-        <v>87</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3">
@@ -8526,16 +8526,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>340</v>
+        <v>260</v>
       </c>
       <c r="C3" t="n">
-        <v>64</v>
+        <v>144</v>
       </c>
       <c r="D3" t="n">
-        <v>323</v>
+        <v>261</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4">
@@ -8545,16 +8545,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>456</v>
+        <v>520</v>
       </c>
       <c r="C4" t="n">
-        <v>365</v>
+        <v>301</v>
       </c>
       <c r="D4" t="n">
-        <v>447</v>
+        <v>497</v>
       </c>
       <c r="E4" t="n">
-        <v>332</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
@@ -8564,16 +8564,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>617</v>
+        <v>488</v>
       </c>
       <c r="C5" t="n">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="D5" t="n">
-        <v>629</v>
+        <v>473</v>
       </c>
       <c r="E5" t="n">
-        <v>166</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
@@ -8583,16 +8583,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>667</v>
+        <v>591</v>
       </c>
       <c r="C6" t="n">
-        <v>154</v>
+        <v>230</v>
       </c>
       <c r="D6" t="n">
-        <v>642</v>
+        <v>565</v>
       </c>
       <c r="E6" t="n">
-        <v>137</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7">
@@ -8602,16 +8602,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>726</v>
+        <v>700</v>
       </c>
       <c r="C7" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D7" t="n">
-        <v>844</v>
+        <v>812</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
@@ -8621,16 +8621,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>671</v>
+        <v>588</v>
       </c>
       <c r="C8" t="n">
-        <v>98</v>
+        <v>181</v>
       </c>
       <c r="D8" t="n">
-        <v>726</v>
+        <v>647</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>184</v>
       </c>
     </row>
     <row r="9">
@@ -8640,16 +8640,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>666</v>
+        <v>510</v>
       </c>
       <c r="C9" t="n">
-        <v>156</v>
+        <v>312</v>
       </c>
       <c r="D9" t="n">
-        <v>628</v>
+        <v>509</v>
       </c>
       <c r="E9" t="n">
-        <v>150</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -8659,16 +8659,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="C10" t="n">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D10" t="n">
-        <v>743</v>
+        <v>717</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -8678,16 +8678,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>427</v>
+        <v>266</v>
       </c>
       <c r="C11" t="n">
-        <v>385</v>
+        <v>546</v>
       </c>
       <c r="D11" t="n">
-        <v>430</v>
+        <v>267</v>
       </c>
       <c r="E11" t="n">
-        <v>358</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12">
@@ -8697,16 +8697,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>498</v>
+        <v>366</v>
       </c>
       <c r="C12" t="n">
-        <v>290</v>
+        <v>422</v>
       </c>
       <c r="D12" t="n">
-        <v>506</v>
+        <v>365</v>
       </c>
       <c r="E12" t="n">
-        <v>306</v>
+        <v>447</v>
       </c>
     </row>
     <row r="13">
@@ -8716,16 +8716,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>537</v>
+        <v>476</v>
       </c>
       <c r="C13" t="n">
-        <v>276</v>
+        <v>337</v>
       </c>
       <c r="D13" t="n">
-        <v>529</v>
+        <v>445</v>
       </c>
       <c r="E13" t="n">
-        <v>258</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14">
@@ -8735,10 +8735,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C14" t="n">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="D14" t="n">
         <v>399</v>

--- a/Data/ModelResponse/1A/evaluation/1A_evaluation_summary.xlsx
+++ b/Data/ModelResponse/1A/evaluation/1A_evaluation_summary.xlsx
@@ -11,7 +11,6 @@
     <sheet name="category_metrics" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="video_metrics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="global_confusion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="category_confusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -428,102 +427,82 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>sample_count</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_prediction_count</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_prediction_count</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>invalid_prediction_rate</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>valid_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>true_negative</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>false_negative</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_positive</t>
         </is>
       </c>
     </row>
@@ -546,52 +525,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.49515625</v>
+        <v>0.6871875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.49515625</v>
+        <v>0.6871875</v>
       </c>
       <c r="H2" t="n">
-        <v>9554</v>
+        <v>0.6714340935446463</v>
       </c>
       <c r="I2" t="n">
-        <v>12305</v>
+        <v>0.7272346661084362</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4943518894758228</v>
+        <v>0.6982212842930359</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6366966715511827</v>
+        <v>0.7056032535020335</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5565670890708632</v>
+        <v>0.647522289031723</v>
       </c>
       <c r="M2" t="n">
-        <v>9646</v>
+        <v>0.6753162504054493</v>
       </c>
       <c r="N2" t="n">
-        <v>6895</v>
+        <v>6948</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4965917331399565</v>
+        <v>2606</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3549657889280531</v>
+        <v>3400</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4140015718517623</v>
-      </c>
-      <c r="R2" t="n">
-        <v>6083</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3471</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6222</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3424</v>
+        <v>6246</v>
       </c>
     </row>
   </sheetData>
@@ -605,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,102 +583,82 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>sample_count</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_prediction_count</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_prediction_count</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>invalid_prediction_rate</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>valid_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>true_negative</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>false_negative</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_positive</t>
         </is>
       </c>
     </row>
@@ -734,52 +681,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.46875</v>
+        <v>0.6575</v>
       </c>
       <c r="G2" t="n">
-        <v>0.46875</v>
+        <v>0.6575</v>
       </c>
       <c r="H2" t="n">
-        <v>387</v>
+        <v>0.6475195822454308</v>
       </c>
       <c r="I2" t="n">
-        <v>492</v>
+        <v>0.6408268733850129</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4613821138211382</v>
+        <v>0.644155844155844</v>
       </c>
       <c r="K2" t="n">
-        <v>0.58656330749354</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5164960182025029</v>
+        <v>0.6731234866828087</v>
       </c>
       <c r="M2" t="n">
-        <v>413</v>
+        <v>0.6698795180722892</v>
       </c>
       <c r="N2" t="n">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4805194805194805</v>
+        <v>139</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3583535108958838</v>
+        <v>135</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4105409153952844</v>
-      </c>
-      <c r="R2" t="n">
-        <v>227</v>
-      </c>
-      <c r="S2" t="n">
-        <v>160</v>
-      </c>
-      <c r="T2" t="n">
-        <v>265</v>
-      </c>
-      <c r="U2" t="n">
-        <v>148</v>
+        <v>278</v>
       </c>
     </row>
     <row r="3">
@@ -801,52 +736,40 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.49375</v>
+        <v>0.68875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.49375</v>
+        <v>0.68875</v>
       </c>
       <c r="H3" t="n">
-        <v>404</v>
+        <v>0.6695842450765864</v>
       </c>
       <c r="I3" t="n">
-        <v>521</v>
+        <v>0.7574257425742574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4990403071017274</v>
+        <v>0.710801393728223</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6435643564356436</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5621621621621622</v>
+        <v>0.6186868686868687</v>
       </c>
       <c r="M3" t="n">
-        <v>396</v>
+        <v>0.6630581867388363</v>
       </c>
       <c r="N3" t="n">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4838709677419355</v>
+        <v>98</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3409090909090909</v>
+        <v>151</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R3" t="n">
-        <v>260</v>
-      </c>
-      <c r="S3" t="n">
-        <v>144</v>
-      </c>
-      <c r="T3" t="n">
-        <v>261</v>
-      </c>
-      <c r="U3" t="n">
-        <v>135</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4">
@@ -868,52 +791,40 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.50125</v>
+        <v>0.7787500000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.50125</v>
+        <v>0.7787500000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>821</v>
+        <v>0.8564885496183207</v>
       </c>
       <c r="I4" t="n">
-        <v>1017</v>
+        <v>0.6833130328867235</v>
       </c>
       <c r="J4" t="n">
-        <v>0.511307767944936</v>
+        <v>0.7601626016260163</v>
       </c>
       <c r="K4" t="n">
-        <v>0.633373934226553</v>
+        <v>0.7248677248677249</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5658324265505985</v>
+        <v>0.8793324775353016</v>
       </c>
       <c r="M4" t="n">
-        <v>779</v>
+        <v>0.794663573085847</v>
       </c>
       <c r="N4" t="n">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="O4" t="n">
-        <v>0.483704974271012</v>
+        <v>260</v>
       </c>
       <c r="P4" t="n">
-        <v>0.362002567394095</v>
+        <v>94</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4140969162995595</v>
-      </c>
-      <c r="R4" t="n">
-        <v>520</v>
-      </c>
-      <c r="S4" t="n">
-        <v>301</v>
-      </c>
-      <c r="T4" t="n">
-        <v>497</v>
-      </c>
-      <c r="U4" t="n">
-        <v>282</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5">
@@ -935,52 +846,40 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.50625</v>
+        <v>0.561875</v>
       </c>
       <c r="G5" t="n">
-        <v>0.50625</v>
+        <v>0.561875</v>
       </c>
       <c r="H5" t="n">
-        <v>805</v>
+        <v>0.5470162748643761</v>
       </c>
       <c r="I5" t="n">
-        <v>961</v>
+        <v>0.7515527950310559</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5078043704474505</v>
+        <v>0.6331763474620618</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6062111801242236</v>
+        <v>0.5951417004048583</v>
       </c>
       <c r="L5" t="n">
-        <v>0.552661381653454</v>
+        <v>0.369811320754717</v>
       </c>
       <c r="M5" t="n">
-        <v>795</v>
+        <v>0.4561675717610551</v>
       </c>
       <c r="N5" t="n">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5039123630672926</v>
+        <v>200</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4050314465408805</v>
+        <v>501</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4490934449093445</v>
-      </c>
-      <c r="R5" t="n">
-        <v>488</v>
-      </c>
-      <c r="S5" t="n">
-        <v>317</v>
-      </c>
-      <c r="T5" t="n">
-        <v>473</v>
-      </c>
-      <c r="U5" t="n">
-        <v>322</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6">
@@ -1002,52 +901,40 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.503125</v>
+        <v>0.608125</v>
       </c>
       <c r="G6" t="n">
-        <v>0.503125</v>
+        <v>0.608125</v>
       </c>
       <c r="H6" t="n">
-        <v>821</v>
+        <v>0.5858407079646017</v>
       </c>
       <c r="I6" t="n">
-        <v>1156</v>
+        <v>0.8063337393422655</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5112456747404844</v>
+        <v>0.6786263454638647</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7198538367844093</v>
+        <v>0.6617021276595745</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5978755690440061</v>
+        <v>0.3992297817715019</v>
       </c>
       <c r="M6" t="n">
-        <v>779</v>
+        <v>0.4979983987189753</v>
       </c>
       <c r="N6" t="n">
-        <v>444</v>
+        <v>662</v>
       </c>
       <c r="O6" t="n">
-        <v>0.481981981981982</v>
+        <v>159</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2747111681643132</v>
+        <v>468</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3499591169255928</v>
-      </c>
-      <c r="R6" t="n">
-        <v>591</v>
-      </c>
-      <c r="S6" t="n">
-        <v>230</v>
-      </c>
-      <c r="T6" t="n">
-        <v>565</v>
-      </c>
-      <c r="U6" t="n">
-        <v>214</v>
+        <v>311</v>
       </c>
     </row>
     <row r="7">
@@ -1069,52 +956,40 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4675</v>
+        <v>0.964375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4675</v>
+        <v>0.964375</v>
       </c>
       <c r="H7" t="n">
-        <v>740</v>
+        <v>0.9658935879945429</v>
       </c>
       <c r="I7" t="n">
-        <v>1512</v>
+        <v>0.9567567567567568</v>
       </c>
       <c r="J7" t="n">
-        <v>0.462962962962963</v>
+        <v>0.9613034623217922</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9459459459459459</v>
+        <v>0.9630911188004614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6216696269982238</v>
+        <v>0.9709302325581395</v>
       </c>
       <c r="M7" t="n">
-        <v>860</v>
+        <v>0.9669947886508397</v>
       </c>
       <c r="N7" t="n">
-        <v>88</v>
+        <v>708</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5454545454545454</v>
+        <v>32</v>
       </c>
       <c r="P7" t="n">
-        <v>0.05581395348837209</v>
+        <v>25</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1012658227848101</v>
-      </c>
-      <c r="R7" t="n">
-        <v>700</v>
-      </c>
-      <c r="S7" t="n">
-        <v>40</v>
-      </c>
-      <c r="T7" t="n">
-        <v>812</v>
-      </c>
-      <c r="U7" t="n">
-        <v>48</v>
+        <v>835</v>
       </c>
     </row>
     <row r="8">
@@ -1136,52 +1011,40 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4825</v>
+        <v>0.6525</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4825</v>
+        <v>0.6525</v>
       </c>
       <c r="H8" t="n">
-        <v>769</v>
+        <v>0.5877988458367683</v>
       </c>
       <c r="I8" t="n">
-        <v>1235</v>
+        <v>0.9271781534460338</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4761133603238866</v>
+        <v>0.7194752774974773</v>
       </c>
       <c r="K8" t="n">
-        <v>0.764629388816645</v>
+        <v>0.8552971576227391</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5868263473053893</v>
+        <v>0.3983152827918171</v>
       </c>
       <c r="M8" t="n">
-        <v>831</v>
+        <v>0.5435139573070608</v>
       </c>
       <c r="N8" t="n">
-        <v>365</v>
+        <v>713</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5041095890410959</v>
+        <v>56</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2214199759326113</v>
+        <v>500</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3076923076923077</v>
-      </c>
-      <c r="R8" t="n">
-        <v>588</v>
-      </c>
-      <c r="S8" t="n">
-        <v>181</v>
-      </c>
-      <c r="T8" t="n">
-        <v>647</v>
-      </c>
-      <c r="U8" t="n">
-        <v>184</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -1203,52 +1066,40 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.486875</v>
+        <v>0.74375</v>
       </c>
       <c r="G9" t="n">
-        <v>0.486875</v>
+        <v>0.74375</v>
       </c>
       <c r="H9" t="n">
-        <v>822</v>
+        <v>0.7994186046511628</v>
       </c>
       <c r="I9" t="n">
-        <v>1019</v>
+        <v>0.6690997566909975</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5004906771344455</v>
+        <v>0.728476821192053</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6204379562043796</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5540467137425312</v>
+        <v>0.8226221079691517</v>
       </c>
       <c r="M9" t="n">
-        <v>778</v>
+        <v>0.757396449704142</v>
       </c>
       <c r="N9" t="n">
-        <v>581</v>
+        <v>550</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4629948364888124</v>
+        <v>272</v>
       </c>
       <c r="P9" t="n">
-        <v>0.345758354755784</v>
+        <v>138</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3958793230316409</v>
-      </c>
-      <c r="R9" t="n">
-        <v>510</v>
-      </c>
-      <c r="S9" t="n">
-        <v>312</v>
-      </c>
-      <c r="T9" t="n">
-        <v>509</v>
-      </c>
-      <c r="U9" t="n">
-        <v>269</v>
+        <v>640</v>
       </c>
     </row>
     <row r="10">
@@ -1270,52 +1121,40 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.505625</v>
+        <v>0.7162500000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.505625</v>
+        <v>0.7162500000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>804</v>
+        <v>0.6535087719298246</v>
       </c>
       <c r="I10" t="n">
-        <v>1447</v>
+        <v>0.9266169154228856</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5044920525224602</v>
+        <v>0.7664609053497943</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9079601990049752</v>
+        <v>0.8717391304347826</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6486006219458018</v>
+        <v>0.5037688442211056</v>
       </c>
       <c r="M10" t="n">
-        <v>796</v>
+        <v>0.6385350318471338</v>
       </c>
       <c r="N10" t="n">
-        <v>153</v>
+        <v>745</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5163398692810458</v>
+        <v>59</v>
       </c>
       <c r="P10" t="n">
-        <v>0.09924623115577889</v>
+        <v>395</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.166491043203372</v>
-      </c>
-      <c r="R10" t="n">
-        <v>730</v>
-      </c>
-      <c r="S10" t="n">
-        <v>74</v>
-      </c>
-      <c r="T10" t="n">
-        <v>717</v>
-      </c>
-      <c r="U10" t="n">
-        <v>79</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -1337,52 +1176,40 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.491875</v>
+        <v>0.574375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.491875</v>
+        <v>0.574375</v>
       </c>
       <c r="H11" t="n">
-        <v>812</v>
+        <v>0.6072013093289689</v>
       </c>
       <c r="I11" t="n">
-        <v>533</v>
+        <v>0.456896551724138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.49906191369606</v>
+        <v>0.5214335910049192</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3275862068965517</v>
+        <v>0.5540950455005056</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3955390334572491</v>
+        <v>0.6954314720812182</v>
       </c>
       <c r="M11" t="n">
-        <v>788</v>
+        <v>0.6167698368036015</v>
       </c>
       <c r="N11" t="n">
-        <v>1067</v>
+        <v>371</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4882849109653233</v>
+        <v>441</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6611675126903553</v>
+        <v>240</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5617250673854447</v>
-      </c>
-      <c r="R11" t="n">
-        <v>266</v>
-      </c>
-      <c r="S11" t="n">
-        <v>546</v>
-      </c>
-      <c r="T11" t="n">
-        <v>267</v>
-      </c>
-      <c r="U11" t="n">
-        <v>521</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12">
@@ -1404,52 +1231,40 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.508125</v>
+        <v>0.615</v>
       </c>
       <c r="G12" t="n">
-        <v>0.508125</v>
+        <v>0.615</v>
       </c>
       <c r="H12" t="n">
-        <v>788</v>
+        <v>0.6143617021276596</v>
       </c>
       <c r="I12" t="n">
-        <v>731</v>
+        <v>0.5862944162436549</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5006839945280438</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4644670050761421</v>
+        <v>0.6155660377358491</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4818959842001317</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="M12" t="n">
-        <v>812</v>
+        <v>0.6289156626506025</v>
       </c>
       <c r="N12" t="n">
-        <v>869</v>
+        <v>462</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5143843498273878</v>
+        <v>326</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5504926108374384</v>
+        <v>290</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5318262938726948</v>
-      </c>
-      <c r="R12" t="n">
-        <v>366</v>
-      </c>
-      <c r="S12" t="n">
-        <v>422</v>
-      </c>
-      <c r="T12" t="n">
-        <v>365</v>
-      </c>
-      <c r="U12" t="n">
-        <v>447</v>
+        <v>522</v>
       </c>
     </row>
     <row r="13">
@@ -1471,52 +1286,40 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.51125</v>
+        <v>0.7075</v>
       </c>
       <c r="G13" t="n">
-        <v>0.51125</v>
+        <v>0.7075</v>
       </c>
       <c r="H13" t="n">
-        <v>813</v>
+        <v>0.7031802120141343</v>
       </c>
       <c r="I13" t="n">
-        <v>921</v>
+        <v>0.7343173431734318</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5168295331161781</v>
+        <v>0.7184115523465704</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5854858548585485</v>
+        <v>0.7123834886817576</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5490196078431373</v>
+        <v>0.6797966963151207</v>
       </c>
       <c r="M13" t="n">
-        <v>787</v>
+        <v>0.6957087126137841</v>
       </c>
       <c r="N13" t="n">
-        <v>679</v>
+        <v>597</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5036818851251841</v>
+        <v>216</v>
       </c>
       <c r="P13" t="n">
-        <v>0.434561626429479</v>
+        <v>252</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4665757162346521</v>
-      </c>
-      <c r="R13" t="n">
-        <v>476</v>
-      </c>
-      <c r="S13" t="n">
-        <v>337</v>
-      </c>
-      <c r="T13" t="n">
-        <v>445</v>
-      </c>
-      <c r="U13" t="n">
-        <v>342</v>
+        <v>535</v>
       </c>
     </row>
     <row r="14">
@@ -1538,52 +1341,40 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.49625</v>
+        <v>0.650625</v>
       </c>
       <c r="G14" t="n">
-        <v>0.49625</v>
+        <v>0.650625</v>
       </c>
       <c r="H14" t="n">
-        <v>768</v>
+        <v>0.6656101426307448</v>
       </c>
       <c r="I14" t="n">
-        <v>760</v>
+        <v>0.546875</v>
       </c>
       <c r="J14" t="n">
-        <v>0.475</v>
+        <v>0.6004288777698356</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4700520833333333</v>
+        <v>0.6408668730650154</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4725130890052356</v>
+        <v>0.7463942307692307</v>
       </c>
       <c r="M14" t="n">
-        <v>832</v>
+        <v>0.6896168795113825</v>
       </c>
       <c r="N14" t="n">
-        <v>840</v>
+        <v>420</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5154761904761904</v>
+        <v>348</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5204326923076923</v>
+        <v>211</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5179425837320574</v>
-      </c>
-      <c r="R14" t="n">
-        <v>361</v>
-      </c>
-      <c r="S14" t="n">
-        <v>407</v>
-      </c>
-      <c r="T14" t="n">
-        <v>399</v>
-      </c>
-      <c r="U14" t="n">
-        <v>433</v>
+        <v>621</v>
       </c>
     </row>
   </sheetData>
@@ -1597,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,102 +1399,82 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n_samples</t>
+          <t>sample_count</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>valid_predictions</t>
+          <t>valid_prediction_count</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>invalid_predictions</t>
+          <t>invalid_prediction_count</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>empty_raw_outputs</t>
+          <t>invalid_prediction_rate</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>overall_accuracy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Accuracy_valid_only</t>
+          <t>valid_accuracy</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Support_0</t>
+          <t>precision_label_0</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Predicted_as_0</t>
+          <t>recall_label_0</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precision_0</t>
+          <t>f1_label_0</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Recall_0</t>
+          <t>precision_label_1</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>F1_0</t>
+          <t>recall_label_1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Support_1</t>
+          <t>f1_label_1</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Predicted_as_1</t>
+          <t>true_negative</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Precision_1</t>
+          <t>false_positive</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Recall_1</t>
+          <t>false_negative</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>F1_1</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
+          <t>true_positive</t>
         </is>
       </c>
     </row>
@@ -1726,52 +1497,40 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.484375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.484375</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H2" t="n">
-        <v>89</v>
+        <v>0.6633663366336634</v>
       </c>
       <c r="I2" t="n">
-        <v>126</v>
+        <v>0.7528089887640449</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4603174603174603</v>
+        <v>0.7052631578947368</v>
       </c>
       <c r="K2" t="n">
-        <v>0.651685393258427</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5395348837209303</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="M2" t="n">
-        <v>103</v>
+        <v>0.7113402061855669</v>
       </c>
       <c r="N2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5303030303030303</v>
+        <v>22</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3398058252427185</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4142011834319526</v>
-      </c>
-      <c r="R2" t="n">
-        <v>58</v>
-      </c>
-      <c r="S2" t="n">
-        <v>31</v>
-      </c>
-      <c r="T2" t="n">
-        <v>68</v>
-      </c>
-      <c r="U2" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -1793,52 +1552,40 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.46875</v>
+        <v>0.6875</v>
       </c>
       <c r="G3" t="n">
-        <v>0.46875</v>
+        <v>0.6875</v>
       </c>
       <c r="H3" t="n">
-        <v>93</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I3" t="n">
-        <v>109</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4587155963302753</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5376344086021505</v>
+        <v>0.6695652173913044</v>
       </c>
       <c r="L3" t="n">
-        <v>0.495049504950495</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="M3" t="n">
-        <v>99</v>
+        <v>0.719626168224299</v>
       </c>
       <c r="N3" t="n">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4819277108433735</v>
+        <v>38</v>
       </c>
       <c r="P3" t="n">
-        <v>0.404040404040404</v>
+        <v>22</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4395604395604396</v>
-      </c>
-      <c r="R3" t="n">
-        <v>50</v>
-      </c>
-      <c r="S3" t="n">
-        <v>43</v>
-      </c>
-      <c r="T3" t="n">
-        <v>59</v>
-      </c>
-      <c r="U3" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -1860,52 +1607,40 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="H4" t="n">
-        <v>110</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="I4" t="n">
-        <v>120</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.55</v>
+        <v>0.711111111111111</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6</v>
+        <v>0.6103896103896104</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5739130434782609</v>
+        <v>0.573170731707317</v>
       </c>
       <c r="M4" t="n">
-        <v>82</v>
+        <v>0.5911949685534591</v>
       </c>
       <c r="N4" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3888888888888889</v>
+        <v>30</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3414634146341464</v>
+        <v>35</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="R4" t="n">
-        <v>66</v>
-      </c>
-      <c r="S4" t="n">
-        <v>44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>54</v>
-      </c>
-      <c r="U4" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -1927,52 +1662,40 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.7395833333333334</v>
       </c>
       <c r="H5" t="n">
-        <v>97</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="I5" t="n">
-        <v>129</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5116279069767442</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6804123711340206</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="L5" t="n">
-        <v>0.584070796460177</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="M5" t="n">
-        <v>95</v>
+        <v>0.7368421052631579</v>
       </c>
       <c r="N5" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5079365079365079</v>
+        <v>25</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3368421052631579</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4050632911392405</v>
-      </c>
-      <c r="R5" t="n">
-        <v>66</v>
-      </c>
-      <c r="S5" t="n">
-        <v>31</v>
-      </c>
-      <c r="T5" t="n">
-        <v>63</v>
-      </c>
-      <c r="U5" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -1994,52 +1717,40 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5</v>
+        <v>0.65625</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.65625</v>
       </c>
       <c r="H6" t="n">
-        <v>103</v>
+        <v>0.6697247706422018</v>
       </c>
       <c r="I6" t="n">
-        <v>127</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5275590551181102</v>
+        <v>0.6886792452830189</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6504854368932039</v>
+        <v>0.6385542168674698</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5826086956521738</v>
+        <v>0.5955056179775281</v>
       </c>
       <c r="M6" t="n">
-        <v>89</v>
+        <v>0.616279069767442</v>
       </c>
       <c r="N6" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4461538461538462</v>
+        <v>30</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3258426966292135</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3766233766233766</v>
-      </c>
-      <c r="R6" t="n">
-        <v>67</v>
-      </c>
-      <c r="S6" t="n">
-        <v>36</v>
-      </c>
-      <c r="T6" t="n">
-        <v>60</v>
-      </c>
-      <c r="U6" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -2061,52 +1772,40 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
+        <v>0.6509433962264151</v>
       </c>
       <c r="I7" t="n">
-        <v>121</v>
+        <v>0.7340425531914894</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4710743801652892</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6063829787234043</v>
+        <v>0.7093023255813954</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5302325581395348</v>
+        <v>0.6224489795918368</v>
       </c>
       <c r="M7" t="n">
-        <v>98</v>
+        <v>0.6630434782608696</v>
       </c>
       <c r="N7" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4788732394366197</v>
+        <v>25</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3469387755102041</v>
+        <v>37</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4023668639053254</v>
-      </c>
-      <c r="R7" t="n">
-        <v>57</v>
-      </c>
-      <c r="S7" t="n">
-        <v>37</v>
-      </c>
-      <c r="T7" t="n">
-        <v>64</v>
-      </c>
-      <c r="U7" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
@@ -2128,52 +1827,40 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4375</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4375</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>92</v>
+        <v>0.7128712871287128</v>
       </c>
       <c r="I8" t="n">
-        <v>140</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4428571428571428</v>
+        <v>0.7461139896373056</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6739130434782609</v>
+        <v>0.7802197802197802</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5344827586206895</v>
+        <v>0.71</v>
       </c>
       <c r="M8" t="n">
-        <v>100</v>
+        <v>0.743455497382199</v>
       </c>
       <c r="N8" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4230769230769231</v>
+        <v>20</v>
       </c>
       <c r="P8" t="n">
-        <v>0.22</v>
+        <v>29</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="R8" t="n">
-        <v>62</v>
-      </c>
-      <c r="S8" t="n">
-        <v>30</v>
-      </c>
-      <c r="T8" t="n">
-        <v>78</v>
-      </c>
-      <c r="U8" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -2195,52 +1882,40 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="H9" t="n">
-        <v>104</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="I9" t="n">
-        <v>124</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5241935483870968</v>
+        <v>0.6542056074766355</v>
       </c>
       <c r="K9" t="n">
-        <v>0.625</v>
+        <v>0.5853658536585366</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5701754385964912</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>0.5647058823529411</v>
       </c>
       <c r="N9" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4264705882352941</v>
+        <v>34</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3295454545454545</v>
+        <v>40</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3717948717948718</v>
-      </c>
-      <c r="R9" t="n">
-        <v>65</v>
-      </c>
-      <c r="S9" t="n">
-        <v>39</v>
-      </c>
-      <c r="T9" t="n">
-        <v>59</v>
-      </c>
-      <c r="U9" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -2262,52 +1937,40 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="H10" t="n">
-        <v>106</v>
+        <v>0.6991150442477876</v>
       </c>
       <c r="I10" t="n">
-        <v>116</v>
+        <v>0.7452830188679245</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5431034482758621</v>
+        <v>0.7214611872146119</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5943396226415094</v>
+        <v>0.6582278481012658</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5675675675675675</v>
+        <v>0.6046511627906976</v>
       </c>
       <c r="M10" t="n">
-        <v>86</v>
+        <v>0.6303030303030303</v>
       </c>
       <c r="N10" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4342105263157895</v>
+        <v>27</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3837209302325582</v>
+        <v>34</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="R10" t="n">
-        <v>63</v>
-      </c>
-      <c r="S10" t="n">
-        <v>43</v>
-      </c>
-      <c r="T10" t="n">
-        <v>53</v>
-      </c>
-      <c r="U10" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -2329,52 +1992,40 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>0.6754385964912281</v>
       </c>
       <c r="I11" t="n">
-        <v>133</v>
+        <v>0.8020833333333334</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5037593984962406</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6979166666666666</v>
+        <v>0.7564102564102564</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5851528384279476</v>
+        <v>0.6145833333333334</v>
       </c>
       <c r="M11" t="n">
-        <v>96</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="N11" t="n">
+        <v>77</v>
+      </c>
+      <c r="O11" t="n">
+        <v>19</v>
+      </c>
+      <c r="P11" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q11" t="n">
         <v>59</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.5084745762711864</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3870967741935484</v>
-      </c>
-      <c r="R11" t="n">
-        <v>67</v>
-      </c>
-      <c r="S11" t="n">
-        <v>29</v>
-      </c>
-      <c r="T11" t="n">
-        <v>66</v>
-      </c>
-      <c r="U11" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="12">
@@ -2396,52 +2047,40 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4166666666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H12" t="n">
-        <v>96</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="I12" t="n">
-        <v>120</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.6777777777777777</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.6759259259259259</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4814814814814815</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="M12" t="n">
-        <v>96</v>
+        <v>0.7156862745098039</v>
       </c>
       <c r="N12" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="O12" t="n">
-        <v>0.3888888888888889</v>
+        <v>35</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2916666666666667</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="R12" t="n">
-        <v>52</v>
-      </c>
-      <c r="S12" t="n">
-        <v>44</v>
-      </c>
-      <c r="T12" t="n">
-        <v>68</v>
-      </c>
-      <c r="U12" t="n">
-        <v>28</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -2463,52 +2102,40 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.453125</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="G13" t="n">
-        <v>0.453125</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>96</v>
+        <v>0.6534653465346535</v>
       </c>
       <c r="I13" t="n">
-        <v>125</v>
+        <v>0.6875</v>
       </c>
       <c r="J13" t="n">
-        <v>0.464</v>
+        <v>0.6700507614213197</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6041666666666666</v>
+        <v>0.6703296703296703</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5248868778280542</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="M13" t="n">
-        <v>96</v>
+        <v>0.6524064171122994</v>
       </c>
       <c r="N13" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4328358208955224</v>
+        <v>30</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3020833333333333</v>
+        <v>35</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3558282208588957</v>
-      </c>
-      <c r="R13" t="n">
-        <v>58</v>
-      </c>
-      <c r="S13" t="n">
-        <v>38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>67</v>
-      </c>
-      <c r="U13" t="n">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2530,52 +2157,40 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>0.7475728155339806</v>
       </c>
       <c r="I14" t="n">
-        <v>121</v>
+        <v>0.7064220183486238</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5371900826446281</v>
+        <v>0.7264150943396226</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.6404494382022472</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5652173913043478</v>
+        <v>0.6867469879518072</v>
       </c>
       <c r="M14" t="n">
-        <v>83</v>
+        <v>0.6627906976744186</v>
       </c>
       <c r="N14" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3802816901408451</v>
+        <v>32</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3253012048192771</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3506493506493507</v>
-      </c>
-      <c r="R14" t="n">
-        <v>65</v>
-      </c>
-      <c r="S14" t="n">
-        <v>44</v>
-      </c>
-      <c r="T14" t="n">
-        <v>56</v>
-      </c>
-      <c r="U14" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -2597,52 +2212,40 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>0.6173913043478261</v>
       </c>
       <c r="I15" t="n">
-        <v>118</v>
+        <v>0.7553191489361702</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4745762711864407</v>
+        <v>0.6794258373205742</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5957446808510638</v>
+        <v>0.7012987012987013</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5283018867924528</v>
+        <v>0.5510204081632653</v>
       </c>
       <c r="M15" t="n">
-        <v>98</v>
+        <v>0.6171428571428571</v>
       </c>
       <c r="N15" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4864864864864865</v>
+        <v>23</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3673469387755102</v>
+        <v>44</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4186046511627907</v>
-      </c>
-      <c r="R15" t="n">
-        <v>56</v>
-      </c>
-      <c r="S15" t="n">
-        <v>38</v>
-      </c>
-      <c r="T15" t="n">
-        <v>62</v>
-      </c>
-      <c r="U15" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -2664,52 +2267,40 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="I16" t="n">
-        <v>133</v>
+        <v>0.8111111111111111</v>
       </c>
       <c r="J16" t="n">
-        <v>0.481203007518797</v>
+        <v>0.756476683937824</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7111111111111111</v>
+        <v>0.8089887640449438</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5739910313901345</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="M16" t="n">
-        <v>102</v>
+        <v>0.7539267015706808</v>
       </c>
       <c r="N16" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="O16" t="n">
-        <v>0.559322033898305</v>
+        <v>17</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3235294117647059</v>
+        <v>30</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4099378881987578</v>
-      </c>
-      <c r="R16" t="n">
-        <v>64</v>
-      </c>
-      <c r="S16" t="n">
-        <v>26</v>
-      </c>
-      <c r="T16" t="n">
-        <v>69</v>
-      </c>
-      <c r="U16" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -2731,52 +2322,40 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="H17" t="n">
-        <v>81</v>
+        <v>0.4862385321100918</v>
       </c>
       <c r="I17" t="n">
-        <v>109</v>
+        <v>0.654320987654321</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4311926605504587</v>
+        <v>0.5578947368421053</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5802469135802469</v>
+        <v>0.6626506024096386</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4947368421052632</v>
+        <v>0.4954954954954955</v>
       </c>
       <c r="M17" t="n">
-        <v>111</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="N17" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5903614457831325</v>
+        <v>28</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4414414414414414</v>
+        <v>56</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5051546391752577</v>
-      </c>
-      <c r="R17" t="n">
-        <v>47</v>
-      </c>
-      <c r="S17" t="n">
-        <v>34</v>
-      </c>
-      <c r="T17" t="n">
-        <v>62</v>
-      </c>
-      <c r="U17" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -2798,52 +2377,40 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="H18" t="n">
-        <v>105</v>
+        <v>0.648936170212766</v>
       </c>
       <c r="I18" t="n">
-        <v>93</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5483870967741935</v>
+        <v>0.6130653266331658</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.5510204081632653</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5151515151515151</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="M18" t="n">
-        <v>87</v>
+        <v>0.5837837837837838</v>
       </c>
       <c r="N18" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4545454545454545</v>
+        <v>44</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5172413793103449</v>
+        <v>33</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4838709677419355</v>
-      </c>
-      <c r="R18" t="n">
-        <v>51</v>
-      </c>
-      <c r="S18" t="n">
         <v>54</v>
-      </c>
-      <c r="T18" t="n">
-        <v>42</v>
-      </c>
-      <c r="U18" t="n">
-        <v>45</v>
       </c>
     </row>
     <row r="19">
@@ -2865,52 +2432,40 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="I19" t="n">
-        <v>112</v>
+        <v>0.6185567010309279</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.6521739130434783</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5567010309278351</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5167464114832535</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="M19" t="n">
-        <v>95</v>
+        <v>0.68</v>
       </c>
       <c r="N19" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4625</v>
+        <v>37</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3894736842105263</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4228571428571429</v>
-      </c>
-      <c r="R19" t="n">
-        <v>54</v>
-      </c>
-      <c r="S19" t="n">
-        <v>43</v>
-      </c>
-      <c r="T19" t="n">
-        <v>58</v>
-      </c>
-      <c r="U19" t="n">
-        <v>37</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20">
@@ -2932,52 +2487,40 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H20" t="n">
-        <v>83</v>
+        <v>0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>137</v>
+        <v>0.8192771084337349</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4525547445255474</v>
+        <v>0.7431693989071038</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7469879518072289</v>
+        <v>0.8369565217391305</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5636363636363636</v>
+        <v>0.7064220183486238</v>
       </c>
       <c r="M20" t="n">
-        <v>109</v>
+        <v>0.7661691542288558</v>
       </c>
       <c r="N20" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6181818181818182</v>
+        <v>15</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3119266055045872</v>
+        <v>32</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4146341463414634</v>
-      </c>
-      <c r="R20" t="n">
-        <v>62</v>
-      </c>
-      <c r="S20" t="n">
-        <v>21</v>
-      </c>
-      <c r="T20" t="n">
-        <v>75</v>
-      </c>
-      <c r="U20" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21">
@@ -2999,52 +2542,40 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="H21" t="n">
-        <v>99</v>
+        <v>0.6756756756756757</v>
       </c>
       <c r="I21" t="n">
-        <v>136</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5147058823529411</v>
+        <v>0.7142857142857142</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7070707070707071</v>
+        <v>0.7037037037037037</v>
       </c>
       <c r="L21" t="n">
-        <v>0.5957446808510637</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="M21" t="n">
-        <v>93</v>
+        <v>0.6551724137931035</v>
       </c>
       <c r="N21" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4821428571428572</v>
+        <v>24</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2903225806451613</v>
+        <v>36</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3624161073825504</v>
-      </c>
-      <c r="R21" t="n">
-        <v>70</v>
-      </c>
-      <c r="S21" t="n">
-        <v>29</v>
-      </c>
-      <c r="T21" t="n">
-        <v>66</v>
-      </c>
-      <c r="U21" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="22">
@@ -3066,52 +2597,40 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="H22" t="n">
-        <v>81</v>
+        <v>0.63</v>
       </c>
       <c r="I22" t="n">
-        <v>133</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4586466165413534</v>
+        <v>0.6961325966850829</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7530864197530864</v>
+        <v>0.8043478260869565</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5700934579439252</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M22" t="n">
-        <v>111</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="N22" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6610169491525424</v>
+        <v>18</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3513513513513514</v>
+        <v>37</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4588235294117647</v>
-      </c>
-      <c r="R22" t="n">
-        <v>61</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
-      <c r="T22" t="n">
-        <v>72</v>
-      </c>
-      <c r="U22" t="n">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23">
@@ -3133,52 +2652,40 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="H23" t="n">
-        <v>84</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="I23" t="n">
-        <v>113</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4778761061946903</v>
+        <v>0.7017543859649122</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5482233502538072</v>
+        <v>0.75</v>
       </c>
       <c r="M23" t="n">
-        <v>108</v>
+        <v>0.7605633802816902</v>
       </c>
       <c r="N23" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O23" t="n">
-        <v>0.620253164556962</v>
+        <v>24</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537037037037037</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5240641711229946</v>
-      </c>
-      <c r="R23" t="n">
-        <v>54</v>
-      </c>
-      <c r="S23" t="n">
-        <v>30</v>
-      </c>
-      <c r="T23" t="n">
-        <v>59</v>
-      </c>
-      <c r="U23" t="n">
-        <v>49</v>
+        <v>81</v>
       </c>
     </row>
     <row r="24">
@@ -3200,52 +2707,40 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.484375</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="G24" t="n">
-        <v>0.484375</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>88</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I24" t="n">
-        <v>133</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4586466165413534</v>
+        <v>0.7526881720430106</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6931818181818182</v>
+        <v>0.8085106382978723</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5520361990950227</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M24" t="n">
-        <v>104</v>
+        <v>0.7676767676767676</v>
       </c>
       <c r="N24" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5423728813559322</v>
+        <v>18</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3076923076923077</v>
+        <v>28</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.392638036809816</v>
-      </c>
-      <c r="R24" t="n">
-        <v>61</v>
-      </c>
-      <c r="S24" t="n">
-        <v>27</v>
-      </c>
-      <c r="T24" t="n">
-        <v>72</v>
-      </c>
-      <c r="U24" t="n">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25">
@@ -3267,52 +2762,40 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.671875</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.671875</v>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="I25" t="n">
-        <v>119</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.704225352112676</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6363636363636364</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5779816513761468</v>
+        <v>0.5806451612903226</v>
       </c>
       <c r="M25" t="n">
-        <v>93</v>
+        <v>0.631578947368421</v>
       </c>
       <c r="N25" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5068493150684932</v>
+        <v>24</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3978494623655914</v>
+        <v>39</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4457831325301205</v>
-      </c>
-      <c r="R25" t="n">
-        <v>63</v>
-      </c>
-      <c r="S25" t="n">
-        <v>36</v>
-      </c>
-      <c r="T25" t="n">
-        <v>56</v>
-      </c>
-      <c r="U25" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26">
@@ -3334,52 +2817,40 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.71875</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4322916666666667</v>
+        <v>0.71875</v>
       </c>
       <c r="H26" t="n">
-        <v>87</v>
+        <v>0.6736842105263158</v>
       </c>
       <c r="I26" t="n">
-        <v>122</v>
+        <v>0.735632183908046</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4098360655737705</v>
+        <v>0.7032967032967034</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.7628865979381443</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4784688995215311</v>
+        <v>0.7047619047619048</v>
       </c>
       <c r="M26" t="n">
-        <v>105</v>
+        <v>0.7326732673267325</v>
       </c>
       <c r="N26" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="O26" t="n">
-        <v>0.4714285714285714</v>
+        <v>23</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3142857142857143</v>
+        <v>31</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.3771428571428572</v>
-      </c>
-      <c r="R26" t="n">
-        <v>50</v>
-      </c>
-      <c r="S26" t="n">
-        <v>37</v>
-      </c>
-      <c r="T26" t="n">
-        <v>72</v>
-      </c>
-      <c r="U26" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
@@ -3401,52 +2872,40 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.546875</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G27" t="n">
-        <v>0.546875</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H27" t="n">
-        <v>101</v>
+        <v>0.7019230769230769</v>
       </c>
       <c r="I27" t="n">
-        <v>110</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5636363636363636</v>
+        <v>0.7121951219512195</v>
       </c>
       <c r="K27" t="n">
-        <v>0.6138613861386139</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5876777251184834</v>
+        <v>0.6593406593406593</v>
       </c>
       <c r="M27" t="n">
-        <v>91</v>
+        <v>0.6703910614525139</v>
       </c>
       <c r="N27" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="O27" t="n">
-        <v>0.524390243902439</v>
+        <v>28</v>
       </c>
       <c r="P27" t="n">
-        <v>0.4725274725274725</v>
+        <v>31</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4971098265895953</v>
-      </c>
-      <c r="R27" t="n">
-        <v>62</v>
-      </c>
-      <c r="S27" t="n">
-        <v>39</v>
-      </c>
-      <c r="T27" t="n">
-        <v>48</v>
-      </c>
-      <c r="U27" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
@@ -3468,52 +2927,40 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.53125</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="G28" t="n">
-        <v>0.53125</v>
+        <v>0.7447916666666666</v>
       </c>
       <c r="H28" t="n">
-        <v>95</v>
+        <v>0.7254901960784313</v>
       </c>
       <c r="I28" t="n">
-        <v>131</v>
+        <v>0.7789473684210526</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5190839694656488</v>
+        <v>0.751269035532995</v>
       </c>
       <c r="K28" t="n">
-        <v>0.7157894736842105</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L28" t="n">
-        <v>0.6017699115044248</v>
+        <v>0.711340206185567</v>
       </c>
       <c r="M28" t="n">
-        <v>97</v>
+        <v>0.7379679144385027</v>
       </c>
       <c r="N28" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5573770491803278</v>
+        <v>21</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3505154639175257</v>
+        <v>28</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.430379746835443</v>
-      </c>
-      <c r="R28" t="n">
-        <v>68</v>
-      </c>
-      <c r="S28" t="n">
-        <v>27</v>
-      </c>
-      <c r="T28" t="n">
-        <v>63</v>
-      </c>
-      <c r="U28" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29">
@@ -3535,52 +2982,40 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G29" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H29" t="n">
-        <v>90</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="I29" t="n">
-        <v>127</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4645669291338583</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="K29" t="n">
-        <v>0.6555555555555556</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="L29" t="n">
-        <v>0.5437788018433179</v>
+        <v>0.6078431372549019</v>
       </c>
       <c r="M29" t="n">
-        <v>102</v>
+        <v>0.6595744680851063</v>
       </c>
       <c r="N29" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O29" t="n">
-        <v>0.5230769230769231</v>
+        <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3333333333333333</v>
+        <v>40</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4071856287425149</v>
-      </c>
-      <c r="R29" t="n">
-        <v>59</v>
-      </c>
-      <c r="S29" t="n">
-        <v>31</v>
-      </c>
-      <c r="T29" t="n">
-        <v>68</v>
-      </c>
-      <c r="U29" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
@@ -3602,52 +3037,40 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="H30" t="n">
-        <v>99</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="I30" t="n">
-        <v>114</v>
+        <v>0.6868686868686869</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5350877192982456</v>
+        <v>0.6903553299492386</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6161616161616161</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="L30" t="n">
-        <v>0.5727699530516432</v>
+        <v>0.6774193548387096</v>
       </c>
       <c r="M30" t="n">
-        <v>93</v>
+        <v>0.6737967914438502</v>
       </c>
       <c r="N30" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="O30" t="n">
-        <v>0.5128205128205128</v>
+        <v>31</v>
       </c>
       <c r="P30" t="n">
-        <v>0.4301075268817204</v>
+        <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4678362573099414</v>
-      </c>
-      <c r="R30" t="n">
-        <v>61</v>
-      </c>
-      <c r="S30" t="n">
-        <v>38</v>
-      </c>
-      <c r="T30" t="n">
-        <v>53</v>
-      </c>
-      <c r="U30" t="n">
-        <v>40</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
@@ -3669,52 +3092,40 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.46875</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G31" t="n">
-        <v>0.46875</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H31" t="n">
-        <v>92</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="I31" t="n">
-        <v>136</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4632352941176471</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6847826086956522</v>
+        <v>0.74</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.74</v>
       </c>
       <c r="M31" t="n">
-        <v>100</v>
+        <v>0.74</v>
       </c>
       <c r="N31" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4821428571428572</v>
+        <v>26</v>
       </c>
       <c r="P31" t="n">
-        <v>0.27</v>
+        <v>26</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="R31" t="n">
-        <v>63</v>
-      </c>
-      <c r="S31" t="n">
-        <v>29</v>
-      </c>
-      <c r="T31" t="n">
-        <v>73</v>
-      </c>
-      <c r="U31" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
@@ -3736,52 +3147,40 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="H32" t="n">
-        <v>89</v>
+        <v>0.6132075471698113</v>
       </c>
       <c r="I32" t="n">
-        <v>117</v>
+        <v>0.7303370786516854</v>
       </c>
       <c r="J32" t="n">
-        <v>0.452991452991453</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5955056179775281</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="L32" t="n">
-        <v>0.5145631067961165</v>
+        <v>0.6019417475728155</v>
       </c>
       <c r="M32" t="n">
-        <v>103</v>
+        <v>0.656084656084656</v>
       </c>
       <c r="N32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="O32" t="n">
-        <v>0.52</v>
+        <v>24</v>
       </c>
       <c r="P32" t="n">
-        <v>0.3786407766990291</v>
+        <v>41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.4382022471910112</v>
-      </c>
-      <c r="R32" t="n">
-        <v>53</v>
-      </c>
-      <c r="S32" t="n">
-        <v>36</v>
-      </c>
-      <c r="T32" t="n">
-        <v>64</v>
-      </c>
-      <c r="U32" t="n">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33">
@@ -3803,52 +3202,40 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H33" t="n">
-        <v>94</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="I33" t="n">
-        <v>140</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5285714285714286</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="K33" t="n">
-        <v>0.7872340425531915</v>
+        <v>0.7763157894736842</v>
       </c>
       <c r="L33" t="n">
-        <v>0.6324786324786325</v>
+        <v>0.6020408163265306</v>
       </c>
       <c r="M33" t="n">
-        <v>98</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="N33" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="O33" t="n">
-        <v>0.6153846153846154</v>
+        <v>17</v>
       </c>
       <c r="P33" t="n">
-        <v>0.3265306122448979</v>
+        <v>39</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4266666666666666</v>
-      </c>
-      <c r="R33" t="n">
-        <v>74</v>
-      </c>
-      <c r="S33" t="n">
-        <v>20</v>
-      </c>
-      <c r="T33" t="n">
-        <v>66</v>
-      </c>
-      <c r="U33" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -3870,52 +3257,40 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5677083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5677083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H34" t="n">
-        <v>93</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="I34" t="n">
-        <v>134</v>
+        <v>0.8172043010752689</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.7638190954773869</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7741935483870968</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="L34" t="n">
-        <v>0.6343612334801763</v>
+        <v>0.696969696969697</v>
       </c>
       <c r="M34" t="n">
-        <v>99</v>
+        <v>0.745945945945946</v>
       </c>
       <c r="N34" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="O34" t="n">
-        <v>0.6379310344827587</v>
+        <v>17</v>
       </c>
       <c r="P34" t="n">
-        <v>0.3737373737373738</v>
+        <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4713375796178345</v>
-      </c>
-      <c r="R34" t="n">
-        <v>72</v>
-      </c>
-      <c r="S34" t="n">
-        <v>21</v>
-      </c>
-      <c r="T34" t="n">
-        <v>62</v>
-      </c>
-      <c r="U34" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35">
@@ -3937,52 +3312,40 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.546875</v>
+        <v>0.671875</v>
       </c>
       <c r="G35" t="n">
-        <v>0.546875</v>
+        <v>0.671875</v>
       </c>
       <c r="H35" t="n">
-        <v>92</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="I35" t="n">
-        <v>119</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5210084033613446</v>
+        <v>0.676923076923077</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6739130434782609</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5876777251184835</v>
+        <v>0.63</v>
       </c>
       <c r="M35" t="n">
-        <v>100</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N35" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="O35" t="n">
-        <v>0.589041095890411</v>
+        <v>26</v>
       </c>
       <c r="P35" t="n">
-        <v>0.43</v>
+        <v>37</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.4971098265895953</v>
-      </c>
-      <c r="R35" t="n">
-        <v>62</v>
-      </c>
-      <c r="S35" t="n">
-        <v>30</v>
-      </c>
-      <c r="T35" t="n">
-        <v>57</v>
-      </c>
-      <c r="U35" t="n">
-        <v>43</v>
+        <v>63</v>
       </c>
     </row>
     <row r="36">
@@ -4004,52 +3367,40 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="G36" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="H36" t="n">
-        <v>84</v>
+        <v>0.6138613861386139</v>
       </c>
       <c r="I36" t="n">
-        <v>115</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4695652173913044</v>
+        <v>0.6702702702702702</v>
       </c>
       <c r="K36" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.7582417582417582</v>
       </c>
       <c r="L36" t="n">
-        <v>0.542713567839196</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="M36" t="n">
-        <v>108</v>
+        <v>0.6934673366834171</v>
       </c>
       <c r="N36" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6103896103896104</v>
+        <v>22</v>
       </c>
       <c r="P36" t="n">
-        <v>0.4351851851851852</v>
+        <v>39</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.508108108108108</v>
-      </c>
-      <c r="R36" t="n">
-        <v>54</v>
-      </c>
-      <c r="S36" t="n">
-        <v>30</v>
-      </c>
-      <c r="T36" t="n">
-        <v>61</v>
-      </c>
-      <c r="U36" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
@@ -4071,52 +3422,40 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.7135416666666666</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>0.7184466019417476</v>
       </c>
       <c r="I37" t="n">
-        <v>135</v>
+        <v>0.74</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4962962962962963</v>
+        <v>0.729064039408867</v>
       </c>
       <c r="K37" t="n">
-        <v>0.67</v>
+        <v>0.7078651685393258</v>
       </c>
       <c r="L37" t="n">
-        <v>0.5702127659574469</v>
+        <v>0.6847826086956522</v>
       </c>
       <c r="M37" t="n">
-        <v>92</v>
+        <v>0.6961325966850829</v>
       </c>
       <c r="N37" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="O37" t="n">
-        <v>0.4210526315789473</v>
+        <v>26</v>
       </c>
       <c r="P37" t="n">
-        <v>0.2608695652173913</v>
+        <v>29</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.3221476510067114</v>
-      </c>
-      <c r="R37" t="n">
-        <v>67</v>
-      </c>
-      <c r="S37" t="n">
-        <v>33</v>
-      </c>
-      <c r="T37" t="n">
-        <v>68</v>
-      </c>
-      <c r="U37" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
     </row>
     <row r="38">
@@ -4138,52 +3477,40 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6197916666666666</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6197916666666666</v>
       </c>
       <c r="H38" t="n">
-        <v>98</v>
+        <v>0.6288659793814433</v>
       </c>
       <c r="I38" t="n">
-        <v>105</v>
+        <v>0.6224489795918368</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4761904761904762</v>
+        <v>0.6256410256410256</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5102040816326531</v>
+        <v>0.6105263157894737</v>
       </c>
       <c r="L38" t="n">
-        <v>0.4926108374384236</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="M38" t="n">
-        <v>94</v>
+        <v>0.6137566137566138</v>
       </c>
       <c r="N38" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="O38" t="n">
-        <v>0.4482758620689655</v>
+        <v>37</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4148936170212766</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.430939226519337</v>
-      </c>
-      <c r="R38" t="n">
-        <v>50</v>
-      </c>
-      <c r="S38" t="n">
-        <v>48</v>
-      </c>
-      <c r="T38" t="n">
-        <v>55</v>
-      </c>
-      <c r="U38" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
@@ -4205,52 +3532,40 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.515625</v>
+        <v>0.71875</v>
       </c>
       <c r="G39" t="n">
-        <v>0.515625</v>
+        <v>0.71875</v>
       </c>
       <c r="H39" t="n">
-        <v>84</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="I39" t="n">
-        <v>119</v>
+        <v>0.7261904761904762</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4621848739495799</v>
+        <v>0.6931818181818181</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6547619047619048</v>
+        <v>0.77</v>
       </c>
       <c r="L39" t="n">
-        <v>0.541871921182266</v>
+        <v>0.7129629629629629</v>
       </c>
       <c r="M39" t="n">
-        <v>108</v>
+        <v>0.7403846153846153</v>
       </c>
       <c r="N39" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6027397260273972</v>
+        <v>23</v>
       </c>
       <c r="P39" t="n">
-        <v>0.4074074074074074</v>
+        <v>31</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.4861878453038674</v>
-      </c>
-      <c r="R39" t="n">
-        <v>55</v>
-      </c>
-      <c r="S39" t="n">
-        <v>29</v>
-      </c>
-      <c r="T39" t="n">
-        <v>64</v>
-      </c>
-      <c r="U39" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
@@ -4272,52 +3587,40 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.453125</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="G40" t="n">
-        <v>0.453125</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="H40" t="n">
-        <v>98</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="I40" t="n">
-        <v>127</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4724409448818898</v>
+        <v>0.66</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6122448979591837</v>
+        <v>0.6444444444444445</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.6170212765957447</v>
       </c>
       <c r="M40" t="n">
-        <v>94</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="N40" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O40" t="n">
-        <v>0.4153846153846154</v>
+        <v>32</v>
       </c>
       <c r="P40" t="n">
-        <v>0.2872340425531915</v>
+        <v>36</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.3396226415094341</v>
-      </c>
-      <c r="R40" t="n">
-        <v>60</v>
-      </c>
-      <c r="S40" t="n">
-        <v>38</v>
-      </c>
-      <c r="T40" t="n">
-        <v>67</v>
-      </c>
-      <c r="U40" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
@@ -4339,52 +3642,40 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6875</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6875</v>
       </c>
       <c r="H41" t="n">
-        <v>105</v>
+        <v>0.68</v>
       </c>
       <c r="I41" t="n">
-        <v>139</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5251798561151079</v>
+        <v>0.7391304347826089</v>
       </c>
       <c r="K41" t="n">
-        <v>0.6952380952380952</v>
+        <v>0.7014925373134329</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5983606557377048</v>
+        <v>0.5402298850574713</v>
       </c>
       <c r="M41" t="n">
-        <v>87</v>
+        <v>0.6103896103896104</v>
       </c>
       <c r="N41" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="O41" t="n">
-        <v>0.3962264150943396</v>
+        <v>20</v>
       </c>
       <c r="P41" t="n">
-        <v>0.2413793103448276</v>
+        <v>40</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R41" t="n">
-        <v>73</v>
-      </c>
-      <c r="S41" t="n">
-        <v>32</v>
-      </c>
-      <c r="T41" t="n">
-        <v>66</v>
-      </c>
-      <c r="U41" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
@@ -4406,52 +3697,40 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4479166666666667</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="H42" t="n">
-        <v>89</v>
+        <v>0.5576923076923077</v>
       </c>
       <c r="I42" t="n">
-        <v>113</v>
+        <v>0.651685393258427</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4247787610619469</v>
+        <v>0.6010362694300518</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5393258426966292</v>
+        <v>0.6477272727272727</v>
       </c>
       <c r="L42" t="n">
-        <v>0.4752475247524752</v>
+        <v>0.5533980582524272</v>
       </c>
       <c r="M42" t="n">
-        <v>103</v>
+        <v>0.5968586387434555</v>
       </c>
       <c r="N42" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="O42" t="n">
-        <v>0.4810126582278481</v>
+        <v>31</v>
       </c>
       <c r="P42" t="n">
-        <v>0.3689320388349515</v>
+        <v>46</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.4175824175824176</v>
-      </c>
-      <c r="R42" t="n">
-        <v>48</v>
-      </c>
-      <c r="S42" t="n">
-        <v>41</v>
-      </c>
-      <c r="T42" t="n">
-        <v>65</v>
-      </c>
-      <c r="U42" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -4473,52 +3752,40 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="G43" t="n">
-        <v>0.4270833333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="H43" t="n">
-        <v>98</v>
+        <v>0.6568627450980392</v>
       </c>
       <c r="I43" t="n">
-        <v>118</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="J43" t="n">
-        <v>0.4491525423728814</v>
+        <v>0.67</v>
       </c>
       <c r="K43" t="n">
-        <v>0.5408163265306123</v>
+        <v>0.6555555555555556</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4907407407407408</v>
+        <v>0.6276595744680851</v>
       </c>
       <c r="M43" t="n">
-        <v>94</v>
+        <v>0.6413043478260869</v>
       </c>
       <c r="N43" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O43" t="n">
-        <v>0.3918918918918919</v>
+        <v>31</v>
       </c>
       <c r="P43" t="n">
-        <v>0.3085106382978723</v>
+        <v>35</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.3452380952380952</v>
-      </c>
-      <c r="R43" t="n">
-        <v>53</v>
-      </c>
-      <c r="S43" t="n">
-        <v>45</v>
-      </c>
-      <c r="T43" t="n">
-        <v>65</v>
-      </c>
-      <c r="U43" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
@@ -4540,52 +3807,40 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.671875</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5729166666666666</v>
+        <v>0.671875</v>
       </c>
       <c r="H44" t="n">
-        <v>111</v>
+        <v>0.6967213114754098</v>
       </c>
       <c r="I44" t="n">
-        <v>123</v>
+        <v>0.7657657657657657</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6178861788617886</v>
+        <v>0.7296137339055793</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6846846846846847</v>
+        <v>0.6285714285714286</v>
       </c>
       <c r="L44" t="n">
-        <v>0.6495726495726496</v>
+        <v>0.5432098765432098</v>
       </c>
       <c r="M44" t="n">
-        <v>81</v>
+        <v>0.5827814569536424</v>
       </c>
       <c r="N44" t="n">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="O44" t="n">
-        <v>0.4927536231884058</v>
+        <v>26</v>
       </c>
       <c r="P44" t="n">
-        <v>0.4197530864197531</v>
+        <v>37</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.4533333333333333</v>
-      </c>
-      <c r="R44" t="n">
-        <v>76</v>
-      </c>
-      <c r="S44" t="n">
-        <v>35</v>
-      </c>
-      <c r="T44" t="n">
-        <v>47</v>
-      </c>
-      <c r="U44" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -4607,52 +3862,40 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H45" t="n">
-        <v>95</v>
+        <v>0.7448979591836735</v>
       </c>
       <c r="I45" t="n">
-        <v>136</v>
+        <v>0.7684210526315789</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5</v>
+        <v>0.7564766839378239</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7157894736842105</v>
+        <v>0.7659574468085106</v>
       </c>
       <c r="L45" t="n">
-        <v>0.5887445887445888</v>
+        <v>0.7422680412371134</v>
       </c>
       <c r="M45" t="n">
-        <v>97</v>
+        <v>0.7539267015706806</v>
       </c>
       <c r="N45" t="n">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="O45" t="n">
-        <v>0.5178571428571429</v>
+        <v>22</v>
       </c>
       <c r="P45" t="n">
-        <v>0.2989690721649484</v>
+        <v>25</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.3790849673202615</v>
-      </c>
-      <c r="R45" t="n">
-        <v>68</v>
-      </c>
-      <c r="S45" t="n">
-        <v>27</v>
-      </c>
-      <c r="T45" t="n">
-        <v>68</v>
-      </c>
-      <c r="U45" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
@@ -4674,52 +3917,40 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H46" t="n">
-        <v>102</v>
+        <v>0.6936936936936937</v>
       </c>
       <c r="I46" t="n">
-        <v>130</v>
+        <v>0.7549019607843137</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5153846153846153</v>
+        <v>0.7230046948356808</v>
       </c>
       <c r="K46" t="n">
-        <v>0.6568627450980392</v>
+        <v>0.691358024691358</v>
       </c>
       <c r="L46" t="n">
-        <v>0.5775862068965517</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="M46" t="n">
-        <v>90</v>
+        <v>0.6549707602339181</v>
       </c>
       <c r="N46" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O46" t="n">
-        <v>0.4354838709677419</v>
+        <v>25</v>
       </c>
       <c r="P46" t="n">
-        <v>0.3</v>
+        <v>34</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.3552631578947368</v>
-      </c>
-      <c r="R46" t="n">
-        <v>67</v>
-      </c>
-      <c r="S46" t="n">
-        <v>35</v>
-      </c>
-      <c r="T46" t="n">
-        <v>63</v>
-      </c>
-      <c r="U46" t="n">
-        <v>27</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -4741,52 +3972,40 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.65625</v>
       </c>
       <c r="H47" t="n">
-        <v>99</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I47" t="n">
-        <v>118</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="J47" t="n">
-        <v>0.4915254237288136</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5858585858585859</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="L47" t="n">
-        <v>0.5345622119815668</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="M47" t="n">
-        <v>93</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="N47" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="O47" t="n">
-        <v>0.4459459459459459</v>
+        <v>33</v>
       </c>
       <c r="P47" t="n">
-        <v>0.3548387096774194</v>
+        <v>33</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.3952095808383234</v>
-      </c>
-      <c r="R47" t="n">
-        <v>58</v>
-      </c>
-      <c r="S47" t="n">
-        <v>41</v>
-      </c>
-      <c r="T47" t="n">
         <v>60</v>
-      </c>
-      <c r="U47" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="48">
@@ -4808,52 +4027,40 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H48" t="n">
-        <v>93</v>
+        <v>0.6574074074074074</v>
       </c>
       <c r="I48" t="n">
-        <v>137</v>
+        <v>0.7634408602150538</v>
       </c>
       <c r="J48" t="n">
-        <v>0.4963503649635037</v>
+        <v>0.7064676616915422</v>
       </c>
       <c r="K48" t="n">
-        <v>0.7311827956989247</v>
+        <v>0.7380952380952381</v>
       </c>
       <c r="L48" t="n">
-        <v>0.5913043478260869</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="M48" t="n">
-        <v>99</v>
+        <v>0.6775956284153005</v>
       </c>
       <c r="N48" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="O48" t="n">
-        <v>0.5454545454545454</v>
+        <v>22</v>
       </c>
       <c r="P48" t="n">
-        <v>0.303030303030303</v>
+        <v>37</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.3896103896103897</v>
-      </c>
-      <c r="R48" t="n">
-        <v>68</v>
-      </c>
-      <c r="S48" t="n">
-        <v>25</v>
-      </c>
-      <c r="T48" t="n">
-        <v>69</v>
-      </c>
-      <c r="U48" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
@@ -4875,52 +4082,40 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.484375</v>
+        <v>0.734375</v>
       </c>
       <c r="G49" t="n">
-        <v>0.484375</v>
+        <v>0.734375</v>
       </c>
       <c r="H49" t="n">
-        <v>87</v>
+        <v>0.6698113207547169</v>
       </c>
       <c r="I49" t="n">
-        <v>126</v>
+        <v>0.8160919540229885</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.7357512953367875</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6551724137931034</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="L49" t="n">
-        <v>0.5352112676056338</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M49" t="n">
-        <v>105</v>
+        <v>0.7329842931937173</v>
       </c>
       <c r="N49" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="O49" t="n">
-        <v>0.5454545454545454</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>0.3428571428571429</v>
+        <v>35</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="R49" t="n">
-        <v>57</v>
-      </c>
-      <c r="S49" t="n">
-        <v>30</v>
-      </c>
-      <c r="T49" t="n">
-        <v>69</v>
-      </c>
-      <c r="U49" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="50">
@@ -4942,52 +4137,40 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6302083333333334</v>
       </c>
       <c r="G50" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.6302083333333334</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>0.6</v>
       </c>
       <c r="I50" t="n">
-        <v>112</v>
+        <v>0.5795454545454546</v>
       </c>
       <c r="J50" t="n">
-        <v>0.4553571428571428</v>
+        <v>0.5895953757225433</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5795454545454546</v>
+        <v>0.6542056074766355</v>
       </c>
       <c r="L50" t="n">
-        <v>0.51</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="M50" t="n">
-        <v>104</v>
+        <v>0.6635071090047393</v>
       </c>
       <c r="N50" t="n">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5375</v>
+        <v>37</v>
       </c>
       <c r="P50" t="n">
-        <v>0.4134615384615384</v>
+        <v>34</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.4673913043478261</v>
-      </c>
-      <c r="R50" t="n">
-        <v>51</v>
-      </c>
-      <c r="S50" t="n">
-        <v>37</v>
-      </c>
-      <c r="T50" t="n">
-        <v>61</v>
-      </c>
-      <c r="U50" t="n">
-        <v>43</v>
+        <v>70</v>
       </c>
     </row>
     <row r="51">
@@ -5009,52 +4192,40 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.53125</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G51" t="n">
-        <v>0.53125</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H51" t="n">
-        <v>88</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="I51" t="n">
-        <v>134</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="J51" t="n">
-        <v>0.4925373134328358</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>0.75</v>
+        <v>0.7954545454545454</v>
       </c>
       <c r="L51" t="n">
-        <v>0.5945945945945946</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="M51" t="n">
-        <v>104</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="N51" t="n">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="O51" t="n">
-        <v>0.6206896551724138</v>
+        <v>18</v>
       </c>
       <c r="P51" t="n">
-        <v>0.3461538461538461</v>
+        <v>34</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.4444444444444444</v>
-      </c>
-      <c r="R51" t="n">
-        <v>66</v>
-      </c>
-      <c r="S51" t="n">
-        <v>22</v>
-      </c>
-      <c r="T51" t="n">
-        <v>68</v>
-      </c>
-      <c r="U51" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
@@ -5076,52 +4247,40 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H52" t="n">
-        <v>93</v>
+        <v>0.74</v>
       </c>
       <c r="I52" t="n">
-        <v>139</v>
+        <v>0.7956989247311828</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5035971223021583</v>
+        <v>0.7668393782383419</v>
       </c>
       <c r="K52" t="n">
-        <v>0.7526881720430108</v>
+        <v>0.7934782608695652</v>
       </c>
       <c r="L52" t="n">
-        <v>0.603448275862069</v>
+        <v>0.7373737373737373</v>
       </c>
       <c r="M52" t="n">
-        <v>99</v>
+        <v>0.7643979057591622</v>
       </c>
       <c r="N52" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="O52" t="n">
-        <v>0.5660377358490566</v>
+        <v>19</v>
       </c>
       <c r="P52" t="n">
-        <v>0.303030303030303</v>
+        <v>26</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.3947368421052631</v>
-      </c>
-      <c r="R52" t="n">
-        <v>70</v>
-      </c>
-      <c r="S52" t="n">
-        <v>23</v>
-      </c>
-      <c r="T52" t="n">
-        <v>69</v>
-      </c>
-      <c r="U52" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
     </row>
     <row r="53">
@@ -5143,52 +4302,40 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6875</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6875</v>
       </c>
       <c r="H53" t="n">
-        <v>95</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="I53" t="n">
-        <v>128</v>
+        <v>0.7157894736842105</v>
       </c>
       <c r="J53" t="n">
-        <v>0.46875</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="K53" t="n">
-        <v>0.631578947368421</v>
+        <v>0.7032967032967034</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5381165919282511</v>
+        <v>0.6597938144329897</v>
       </c>
       <c r="M53" t="n">
-        <v>97</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="N53" t="n">
+        <v>68</v>
+      </c>
+      <c r="O53" t="n">
+        <v>27</v>
+      </c>
+      <c r="P53" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q53" t="n">
         <v>64</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0.453125</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0.2989690721649484</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.3602484472049689</v>
-      </c>
-      <c r="R53" t="n">
-        <v>60</v>
-      </c>
-      <c r="S53" t="n">
-        <v>35</v>
-      </c>
-      <c r="T53" t="n">
-        <v>68</v>
-      </c>
-      <c r="U53" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="54">
@@ -5210,52 +4357,40 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.46875</v>
+        <v>0.734375</v>
       </c>
       <c r="G54" t="n">
-        <v>0.46875</v>
+        <v>0.734375</v>
       </c>
       <c r="H54" t="n">
-        <v>99</v>
+        <v>0.74</v>
       </c>
       <c r="I54" t="n">
-        <v>125</v>
+        <v>0.7474747474747475</v>
       </c>
       <c r="J54" t="n">
-        <v>0.488</v>
+        <v>0.743718592964824</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6161616161616161</v>
+        <v>0.7282608695652174</v>
       </c>
       <c r="L54" t="n">
-        <v>0.5446428571428571</v>
+        <v>0.7204301075268817</v>
       </c>
       <c r="M54" t="n">
-        <v>93</v>
+        <v>0.7243243243243243</v>
       </c>
       <c r="N54" t="n">
+        <v>74</v>
+      </c>
+      <c r="O54" t="n">
+        <v>25</v>
+      </c>
+      <c r="P54" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q54" t="n">
         <v>67</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.4328358208955224</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.3118279569892473</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.3625</v>
-      </c>
-      <c r="R54" t="n">
-        <v>61</v>
-      </c>
-      <c r="S54" t="n">
-        <v>38</v>
-      </c>
-      <c r="T54" t="n">
-        <v>64</v>
-      </c>
-      <c r="U54" t="n">
-        <v>29</v>
       </c>
     </row>
     <row r="55">
@@ -5277,52 +4412,40 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.734375</v>
       </c>
       <c r="G55" t="n">
-        <v>0.4791666666666667</v>
+        <v>0.734375</v>
       </c>
       <c r="H55" t="n">
-        <v>90</v>
+        <v>0.693069306930693</v>
       </c>
       <c r="I55" t="n">
-        <v>124</v>
+        <v>0.7777777777777778</v>
       </c>
       <c r="J55" t="n">
-        <v>0.4596774193548387</v>
+        <v>0.7329842931937172</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.7802197802197802</v>
       </c>
       <c r="L55" t="n">
-        <v>0.5327102803738317</v>
+        <v>0.696078431372549</v>
       </c>
       <c r="M55" t="n">
-        <v>102</v>
+        <v>0.7357512953367875</v>
       </c>
       <c r="N55" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O55" t="n">
-        <v>0.5147058823529411</v>
+        <v>20</v>
       </c>
       <c r="P55" t="n">
-        <v>0.3431372549019608</v>
+        <v>31</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.4117647058823529</v>
-      </c>
-      <c r="R55" t="n">
-        <v>57</v>
-      </c>
-      <c r="S55" t="n">
-        <v>33</v>
-      </c>
-      <c r="T55" t="n">
-        <v>67</v>
-      </c>
-      <c r="U55" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56">
@@ -5344,52 +4467,40 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="G56" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.734375</v>
       </c>
       <c r="H56" t="n">
-        <v>94</v>
+        <v>0.7009345794392523</v>
       </c>
       <c r="I56" t="n">
-        <v>132</v>
+        <v>0.7978723404255319</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5075757575757576</v>
+        <v>0.7462686567164178</v>
       </c>
       <c r="K56" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7764705882352941</v>
       </c>
       <c r="L56" t="n">
-        <v>0.5929203539823009</v>
+        <v>0.673469387755102</v>
       </c>
       <c r="M56" t="n">
-        <v>98</v>
+        <v>0.7213114754098361</v>
       </c>
       <c r="N56" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="O56" t="n">
-        <v>0.55</v>
+        <v>19</v>
       </c>
       <c r="P56" t="n">
-        <v>0.336734693877551</v>
+        <v>32</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.4177215189873417</v>
-      </c>
-      <c r="R56" t="n">
-        <v>67</v>
-      </c>
-      <c r="S56" t="n">
-        <v>27</v>
-      </c>
-      <c r="T56" t="n">
-        <v>65</v>
-      </c>
-      <c r="U56" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
@@ -5411,52 +4522,40 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="H57" t="n">
-        <v>95</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="I57" t="n">
-        <v>120</v>
+        <v>0.6526315789473685</v>
       </c>
       <c r="J57" t="n">
-        <v>0.4666666666666667</v>
+        <v>0.6169154228855722</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5894736842105263</v>
+        <v>0.6162790697674418</v>
       </c>
       <c r="L57" t="n">
-        <v>0.5209302325581395</v>
+        <v>0.5463917525773195</v>
       </c>
       <c r="M57" t="n">
-        <v>97</v>
+        <v>0.5792349726775955</v>
       </c>
       <c r="N57" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="O57" t="n">
-        <v>0.4583333333333333</v>
+        <v>33</v>
       </c>
       <c r="P57" t="n">
-        <v>0.3402061855670103</v>
+        <v>44</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.3905325443786982</v>
-      </c>
-      <c r="R57" t="n">
-        <v>56</v>
-      </c>
-      <c r="S57" t="n">
-        <v>39</v>
-      </c>
-      <c r="T57" t="n">
-        <v>64</v>
-      </c>
-      <c r="U57" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58">
@@ -5478,52 +4577,40 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="G58" t="n">
-        <v>0.5</v>
+        <v>0.7760416666666666</v>
       </c>
       <c r="H58" t="n">
-        <v>91</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="I58" t="n">
-        <v>133</v>
+        <v>0.8351648351648352</v>
       </c>
       <c r="J58" t="n">
-        <v>0.481203007518797</v>
+        <v>0.7794871794871795</v>
       </c>
       <c r="K58" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.8295454545454546</v>
       </c>
       <c r="L58" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.7227722772277227</v>
       </c>
       <c r="M58" t="n">
-        <v>101</v>
+        <v>0.7724867724867726</v>
       </c>
       <c r="N58" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="O58" t="n">
-        <v>0.5423728813559322</v>
+        <v>15</v>
       </c>
       <c r="P58" t="n">
-        <v>0.3168316831683168</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.4000000000000001</v>
-      </c>
-      <c r="R58" t="n">
-        <v>64</v>
-      </c>
-      <c r="S58" t="n">
-        <v>27</v>
-      </c>
-      <c r="T58" t="n">
-        <v>69</v>
-      </c>
-      <c r="U58" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59">
@@ -5545,52 +4632,40 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.484375</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="G59" t="n">
-        <v>0.484375</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H59" t="n">
-        <v>88</v>
+        <v>0.6744186046511628</v>
       </c>
       <c r="I59" t="n">
-        <v>119</v>
+        <v>0.6590909090909091</v>
       </c>
       <c r="J59" t="n">
-        <v>0.453781512605042</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="K59" t="n">
-        <v>0.6136363636363636</v>
+        <v>0.7169811320754716</v>
       </c>
       <c r="L59" t="n">
-        <v>0.5217391304347826</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="M59" t="n">
-        <v>104</v>
+        <v>0.7238095238095238</v>
       </c>
       <c r="N59" t="n">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="O59" t="n">
-        <v>0.5342465753424658</v>
+        <v>30</v>
       </c>
       <c r="P59" t="n">
-        <v>0.375</v>
+        <v>28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.440677966101695</v>
-      </c>
-      <c r="R59" t="n">
-        <v>54</v>
-      </c>
-      <c r="S59" t="n">
-        <v>34</v>
-      </c>
-      <c r="T59" t="n">
-        <v>65</v>
-      </c>
-      <c r="U59" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60">
@@ -5612,52 +4687,40 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="H60" t="n">
-        <v>111</v>
+        <v>0.717948717948718</v>
       </c>
       <c r="I60" t="n">
-        <v>123</v>
+        <v>0.7567567567567568</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5609756097560976</v>
+        <v>0.736842105263158</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.64</v>
       </c>
       <c r="L60" t="n">
-        <v>0.5897435897435899</v>
+        <v>0.5925925925925926</v>
       </c>
       <c r="M60" t="n">
-        <v>81</v>
+        <v>0.6153846153846153</v>
       </c>
       <c r="N60" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="O60" t="n">
-        <v>0.391304347826087</v>
+        <v>27</v>
       </c>
       <c r="P60" t="n">
-        <v>0.3333333333333333</v>
+        <v>33</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="R60" t="n">
-        <v>69</v>
-      </c>
-      <c r="S60" t="n">
-        <v>42</v>
-      </c>
-      <c r="T60" t="n">
-        <v>54</v>
-      </c>
-      <c r="U60" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61">
@@ -5679,52 +4742,40 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H61" t="n">
-        <v>98</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="I61" t="n">
-        <v>118</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5254237288135594</v>
+        <v>0.6836734693877551</v>
       </c>
       <c r="K61" t="n">
-        <v>0.6326530612244898</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="L61" t="n">
-        <v>0.5740740740740742</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="M61" t="n">
-        <v>94</v>
+        <v>0.6702127659574468</v>
       </c>
       <c r="N61" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O61" t="n">
-        <v>0.5135135135135135</v>
+        <v>31</v>
       </c>
       <c r="P61" t="n">
-        <v>0.4042553191489361</v>
+        <v>31</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.4523809523809524</v>
-      </c>
-      <c r="R61" t="n">
-        <v>62</v>
-      </c>
-      <c r="S61" t="n">
-        <v>36</v>
-      </c>
-      <c r="T61" t="n">
-        <v>56</v>
-      </c>
-      <c r="U61" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62">
@@ -5746,52 +4797,40 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.453125</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="G62" t="n">
-        <v>0.453125</v>
+        <v>0.6354166666666666</v>
       </c>
       <c r="H62" t="n">
-        <v>106</v>
+        <v>0.65</v>
       </c>
       <c r="I62" t="n">
-        <v>121</v>
+        <v>0.7358490566037735</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5041322314049587</v>
+        <v>0.6902654867256638</v>
       </c>
       <c r="K62" t="n">
-        <v>0.5754716981132075</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="L62" t="n">
-        <v>0.5374449339207049</v>
+        <v>0.5116279069767442</v>
       </c>
       <c r="M62" t="n">
-        <v>86</v>
+        <v>0.5569620253164557</v>
       </c>
       <c r="N62" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O62" t="n">
-        <v>0.3661971830985916</v>
+        <v>28</v>
       </c>
       <c r="P62" t="n">
-        <v>0.3023255813953488</v>
+        <v>42</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.3312101910828025</v>
-      </c>
-      <c r="R62" t="n">
-        <v>61</v>
-      </c>
-      <c r="S62" t="n">
-        <v>45</v>
-      </c>
-      <c r="T62" t="n">
-        <v>60</v>
-      </c>
-      <c r="U62" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
@@ -5813,52 +4852,40 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G63" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H63" t="n">
-        <v>88</v>
+        <v>0.6181818181818182</v>
       </c>
       <c r="I63" t="n">
-        <v>122</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="J63" t="n">
-        <v>0.4344262295081967</v>
+        <v>0.6868686868686869</v>
       </c>
       <c r="K63" t="n">
-        <v>0.6022727272727273</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="L63" t="n">
-        <v>0.5047619047619047</v>
+        <v>0.5961538461538461</v>
       </c>
       <c r="M63" t="n">
-        <v>104</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="N63" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O63" t="n">
-        <v>0.5</v>
+        <v>20</v>
       </c>
       <c r="P63" t="n">
-        <v>0.3365384615384616</v>
+        <v>42</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.4022988505747127</v>
-      </c>
-      <c r="R63" t="n">
-        <v>53</v>
-      </c>
-      <c r="S63" t="n">
-        <v>35</v>
-      </c>
-      <c r="T63" t="n">
-        <v>69</v>
-      </c>
-      <c r="U63" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -5880,52 +4907,40 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H64" t="n">
-        <v>91</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="I64" t="n">
-        <v>132</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="J64" t="n">
-        <v>0.4848484848484849</v>
+        <v>0.6631578947368419</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7032967032967034</v>
+        <v>0.6989247311827957</v>
       </c>
       <c r="L64" t="n">
-        <v>0.5739910313901345</v>
+        <v>0.6435643564356436</v>
       </c>
       <c r="M64" t="n">
-        <v>101</v>
+        <v>0.6701030927835052</v>
       </c>
       <c r="N64" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="O64" t="n">
-        <v>0.55</v>
+        <v>28</v>
       </c>
       <c r="P64" t="n">
-        <v>0.3267326732673267</v>
+        <v>36</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.4099378881987578</v>
-      </c>
-      <c r="R64" t="n">
-        <v>64</v>
-      </c>
-      <c r="S64" t="n">
-        <v>27</v>
-      </c>
-      <c r="T64" t="n">
-        <v>68</v>
-      </c>
-      <c r="U64" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -5947,52 +4962,40 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.703125</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.703125</v>
       </c>
       <c r="H65" t="n">
-        <v>95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>126</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="J65" t="n">
-        <v>0.4682539682539683</v>
+        <v>0.7076923076923077</v>
       </c>
       <c r="K65" t="n">
-        <v>0.6210526315789474</v>
+        <v>0.7173913043478261</v>
       </c>
       <c r="L65" t="n">
-        <v>0.5339366515837105</v>
+        <v>0.6804123711340206</v>
       </c>
       <c r="M65" t="n">
-        <v>97</v>
+        <v>0.6984126984126985</v>
       </c>
       <c r="N65" t="n">
+        <v>69</v>
+      </c>
+      <c r="O65" t="n">
+        <v>26</v>
+      </c>
+      <c r="P65" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q65" t="n">
         <v>66</v>
-      </c>
-      <c r="O65" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="P65" t="n">
-        <v>0.3092783505154639</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>0.3680981595092024</v>
-      </c>
-      <c r="R65" t="n">
-        <v>59</v>
-      </c>
-      <c r="S65" t="n">
-        <v>36</v>
-      </c>
-      <c r="T65" t="n">
-        <v>67</v>
-      </c>
-      <c r="U65" t="n">
-        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -6014,52 +5017,40 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="G66" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="H66" t="n">
-        <v>83</v>
+        <v>0.59</v>
       </c>
       <c r="I66" t="n">
-        <v>118</v>
+        <v>0.7108433734939759</v>
       </c>
       <c r="J66" t="n">
-        <v>0.423728813559322</v>
+        <v>0.644808743169399</v>
       </c>
       <c r="K66" t="n">
-        <v>0.6024096385542169</v>
+        <v>0.7391304347826086</v>
       </c>
       <c r="L66" t="n">
-        <v>0.4975124378109452</v>
+        <v>0.6238532110091743</v>
       </c>
       <c r="M66" t="n">
-        <v>109</v>
+        <v>0.6766169154228856</v>
       </c>
       <c r="N66" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="O66" t="n">
-        <v>0.5540540540540541</v>
+        <v>24</v>
       </c>
       <c r="P66" t="n">
-        <v>0.3761467889908257</v>
+        <v>41</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.4480874316939891</v>
-      </c>
-      <c r="R66" t="n">
-        <v>50</v>
-      </c>
-      <c r="S66" t="n">
-        <v>33</v>
-      </c>
-      <c r="T66" t="n">
         <v>68</v>
-      </c>
-      <c r="U66" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="67">
@@ -6081,52 +5072,40 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H67" t="n">
-        <v>92</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="I67" t="n">
-        <v>123</v>
+        <v>0.75</v>
       </c>
       <c r="J67" t="n">
-        <v>0.4552845528455284</v>
+        <v>0.7113402061855669</v>
       </c>
       <c r="K67" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.7444444444444445</v>
       </c>
       <c r="L67" t="n">
-        <v>0.5209302325581395</v>
+        <v>0.67</v>
       </c>
       <c r="M67" t="n">
-        <v>100</v>
+        <v>0.7052631578947369</v>
       </c>
       <c r="N67" t="n">
         <v>69</v>
       </c>
       <c r="O67" t="n">
-        <v>0.4782608695652174</v>
+        <v>23</v>
       </c>
       <c r="P67" t="n">
-        <v>0.33</v>
+        <v>33</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.3905325443786983</v>
-      </c>
-      <c r="R67" t="n">
-        <v>56</v>
-      </c>
-      <c r="S67" t="n">
-        <v>36</v>
-      </c>
-      <c r="T67" t="n">
         <v>67</v>
-      </c>
-      <c r="U67" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="68">
@@ -6148,52 +5127,40 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.5</v>
+        <v>0.65625</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5</v>
+        <v>0.65625</v>
       </c>
       <c r="H68" t="n">
-        <v>98</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="I68" t="n">
-        <v>128</v>
+        <v>0.7346938775510204</v>
       </c>
       <c r="J68" t="n">
-        <v>0.5078125</v>
+        <v>0.6857142857142857</v>
       </c>
       <c r="K68" t="n">
-        <v>0.6632653061224489</v>
+        <v>0.675</v>
       </c>
       <c r="L68" t="n">
-        <v>0.5752212389380531</v>
+        <v>0.574468085106383</v>
       </c>
       <c r="M68" t="n">
-        <v>94</v>
+        <v>0.6206896551724138</v>
       </c>
       <c r="N68" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O68" t="n">
-        <v>0.484375</v>
+        <v>26</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3297872340425532</v>
+        <v>40</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.3924050632911392</v>
-      </c>
-      <c r="R68" t="n">
-        <v>65</v>
-      </c>
-      <c r="S68" t="n">
-        <v>33</v>
-      </c>
-      <c r="T68" t="n">
-        <v>63</v>
-      </c>
-      <c r="U68" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69">
@@ -6215,52 +5182,40 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.625</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4895833333333333</v>
+        <v>0.625</v>
       </c>
       <c r="H69" t="n">
-        <v>94</v>
+        <v>0.6018518518518519</v>
       </c>
       <c r="I69" t="n">
-        <v>110</v>
+        <v>0.6914893617021277</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4818181818181818</v>
+        <v>0.6435643564356436</v>
       </c>
       <c r="K69" t="n">
-        <v>0.5638297872340425</v>
+        <v>0.6547619047619048</v>
       </c>
       <c r="L69" t="n">
-        <v>0.5196078431372548</v>
+        <v>0.5612244897959183</v>
       </c>
       <c r="M69" t="n">
-        <v>98</v>
+        <v>0.6043956043956044</v>
       </c>
       <c r="N69" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="O69" t="n">
-        <v>0.5</v>
+        <v>29</v>
       </c>
       <c r="P69" t="n">
-        <v>0.4183673469387755</v>
+        <v>43</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.4555555555555555</v>
-      </c>
-      <c r="R69" t="n">
-        <v>53</v>
-      </c>
-      <c r="S69" t="n">
-        <v>41</v>
-      </c>
-      <c r="T69" t="n">
-        <v>57</v>
-      </c>
-      <c r="U69" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70">
@@ -6282,52 +5237,40 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.515625</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="G70" t="n">
-        <v>0.515625</v>
+        <v>0.6822916666666666</v>
       </c>
       <c r="H70" t="n">
-        <v>83</v>
+        <v>0.6078431372549019</v>
       </c>
       <c r="I70" t="n">
-        <v>128</v>
+        <v>0.7469879518072289</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4609375</v>
+        <v>0.6702702702702701</v>
       </c>
       <c r="K70" t="n">
-        <v>0.7108433734939759</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="L70" t="n">
-        <v>0.5592417061611374</v>
+        <v>0.6330275229357798</v>
       </c>
       <c r="M70" t="n">
-        <v>109</v>
+        <v>0.6934673366834171</v>
       </c>
       <c r="N70" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="O70" t="n">
-        <v>0.625</v>
+        <v>21</v>
       </c>
       <c r="P70" t="n">
-        <v>0.3669724770642202</v>
+        <v>40</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.4624277456647399</v>
-      </c>
-      <c r="R70" t="n">
-        <v>59</v>
-      </c>
-      <c r="S70" t="n">
-        <v>24</v>
-      </c>
-      <c r="T70" t="n">
         <v>69</v>
-      </c>
-      <c r="U70" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -6349,52 +5292,40 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G71" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H71" t="n">
-        <v>93</v>
+        <v>0.6407766990291263</v>
       </c>
       <c r="I71" t="n">
-        <v>130</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="J71" t="n">
-        <v>0.4769230769230769</v>
+        <v>0.6734693877551021</v>
       </c>
       <c r="K71" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6966292134831461</v>
       </c>
       <c r="L71" t="n">
-        <v>0.5560538116591929</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="M71" t="n">
-        <v>99</v>
+        <v>0.6595744680851064</v>
       </c>
       <c r="N71" t="n">
+        <v>66</v>
+      </c>
+      <c r="O71" t="n">
+        <v>27</v>
+      </c>
+      <c r="P71" t="n">
+        <v>37</v>
+      </c>
+      <c r="Q71" t="n">
         <v>62</v>
-      </c>
-      <c r="O71" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P71" t="n">
-        <v>0.3131313131313131</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>0.3850931677018634</v>
-      </c>
-      <c r="R71" t="n">
-        <v>62</v>
-      </c>
-      <c r="S71" t="n">
-        <v>31</v>
-      </c>
-      <c r="T71" t="n">
-        <v>68</v>
-      </c>
-      <c r="U71" t="n">
-        <v>31</v>
       </c>
     </row>
     <row r="72">
@@ -6416,52 +5347,40 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="H72" t="n">
-        <v>101</v>
+        <v>0.7473684210526316</v>
       </c>
       <c r="I72" t="n">
-        <v>119</v>
+        <v>0.7029702970297029</v>
       </c>
       <c r="J72" t="n">
-        <v>0.5378151260504201</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="K72" t="n">
-        <v>0.6336633663366337</v>
+        <v>0.6907216494845361</v>
       </c>
       <c r="L72" t="n">
-        <v>0.5818181818181819</v>
+        <v>0.7362637362637363</v>
       </c>
       <c r="M72" t="n">
-        <v>91</v>
+        <v>0.7127659574468086</v>
       </c>
       <c r="N72" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="O72" t="n">
-        <v>0.4931506849315068</v>
+        <v>30</v>
       </c>
       <c r="P72" t="n">
-        <v>0.3956043956043956</v>
+        <v>24</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.4390243902439024</v>
-      </c>
-      <c r="R72" t="n">
-        <v>64</v>
-      </c>
-      <c r="S72" t="n">
-        <v>37</v>
-      </c>
-      <c r="T72" t="n">
-        <v>55</v>
-      </c>
-      <c r="U72" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
     </row>
     <row r="73">
@@ -6483,52 +5402,40 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="G73" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="H73" t="n">
-        <v>105</v>
+        <v>0.5964912280701754</v>
       </c>
       <c r="I73" t="n">
-        <v>108</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="J73" t="n">
-        <v>0.5185185185185185</v>
+        <v>0.6210045662100456</v>
       </c>
       <c r="K73" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.5256410256410257</v>
       </c>
       <c r="L73" t="n">
-        <v>0.5258215962441314</v>
+        <v>0.4712643678160919</v>
       </c>
       <c r="M73" t="n">
-        <v>87</v>
+        <v>0.496969696969697</v>
       </c>
       <c r="N73" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="O73" t="n">
-        <v>0.4166666666666667</v>
+        <v>37</v>
       </c>
       <c r="P73" t="n">
-        <v>0.4022988505747127</v>
+        <v>46</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.4093567251461988</v>
-      </c>
-      <c r="R73" t="n">
-        <v>56</v>
-      </c>
-      <c r="S73" t="n">
-        <v>49</v>
-      </c>
-      <c r="T73" t="n">
-        <v>52</v>
-      </c>
-      <c r="U73" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="74">
@@ -6550,52 +5457,40 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="H74" t="n">
-        <v>84</v>
+        <v>0.5</v>
       </c>
       <c r="I74" t="n">
-        <v>124</v>
+        <v>0.6309523809523809</v>
       </c>
       <c r="J74" t="n">
-        <v>0.4193548387096774</v>
+        <v>0.5578947368421052</v>
       </c>
       <c r="K74" t="n">
-        <v>0.6190476190476191</v>
+        <v>0.6395348837209303</v>
       </c>
       <c r="L74" t="n">
-        <v>0.5</v>
+        <v>0.5092592592592593</v>
       </c>
       <c r="M74" t="n">
-        <v>108</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="N74" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="O74" t="n">
-        <v>0.5294117647058824</v>
+        <v>31</v>
       </c>
       <c r="P74" t="n">
-        <v>0.3333333333333333</v>
+        <v>53</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.409090909090909</v>
-      </c>
-      <c r="R74" t="n">
-        <v>52</v>
-      </c>
-      <c r="S74" t="n">
-        <v>32</v>
-      </c>
-      <c r="T74" t="n">
-        <v>72</v>
-      </c>
-      <c r="U74" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75">
@@ -6617,52 +5512,40 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.5989583333333334</v>
       </c>
       <c r="H75" t="n">
-        <v>99</v>
+        <v>0.6122448979591837</v>
       </c>
       <c r="I75" t="n">
-        <v>102</v>
+        <v>0.6060606060606061</v>
       </c>
       <c r="J75" t="n">
-        <v>0.4901960784313725</v>
+        <v>0.6091370558375634</v>
       </c>
       <c r="K75" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.5851063829787234</v>
       </c>
       <c r="L75" t="n">
-        <v>0.4975124378109453</v>
+        <v>0.5913978494623656</v>
       </c>
       <c r="M75" t="n">
-        <v>93</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="N75" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="O75" t="n">
-        <v>0.4555555555555555</v>
+        <v>39</v>
       </c>
       <c r="P75" t="n">
-        <v>0.4408602150537634</v>
+        <v>38</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.4480874316939891</v>
-      </c>
-      <c r="R75" t="n">
-        <v>50</v>
-      </c>
-      <c r="S75" t="n">
-        <v>49</v>
-      </c>
-      <c r="T75" t="n">
-        <v>52</v>
-      </c>
-      <c r="U75" t="n">
-        <v>41</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76">
@@ -6684,52 +5567,40 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H76" t="n">
-        <v>99</v>
+        <v>0.75</v>
       </c>
       <c r="I76" t="n">
-        <v>140</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.7826086956521738</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="L76" t="n">
-        <v>0.6276150627615062</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="M76" t="n">
-        <v>93</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="N76" t="n">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="O76" t="n">
-        <v>0.5384615384615384</v>
+        <v>18</v>
       </c>
       <c r="P76" t="n">
-        <v>0.3010752688172043</v>
+        <v>27</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.3862068965517241</v>
-      </c>
-      <c r="R76" t="n">
-        <v>75</v>
-      </c>
-      <c r="S76" t="n">
-        <v>24</v>
-      </c>
-      <c r="T76" t="n">
-        <v>65</v>
-      </c>
-      <c r="U76" t="n">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="77">
@@ -6751,52 +5622,40 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.703125</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.703125</v>
       </c>
       <c r="H77" t="n">
-        <v>97</v>
+        <v>0.6886792452830188</v>
       </c>
       <c r="I77" t="n">
-        <v>120</v>
+        <v>0.7525773195876289</v>
       </c>
       <c r="J77" t="n">
-        <v>0.5</v>
+        <v>0.7192118226600984</v>
       </c>
       <c r="K77" t="n">
-        <v>0.6185567010309279</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="L77" t="n">
-        <v>0.5529953917050692</v>
+        <v>0.6526315789473685</v>
       </c>
       <c r="M77" t="n">
-        <v>95</v>
+        <v>0.6850828729281767</v>
       </c>
       <c r="N77" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O77" t="n">
-        <v>0.4861111111111111</v>
+        <v>24</v>
       </c>
       <c r="P77" t="n">
-        <v>0.3684210526315789</v>
+        <v>33</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.4191616766467066</v>
-      </c>
-      <c r="R77" t="n">
-        <v>60</v>
-      </c>
-      <c r="S77" t="n">
-        <v>37</v>
-      </c>
-      <c r="T77" t="n">
-        <v>60</v>
-      </c>
-      <c r="U77" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="78">
@@ -6818,52 +5677,40 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.609375</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="G78" t="n">
-        <v>0.609375</v>
+        <v>0.7552083333333334</v>
       </c>
       <c r="H78" t="n">
-        <v>111</v>
+        <v>0.7711864406779662</v>
       </c>
       <c r="I78" t="n">
-        <v>128</v>
+        <v>0.8198198198198198</v>
       </c>
       <c r="J78" t="n">
-        <v>0.640625</v>
+        <v>0.7947598253275109</v>
       </c>
       <c r="K78" t="n">
-        <v>0.7387387387387387</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="L78" t="n">
-        <v>0.6861924686192469</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M78" t="n">
-        <v>81</v>
+        <v>0.6967741935483871</v>
       </c>
       <c r="N78" t="n">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="O78" t="n">
-        <v>0.546875</v>
+        <v>20</v>
       </c>
       <c r="P78" t="n">
-        <v>0.4320987654320987</v>
+        <v>27</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.4827586206896552</v>
-      </c>
-      <c r="R78" t="n">
-        <v>82</v>
-      </c>
-      <c r="S78" t="n">
-        <v>29</v>
-      </c>
-      <c r="T78" t="n">
-        <v>46</v>
-      </c>
-      <c r="U78" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79">
@@ -6885,52 +5732,40 @@
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.53125</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="G79" t="n">
-        <v>0.53125</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="H79" t="n">
-        <v>94</v>
+        <v>0.6637931034482759</v>
       </c>
       <c r="I79" t="n">
-        <v>130</v>
+        <v>0.8191489361702128</v>
       </c>
       <c r="J79" t="n">
-        <v>0.5153846153846153</v>
+        <v>0.7333333333333334</v>
       </c>
       <c r="K79" t="n">
-        <v>0.7127659574468085</v>
+        <v>0.7763157894736842</v>
       </c>
       <c r="L79" t="n">
-        <v>0.5982142857142856</v>
+        <v>0.6020408163265306</v>
       </c>
       <c r="M79" t="n">
-        <v>98</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="N79" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="O79" t="n">
-        <v>0.5645161290322581</v>
+        <v>17</v>
       </c>
       <c r="P79" t="n">
-        <v>0.3571428571428572</v>
+        <v>39</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.4375000000000001</v>
-      </c>
-      <c r="R79" t="n">
-        <v>67</v>
-      </c>
-      <c r="S79" t="n">
-        <v>27</v>
-      </c>
-      <c r="T79" t="n">
-        <v>63</v>
-      </c>
-      <c r="U79" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
@@ -6952,52 +5787,40 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.53125</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G80" t="n">
-        <v>0.53125</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H80" t="n">
-        <v>87</v>
+        <v>0.6262626262626263</v>
       </c>
       <c r="I80" t="n">
-        <v>113</v>
+        <v>0.7126436781609196</v>
       </c>
       <c r="J80" t="n">
-        <v>0.4867256637168141</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="K80" t="n">
-        <v>0.632183908045977</v>
+        <v>0.7311827956989247</v>
       </c>
       <c r="L80" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.6476190476190476</v>
       </c>
       <c r="M80" t="n">
-        <v>105</v>
+        <v>0.6868686868686869</v>
       </c>
       <c r="N80" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="O80" t="n">
-        <v>0.5949367088607594</v>
+        <v>25</v>
       </c>
       <c r="P80" t="n">
-        <v>0.4476190476190476</v>
+        <v>37</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.5108695652173914</v>
-      </c>
-      <c r="R80" t="n">
-        <v>55</v>
-      </c>
-      <c r="S80" t="n">
-        <v>32</v>
-      </c>
-      <c r="T80" t="n">
-        <v>58</v>
-      </c>
-      <c r="U80" t="n">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81">
@@ -7019,52 +5842,40 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G81" t="n">
-        <v>0.5104166666666666</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H81" t="n">
-        <v>92</v>
+        <v>0.6486486486486487</v>
       </c>
       <c r="I81" t="n">
-        <v>128</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="J81" t="n">
-        <v>0.4921875</v>
+        <v>0.7093596059113302</v>
       </c>
       <c r="K81" t="n">
-        <v>0.6847826086956522</v>
+        <v>0.7530864197530864</v>
       </c>
       <c r="L81" t="n">
-        <v>0.5727272727272728</v>
+        <v>0.61</v>
       </c>
       <c r="M81" t="n">
-        <v>100</v>
+        <v>0.6740331491712707</v>
       </c>
       <c r="N81" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O81" t="n">
-        <v>0.546875</v>
+        <v>20</v>
       </c>
       <c r="P81" t="n">
-        <v>0.35</v>
+        <v>39</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.4268292682926829</v>
-      </c>
-      <c r="R81" t="n">
-        <v>63</v>
-      </c>
-      <c r="S81" t="n">
-        <v>29</v>
-      </c>
-      <c r="T81" t="n">
-        <v>65</v>
-      </c>
-      <c r="U81" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82">
@@ -7086,52 +5897,40 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.5677083333333334</v>
       </c>
       <c r="H82" t="n">
-        <v>84</v>
+        <v>0.504950495049505</v>
       </c>
       <c r="I82" t="n">
-        <v>113</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="J82" t="n">
-        <v>0.415929203539823</v>
+        <v>0.5513513513513513</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5595238095238095</v>
+        <v>0.6373626373626373</v>
       </c>
       <c r="L82" t="n">
-        <v>0.4771573604060914</v>
+        <v>0.5370370370370371</v>
       </c>
       <c r="M82" t="n">
-        <v>108</v>
+        <v>0.5829145728643216</v>
       </c>
       <c r="N82" t="n">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="O82" t="n">
-        <v>0.5316455696202531</v>
+        <v>33</v>
       </c>
       <c r="P82" t="n">
-        <v>0.3888888888888889</v>
+        <v>50</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.4491978609625669</v>
-      </c>
-      <c r="R82" t="n">
-        <v>47</v>
-      </c>
-      <c r="S82" t="n">
-        <v>37</v>
-      </c>
-      <c r="T82" t="n">
-        <v>66</v>
-      </c>
-      <c r="U82" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83">
@@ -7153,52 +5952,40 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="H83" t="n">
-        <v>94</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="I83" t="n">
-        <v>111</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="J83" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.6881720430107526</v>
       </c>
       <c r="K83" t="n">
-        <v>0.5425531914893617</v>
+        <v>0.7</v>
       </c>
       <c r="L83" t="n">
-        <v>0.4975609756097561</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M83" t="n">
-        <v>98</v>
+        <v>0.7070707070707072</v>
       </c>
       <c r="N83" t="n">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="O83" t="n">
-        <v>0.4691358024691358</v>
+        <v>30</v>
       </c>
       <c r="P83" t="n">
-        <v>0.3877551020408163</v>
+        <v>28</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.4245810055865922</v>
-      </c>
-      <c r="R83" t="n">
-        <v>51</v>
-      </c>
-      <c r="S83" t="n">
-        <v>43</v>
-      </c>
-      <c r="T83" t="n">
-        <v>60</v>
-      </c>
-      <c r="U83" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="84">
@@ -7220,52 +6007,40 @@
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H84" t="n">
-        <v>103</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="I84" t="n">
-        <v>127</v>
+        <v>0.7864077669902912</v>
       </c>
       <c r="J84" t="n">
-        <v>0.5590551181102362</v>
+        <v>0.7570093457943925</v>
       </c>
       <c r="K84" t="n">
-        <v>0.6893203883495146</v>
+        <v>0.7283950617283951</v>
       </c>
       <c r="L84" t="n">
-        <v>0.6173913043478261</v>
+        <v>0.6629213483146067</v>
       </c>
       <c r="M84" t="n">
-        <v>89</v>
+        <v>0.6941176470588235</v>
       </c>
       <c r="N84" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="O84" t="n">
-        <v>0.5076923076923077</v>
+        <v>22</v>
       </c>
       <c r="P84" t="n">
-        <v>0.3707865168539326</v>
+        <v>30</v>
       </c>
       <c r="Q84" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="R84" t="n">
-        <v>71</v>
-      </c>
-      <c r="S84" t="n">
-        <v>32</v>
-      </c>
-      <c r="T84" t="n">
-        <v>56</v>
-      </c>
-      <c r="U84" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85">
@@ -7287,52 +6062,40 @@
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G85" t="n">
-        <v>0.484375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H85" t="n">
-        <v>107</v>
+        <v>0.6902654867256637</v>
       </c>
       <c r="I85" t="n">
-        <v>136</v>
+        <v>0.7289719626168224</v>
       </c>
       <c r="J85" t="n">
-        <v>0.5294117647058824</v>
+        <v>0.709090909090909</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.6329113924050633</v>
       </c>
       <c r="L85" t="n">
-        <v>0.5925925925925926</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="M85" t="n">
-        <v>85</v>
+        <v>0.6097560975609757</v>
       </c>
       <c r="N85" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="O85" t="n">
-        <v>0.375</v>
+        <v>29</v>
       </c>
       <c r="P85" t="n">
-        <v>0.2470588235294118</v>
+        <v>35</v>
       </c>
       <c r="Q85" t="n">
-        <v>0.2978723404255319</v>
-      </c>
-      <c r="R85" t="n">
-        <v>72</v>
-      </c>
-      <c r="S85" t="n">
-        <v>35</v>
-      </c>
-      <c r="T85" t="n">
-        <v>64</v>
-      </c>
-      <c r="U85" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
@@ -7354,52 +6117,40 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.453125</v>
+        <v>0.796875</v>
       </c>
       <c r="G86" t="n">
-        <v>0.453125</v>
+        <v>0.796875</v>
       </c>
       <c r="H86" t="n">
-        <v>101</v>
+        <v>0.8297872340425532</v>
       </c>
       <c r="I86" t="n">
-        <v>130</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4846153846153846</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="K86" t="n">
-        <v>0.6237623762376238</v>
+        <v>0.7653061224489796</v>
       </c>
       <c r="L86" t="n">
-        <v>0.5454545454545455</v>
+        <v>0.8241758241758241</v>
       </c>
       <c r="M86" t="n">
-        <v>91</v>
+        <v>0.7936507936507936</v>
       </c>
       <c r="N86" t="n">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="O86" t="n">
-        <v>0.3870967741935484</v>
+        <v>23</v>
       </c>
       <c r="P86" t="n">
-        <v>0.2637362637362637</v>
+        <v>16</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.3137254901960784</v>
-      </c>
-      <c r="R86" t="n">
-        <v>63</v>
-      </c>
-      <c r="S86" t="n">
-        <v>38</v>
-      </c>
-      <c r="T86" t="n">
-        <v>67</v>
-      </c>
-      <c r="U86" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
@@ -7421,52 +6172,40 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="G87" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.6614583333333334</v>
       </c>
       <c r="H87" t="n">
-        <v>97</v>
+        <v>0.66</v>
       </c>
       <c r="I87" t="n">
-        <v>112</v>
+        <v>0.6804123711340206</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4821428571428572</v>
+        <v>0.6700507614213199</v>
       </c>
       <c r="K87" t="n">
-        <v>0.5567010309278351</v>
+        <v>0.6630434782608695</v>
       </c>
       <c r="L87" t="n">
-        <v>0.5167464114832535</v>
+        <v>0.6421052631578947</v>
       </c>
       <c r="M87" t="n">
-        <v>95</v>
+        <v>0.6524064171122995</v>
       </c>
       <c r="N87" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="O87" t="n">
-        <v>0.4625</v>
+        <v>31</v>
       </c>
       <c r="P87" t="n">
-        <v>0.3894736842105263</v>
+        <v>34</v>
       </c>
       <c r="Q87" t="n">
-        <v>0.4228571428571429</v>
-      </c>
-      <c r="R87" t="n">
-        <v>54</v>
-      </c>
-      <c r="S87" t="n">
-        <v>43</v>
-      </c>
-      <c r="T87" t="n">
-        <v>58</v>
-      </c>
-      <c r="U87" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88">
@@ -7488,52 +6227,40 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.53125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G88" t="n">
-        <v>0.53125</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H88" t="n">
-        <v>101</v>
+        <v>0.6947368421052632</v>
       </c>
       <c r="I88" t="n">
-        <v>109</v>
+        <v>0.6534653465346535</v>
       </c>
       <c r="J88" t="n">
-        <v>0.5504587155963303</v>
+        <v>0.6734693877551021</v>
       </c>
       <c r="K88" t="n">
-        <v>0.594059405940594</v>
+        <v>0.6391752577319587</v>
       </c>
       <c r="L88" t="n">
-        <v>0.5714285714285715</v>
+        <v>0.6813186813186813</v>
       </c>
       <c r="M88" t="n">
-        <v>91</v>
+        <v>0.6595744680851064</v>
       </c>
       <c r="N88" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="O88" t="n">
-        <v>0.5060240963855421</v>
+        <v>35</v>
       </c>
       <c r="P88" t="n">
-        <v>0.4615384615384616</v>
+        <v>29</v>
       </c>
       <c r="Q88" t="n">
-        <v>0.4827586206896552</v>
-      </c>
-      <c r="R88" t="n">
-        <v>60</v>
-      </c>
-      <c r="S88" t="n">
-        <v>41</v>
-      </c>
-      <c r="T88" t="n">
-        <v>49</v>
-      </c>
-      <c r="U88" t="n">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89">
@@ -7555,52 +6282,40 @@
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5260416666666666</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="H89" t="n">
-        <v>103</v>
+        <v>0.6764705882352942</v>
       </c>
       <c r="I89" t="n">
-        <v>120</v>
+        <v>0.6699029126213593</v>
       </c>
       <c r="J89" t="n">
-        <v>0.55</v>
+        <v>0.6731707317073171</v>
       </c>
       <c r="K89" t="n">
-        <v>0.6407766990291263</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="L89" t="n">
-        <v>0.5919282511210763</v>
+        <v>0.6292134831460674</v>
       </c>
       <c r="M89" t="n">
-        <v>89</v>
+        <v>0.6256983240223464</v>
       </c>
       <c r="N89" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="O89" t="n">
-        <v>0.4861111111111111</v>
+        <v>34</v>
       </c>
       <c r="P89" t="n">
-        <v>0.3932584269662922</v>
+        <v>33</v>
       </c>
       <c r="Q89" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="R89" t="n">
-        <v>66</v>
-      </c>
-      <c r="S89" t="n">
-        <v>37</v>
-      </c>
-      <c r="T89" t="n">
-        <v>54</v>
-      </c>
-      <c r="U89" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90">
@@ -7622,52 +6337,40 @@
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H90" t="n">
-        <v>100</v>
+        <v>0.6880733944954128</v>
       </c>
       <c r="I90" t="n">
-        <v>127</v>
+        <v>0.75</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4881889763779528</v>
+        <v>0.7177033492822965</v>
       </c>
       <c r="K90" t="n">
-        <v>0.62</v>
+        <v>0.6987951807228916</v>
       </c>
       <c r="L90" t="n">
-        <v>0.5462555066079294</v>
+        <v>0.6304347826086957</v>
       </c>
       <c r="M90" t="n">
-        <v>92</v>
+        <v>0.6628571428571429</v>
       </c>
       <c r="N90" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="O90" t="n">
-        <v>0.4153846153846154</v>
+        <v>25</v>
       </c>
       <c r="P90" t="n">
-        <v>0.2934782608695652</v>
+        <v>34</v>
       </c>
       <c r="Q90" t="n">
-        <v>0.3439490445859873</v>
-      </c>
-      <c r="R90" t="n">
-        <v>62</v>
-      </c>
-      <c r="S90" t="n">
-        <v>38</v>
-      </c>
-      <c r="T90" t="n">
-        <v>65</v>
-      </c>
-      <c r="U90" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91">
@@ -7689,52 +6392,40 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="H91" t="n">
-        <v>105</v>
+        <v>0.7565217391304347</v>
       </c>
       <c r="I91" t="n">
-        <v>123</v>
+        <v>0.8285714285714286</v>
       </c>
       <c r="J91" t="n">
-        <v>0.5772357723577236</v>
+        <v>0.7909090909090909</v>
       </c>
       <c r="K91" t="n">
-        <v>0.6761904761904762</v>
+        <v>0.7662337662337663</v>
       </c>
       <c r="L91" t="n">
-        <v>0.6228070175438597</v>
+        <v>0.6781609195402298</v>
       </c>
       <c r="M91" t="n">
+        <v>0.7195121951219511</v>
+      </c>
+      <c r="N91" t="n">
         <v>87</v>
       </c>
-      <c r="N91" t="n">
-        <v>69</v>
-      </c>
       <c r="O91" t="n">
-        <v>0.5072463768115942</v>
+        <v>18</v>
       </c>
       <c r="P91" t="n">
-        <v>0.4022988505747127</v>
+        <v>28</v>
       </c>
       <c r="Q91" t="n">
-        <v>0.4487179487179487</v>
-      </c>
-      <c r="R91" t="n">
-        <v>71</v>
-      </c>
-      <c r="S91" t="n">
-        <v>34</v>
-      </c>
-      <c r="T91" t="n">
-        <v>52</v>
-      </c>
-      <c r="U91" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
@@ -7756,52 +6447,40 @@
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.671875</v>
       </c>
       <c r="G92" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.671875</v>
       </c>
       <c r="H92" t="n">
-        <v>106</v>
+        <v>0.6869565217391305</v>
       </c>
       <c r="I92" t="n">
-        <v>112</v>
+        <v>0.7452830188679245</v>
       </c>
       <c r="J92" t="n">
-        <v>0.5625</v>
+        <v>0.7149321266968325</v>
       </c>
       <c r="K92" t="n">
-        <v>0.5943396226415094</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="L92" t="n">
-        <v>0.5779816513761468</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="M92" t="n">
-        <v>86</v>
+        <v>0.6134969325153374</v>
       </c>
       <c r="N92" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O92" t="n">
-        <v>0.4625</v>
+        <v>27</v>
       </c>
       <c r="P92" t="n">
-        <v>0.4302325581395349</v>
+        <v>36</v>
       </c>
       <c r="Q92" t="n">
-        <v>0.4457831325301205</v>
-      </c>
-      <c r="R92" t="n">
-        <v>63</v>
-      </c>
-      <c r="S92" t="n">
-        <v>43</v>
-      </c>
-      <c r="T92" t="n">
-        <v>49</v>
-      </c>
-      <c r="U92" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93">
@@ -7823,52 +6502,40 @@
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="G93" t="n">
-        <v>0.4947916666666667</v>
+        <v>0.6510416666666666</v>
       </c>
       <c r="H93" t="n">
-        <v>103</v>
+        <v>0.6730769230769231</v>
       </c>
       <c r="I93" t="n">
-        <v>124</v>
+        <v>0.6796116504854369</v>
       </c>
       <c r="J93" t="n">
-        <v>0.5241935483870968</v>
+        <v>0.6763285024154591</v>
       </c>
       <c r="K93" t="n">
-        <v>0.6310679611650486</v>
+        <v>0.625</v>
       </c>
       <c r="L93" t="n">
-        <v>0.5726872246696035</v>
+        <v>0.6179775280898876</v>
       </c>
       <c r="M93" t="n">
-        <v>89</v>
+        <v>0.6214689265536723</v>
       </c>
       <c r="N93" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O93" t="n">
-        <v>0.4411764705882353</v>
+        <v>33</v>
       </c>
       <c r="P93" t="n">
-        <v>0.3370786516853932</v>
+        <v>34</v>
       </c>
       <c r="Q93" t="n">
-        <v>0.3821656050955414</v>
-      </c>
-      <c r="R93" t="n">
-        <v>65</v>
-      </c>
-      <c r="S93" t="n">
-        <v>38</v>
-      </c>
-      <c r="T93" t="n">
-        <v>59</v>
-      </c>
-      <c r="U93" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
     </row>
     <row r="94">
@@ -7890,52 +6557,40 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="G94" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.765625</v>
       </c>
       <c r="H94" t="n">
-        <v>104</v>
+        <v>0.7864077669902912</v>
       </c>
       <c r="I94" t="n">
-        <v>125</v>
+        <v>0.7788461538461539</v>
       </c>
       <c r="J94" t="n">
-        <v>0.536</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="K94" t="n">
-        <v>0.6442307692307693</v>
+        <v>0.7415730337078652</v>
       </c>
       <c r="L94" t="n">
-        <v>0.5851528384279477</v>
+        <v>0.75</v>
       </c>
       <c r="M94" t="n">
-        <v>88</v>
+        <v>0.7457627118644068</v>
       </c>
       <c r="N94" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="O94" t="n">
-        <v>0.4477611940298508</v>
+        <v>23</v>
       </c>
       <c r="P94" t="n">
-        <v>0.3409090909090909</v>
+        <v>22</v>
       </c>
       <c r="Q94" t="n">
-        <v>0.3870967741935484</v>
-      </c>
-      <c r="R94" t="n">
-        <v>67</v>
-      </c>
-      <c r="S94" t="n">
-        <v>37</v>
-      </c>
-      <c r="T94" t="n">
-        <v>58</v>
-      </c>
-      <c r="U94" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
     </row>
     <row r="95">
@@ -7957,52 +6612,40 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.671875</v>
       </c>
       <c r="G95" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.671875</v>
       </c>
       <c r="H95" t="n">
-        <v>96</v>
+        <v>0.6633663366336634</v>
       </c>
       <c r="I95" t="n">
-        <v>117</v>
+        <v>0.6979166666666666</v>
       </c>
       <c r="J95" t="n">
-        <v>0.4786324786324787</v>
+        <v>0.6802030456852792</v>
       </c>
       <c r="K95" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.6813186813186813</v>
       </c>
       <c r="L95" t="n">
-        <v>0.5258215962441315</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="M95" t="n">
-        <v>96</v>
+        <v>0.663101604278075</v>
       </c>
       <c r="N95" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="O95" t="n">
-        <v>0.4666666666666667</v>
+        <v>29</v>
       </c>
       <c r="P95" t="n">
-        <v>0.3645833333333333</v>
+        <v>34</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.4093567251461988</v>
-      </c>
-      <c r="R95" t="n">
-        <v>56</v>
-      </c>
-      <c r="S95" t="n">
-        <v>40</v>
-      </c>
-      <c r="T95" t="n">
-        <v>61</v>
-      </c>
-      <c r="U95" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96">
@@ -8024,52 +6667,40 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.734375</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.734375</v>
       </c>
       <c r="H96" t="n">
-        <v>94</v>
+        <v>0.7087378640776699</v>
       </c>
       <c r="I96" t="n">
-        <v>139</v>
+        <v>0.776595744680851</v>
       </c>
       <c r="J96" t="n">
-        <v>0.4748201438848921</v>
+        <v>0.7411167512690355</v>
       </c>
       <c r="K96" t="n">
-        <v>0.7021276595744681</v>
+        <v>0.7640449438202247</v>
       </c>
       <c r="L96" t="n">
-        <v>0.5665236051502146</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="M96" t="n">
-        <v>98</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="N96" t="n">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="O96" t="n">
-        <v>0.4716981132075472</v>
+        <v>21</v>
       </c>
       <c r="P96" t="n">
-        <v>0.2551020408163265</v>
+        <v>30</v>
       </c>
       <c r="Q96" t="n">
-        <v>0.3311258278145695</v>
-      </c>
-      <c r="R96" t="n">
-        <v>66</v>
-      </c>
-      <c r="S96" t="n">
-        <v>28</v>
-      </c>
-      <c r="T96" t="n">
-        <v>73</v>
-      </c>
-      <c r="U96" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97">
@@ -8091,52 +6722,40 @@
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.609375</v>
       </c>
       <c r="G97" t="n">
-        <v>0.5364583333333334</v>
+        <v>0.609375</v>
       </c>
       <c r="H97" t="n">
-        <v>94</v>
+        <v>0.5871559633027523</v>
       </c>
       <c r="I97" t="n">
-        <v>99</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="J97" t="n">
-        <v>0.5252525252525253</v>
+        <v>0.6305418719211823</v>
       </c>
       <c r="K97" t="n">
-        <v>0.5531914893617021</v>
+        <v>0.6385542168674698</v>
       </c>
       <c r="L97" t="n">
-        <v>0.5388601036269431</v>
+        <v>0.5408163265306123</v>
       </c>
       <c r="M97" t="n">
-        <v>98</v>
+        <v>0.5856353591160222</v>
       </c>
       <c r="N97" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="O97" t="n">
-        <v>0.5483870967741935</v>
+        <v>30</v>
       </c>
       <c r="P97" t="n">
-        <v>0.5204081632653061</v>
+        <v>45</v>
       </c>
       <c r="Q97" t="n">
-        <v>0.5340314136125655</v>
-      </c>
-      <c r="R97" t="n">
-        <v>52</v>
-      </c>
-      <c r="S97" t="n">
-        <v>42</v>
-      </c>
-      <c r="T97" t="n">
-        <v>47</v>
-      </c>
-      <c r="U97" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98">
@@ -8158,52 +6777,40 @@
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="G98" t="n">
-        <v>0.5052083333333334</v>
+        <v>0.6875</v>
       </c>
       <c r="H98" t="n">
-        <v>90</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="I98" t="n">
-        <v>121</v>
+        <v>0.7111111111111111</v>
       </c>
       <c r="J98" t="n">
-        <v>0.4793388429752066</v>
+        <v>0.6808510638297872</v>
       </c>
       <c r="K98" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="L98" t="n">
-        <v>0.5497630331753555</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="M98" t="n">
-        <v>102</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="N98" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="O98" t="n">
-        <v>0.5492957746478874</v>
+        <v>26</v>
       </c>
       <c r="P98" t="n">
-        <v>0.3823529411764706</v>
+        <v>34</v>
       </c>
       <c r="Q98" t="n">
-        <v>0.4508670520231214</v>
-      </c>
-      <c r="R98" t="n">
-        <v>58</v>
-      </c>
-      <c r="S98" t="n">
-        <v>32</v>
-      </c>
-      <c r="T98" t="n">
-        <v>63</v>
-      </c>
-      <c r="U98" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99">
@@ -8225,52 +6832,40 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4635416666666667</v>
+        <v>0.6927083333333334</v>
       </c>
       <c r="H99" t="n">
-        <v>101</v>
+        <v>0.723404255319149</v>
       </c>
       <c r="I99" t="n">
-        <v>122</v>
+        <v>0.6732673267326733</v>
       </c>
       <c r="J99" t="n">
-        <v>0.4918032786885246</v>
+        <v>0.6974358974358975</v>
       </c>
       <c r="K99" t="n">
-        <v>0.594059405940594</v>
+        <v>0.6632653061224489</v>
       </c>
       <c r="L99" t="n">
-        <v>0.5381165919282511</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="M99" t="n">
-        <v>91</v>
+        <v>0.6878306878306879</v>
       </c>
       <c r="N99" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="O99" t="n">
-        <v>0.4142857142857143</v>
+        <v>33</v>
       </c>
       <c r="P99" t="n">
-        <v>0.3186813186813187</v>
+        <v>26</v>
       </c>
       <c r="Q99" t="n">
-        <v>0.3602484472049689</v>
-      </c>
-      <c r="R99" t="n">
-        <v>60</v>
-      </c>
-      <c r="S99" t="n">
-        <v>41</v>
-      </c>
-      <c r="T99" t="n">
-        <v>62</v>
-      </c>
-      <c r="U99" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100">
@@ -8292,52 +6887,40 @@
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="G100" t="n">
-        <v>0.4739583333333333</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="H100" t="n">
-        <v>90</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>123</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4552845528455284</v>
+        <v>0.7263157894736842</v>
       </c>
       <c r="K100" t="n">
-        <v>0.6222222222222222</v>
+        <v>0.7717391304347826</v>
       </c>
       <c r="L100" t="n">
-        <v>0.5258215962441314</v>
+        <v>0.696078431372549</v>
       </c>
       <c r="M100" t="n">
-        <v>102</v>
+        <v>0.731958762886598</v>
       </c>
       <c r="N100" t="n">
         <v>69</v>
       </c>
       <c r="O100" t="n">
-        <v>0.5072463768115942</v>
+        <v>21</v>
       </c>
       <c r="P100" t="n">
-        <v>0.3431372549019608</v>
+        <v>31</v>
       </c>
       <c r="Q100" t="n">
-        <v>0.4093567251461988</v>
-      </c>
-      <c r="R100" t="n">
-        <v>56</v>
-      </c>
-      <c r="S100" t="n">
-        <v>34</v>
-      </c>
-      <c r="T100" t="n">
-        <v>67</v>
-      </c>
-      <c r="U100" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="101">
@@ -8359,52 +6942,40 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="G101" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.6770833333333334</v>
       </c>
       <c r="H101" t="n">
-        <v>98</v>
+        <v>0.6698113207547169</v>
       </c>
       <c r="I101" t="n">
-        <v>120</v>
+        <v>0.7244897959183674</v>
       </c>
       <c r="J101" t="n">
-        <v>0.525</v>
+        <v>0.696078431372549</v>
       </c>
       <c r="K101" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.686046511627907</v>
       </c>
       <c r="L101" t="n">
-        <v>0.5779816513761468</v>
+        <v>0.6276595744680851</v>
       </c>
       <c r="M101" t="n">
-        <v>94</v>
+        <v>0.6555555555555557</v>
       </c>
       <c r="N101" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O101" t="n">
-        <v>0.5138888888888888</v>
+        <v>27</v>
       </c>
       <c r="P101" t="n">
-        <v>0.3936170212765958</v>
+        <v>35</v>
       </c>
       <c r="Q101" t="n">
-        <v>0.4457831325301205</v>
-      </c>
-      <c r="R101" t="n">
-        <v>63</v>
-      </c>
-      <c r="S101" t="n">
-        <v>35</v>
-      </c>
-      <c r="T101" t="n">
-        <v>57</v>
-      </c>
-      <c r="U101" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -8440,10 +7011,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6083</v>
+        <v>6948</v>
       </c>
       <c r="C2" t="n">
-        <v>3471</v>
+        <v>2606</v>
       </c>
     </row>
     <row r="3">
@@ -8453,298 +7024,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6222</v>
+        <v>3400</v>
       </c>
       <c r="C3" t="n">
-        <v>3424</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>normalized_question_category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_0</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>actual_0_pred_1</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_0</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>actual_1_pred_1</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CausaleEsplicita</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>227</v>
-      </c>
-      <c r="C2" t="n">
-        <v>160</v>
-      </c>
-      <c r="D2" t="n">
-        <v>265</v>
-      </c>
-      <c r="E2" t="n">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CausaleImplicita</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>260</v>
-      </c>
-      <c r="C3" t="n">
-        <v>144</v>
-      </c>
-      <c r="D3" t="n">
-        <v>261</v>
-      </c>
-      <c r="E3" t="n">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Controfattuale</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>520</v>
-      </c>
-      <c r="C4" t="n">
-        <v>301</v>
-      </c>
-      <c r="D4" t="n">
-        <v>497</v>
-      </c>
-      <c r="E4" t="n">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ImplicitoParziale</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>488</v>
-      </c>
-      <c r="C5" t="n">
-        <v>317</v>
-      </c>
-      <c r="D5" t="n">
-        <v>473</v>
-      </c>
-      <c r="E5" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ImplicitoTot</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>591</v>
-      </c>
-      <c r="C6" t="n">
-        <v>230</v>
-      </c>
-      <c r="D6" t="n">
-        <v>565</v>
-      </c>
-      <c r="E6" t="n">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Incertezza</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>700</v>
-      </c>
-      <c r="C7" t="n">
-        <v>40</v>
-      </c>
-      <c r="D7" t="n">
-        <v>812</v>
-      </c>
-      <c r="E7" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>OutofScope</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>588</v>
-      </c>
-      <c r="C8" t="n">
-        <v>181</v>
-      </c>
-      <c r="D8" t="n">
-        <v>647</v>
-      </c>
-      <c r="E8" t="n">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pianificazione</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>510</v>
-      </c>
-      <c r="C9" t="n">
-        <v>312</v>
-      </c>
-      <c r="D9" t="n">
-        <v>509</v>
-      </c>
-      <c r="E9" t="n">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Sentiment</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>730</v>
-      </c>
-      <c r="C10" t="n">
-        <v>74</v>
-      </c>
-      <c r="D10" t="n">
-        <v>717</v>
-      </c>
-      <c r="E10" t="n">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SpazialeParziale</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>266</v>
-      </c>
-      <c r="C11" t="n">
-        <v>546</v>
-      </c>
-      <c r="D11" t="n">
-        <v>267</v>
-      </c>
-      <c r="E11" t="n">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SpazialeTotale</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>366</v>
-      </c>
-      <c r="C12" t="n">
-        <v>422</v>
-      </c>
-      <c r="D12" t="n">
-        <v>365</v>
-      </c>
-      <c r="E12" t="n">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>TemporaleDurata</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>476</v>
-      </c>
-      <c r="C13" t="n">
-        <v>337</v>
-      </c>
-      <c r="D13" t="n">
-        <v>445</v>
-      </c>
-      <c r="E13" t="n">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TemporaleParziale</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>361</v>
-      </c>
-      <c r="C14" t="n">
-        <v>407</v>
-      </c>
-      <c r="D14" t="n">
-        <v>399</v>
-      </c>
-      <c r="E14" t="n">
-        <v>433</v>
+        <v>6246</v>
       </c>
     </row>
   </sheetData>
